--- a/IEDC_content_fill/IEDC_Prototype_Datasets_Batch1_Upload_MASTER.xlsx
+++ b/IEDC_content_fill/IEDC_Prototype_Datasets_Batch1_Upload_MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan Pauliuk\FILES\ARBEIT\PROJECTS\Database\IE_DataCommons\IEDC_software\IEDC_content_fill\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0B7B03-C996-4071-BBF2-CF695E677924}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D95F90-5915-4651-A1DC-DE19ED407075}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20448" windowHeight="9684" tabRatio="603" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15143" uniqueCount="3256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15851" uniqueCount="3441">
   <si>
     <t>Description</t>
   </si>
@@ -9799,6 +9799,562 @@
   </si>
   <si>
     <t>August 4, 2025 update</t>
+  </si>
+  <si>
+    <t>3_MC_Buildings_EU_Renovation_Maintenance_Damgaard_2022</t>
+  </si>
+  <si>
+    <t>9 building types</t>
+  </si>
+  <si>
+    <t>12 major construction materials</t>
+  </si>
+  <si>
+    <t>EU27</t>
+  </si>
+  <si>
+    <t>EU aggregate</t>
+  </si>
+  <si>
+    <t>one representative value for all age-cohorts</t>
+  </si>
+  <si>
+    <t>Specific material requirement (in kg/m²) of building renovation. The material values here are added to the building during renovation</t>
+  </si>
+  <si>
+    <t>material requirement; material content; building; renovation; energy efficiency</t>
+  </si>
+  <si>
+    <t>Value(U,Y,c,r,m,v,L)</t>
+  </si>
+  <si>
+    <t>Material composition of glass measured in mass per area for strategy refurbishment (R5) applied to educational buildings, service building of age-cohort n.a. in use phase - buildings in EU27 is 6.13 kg/m², for non-energy related renovation.</t>
+  </si>
+  <si>
+    <t>[Data type] of [Aspect 5] measured in [Aspect 7] for strategy [Aspect 6] applied to [Aspect 2] of age-cohort [Aspect 3] in [Aspect 1] in [Aspect 4] is [Value].</t>
+  </si>
+  <si>
+    <t>Anders DAMGAARD</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2760/772724</t>
+  </si>
+  <si>
+    <t>pdf report</t>
+  </si>
+  <si>
+    <t>1_F_Function_FreightTransp_History_EUROSTAT</t>
+  </si>
+  <si>
+    <t>Land vehicles (road and rail)</t>
+  </si>
+  <si>
+    <t>2 vehicle types: trucks and freight trains</t>
+  </si>
+  <si>
+    <t>Function (in tkm) of freight transport provided by in-use stocks of vehicle categories</t>
+  </si>
+  <si>
+    <t>freight rail; trucks; service flows; ton km; EU; freight transport</t>
+  </si>
+  <si>
+    <t>Value(V,g,p,r,c)</t>
+  </si>
+  <si>
+    <t>Flow measured as ton-km generated by train in use phase in Croatia in 2010 is 2618 million tkm/yr.</t>
+  </si>
+  <si>
+    <t>[Data type] measured as [Aspect 1] generated by [Aspect 2] in [Aspect 3] in [Aspect 4] in [Aspect 5] is [Value].</t>
+  </si>
+  <si>
+    <t>https://ec.europa.eu/eurostat/databrowser/view/rail_go_total__custom_10629027/default/table?lang=en</t>
+  </si>
+  <si>
+    <t>dynamic web page</t>
+  </si>
+  <si>
+    <t>https://ec.europa.eu/eurostat/cache/metadata/en/rail_if_esms.htm</t>
+  </si>
+  <si>
+    <t>EUROSTAT Transport Statistics</t>
+  </si>
+  <si>
+    <t>Patricia Fortes</t>
+  </si>
+  <si>
+    <t>Numbers manually copied from original source to Excel spreadsheet</t>
+  </si>
+  <si>
+    <t>3_MC_Vehicles_CIRCOMOD</t>
+  </si>
+  <si>
+    <t>one aggregate end-use sector</t>
+  </si>
+  <si>
+    <t>about 100 different passenger vehicle and other vehicle types</t>
+  </si>
+  <si>
+    <t>all major engineering and technology materials</t>
+  </si>
+  <si>
+    <t>up to 80 different materials</t>
+  </si>
+  <si>
+    <t>Values for 8 single-countries and globally aggregate/representative values</t>
+  </si>
+  <si>
+    <t>1976-2060</t>
+  </si>
+  <si>
+    <t>values for individual age-cohorts and for time ranges</t>
+  </si>
+  <si>
+    <t>material composition of vehicles in kg of engineering material by vehicle or by component, compiled from various sources (see comment field).</t>
+  </si>
+  <si>
+    <t>material composition; material content; vehicles; manufacturing; engineering materials; cars; trains; trucks; busses</t>
+  </si>
+  <si>
+    <t>Data compiled from different sources as part of the EU Horizon CIRCOMOD projects input database collection effort. See the comment for the data source of each data point.</t>
+  </si>
+  <si>
+    <t>Value(U,g,c,r,k,m,v,L)</t>
+  </si>
+  <si>
+    <t>Material composition measured as mass per unit of copper in entire device of private car in use phase - vehicles in 1995 in China for resource efficiency strategy none is 20.11 kg.</t>
+  </si>
+  <si>
+    <t>[Data type] measured as [Aspect 8] of [Aspect 6] in [Aspect 5] of [Aspect 2] in [Aspect 1] in [Aspect 3] in [Aspect 4] for resource efficiency strategy [Aspect 7] is [Value].</t>
+  </si>
+  <si>
+    <t>Further checking and formatting by Stefan Pauliuk for IEDC upload</t>
+  </si>
+  <si>
+    <t>1_F_Function_PassTransp_History_EUROSTAT</t>
+  </si>
+  <si>
+    <t>4 vehicle types: private cars, motorcycles, coaches, passenger rail</t>
+  </si>
+  <si>
+    <t>Function (in pkm) of passenger transport provided by in-use stocks of vehicle categories</t>
+  </si>
+  <si>
+    <t>passenger rail; motorcyle; coaches; busses; passenger vehicles; service flows; passenger km; EU; passenger transport</t>
+  </si>
+  <si>
+    <t>Flow measured as passenger-km generated by passenger vehicles in use phase in Czech Republic in 2009 is 72290 million pkm/yr.</t>
+  </si>
+  <si>
+    <t>https://ec.europa.eu/eurostat/databrowser/view/road_pa_mov/default/table?lang=en&amp;category=road.road_pa</t>
+  </si>
+  <si>
+    <t>3_MC_Buildings_Austria_Renovation_Maintenance_Lederer_2021</t>
+  </si>
+  <si>
+    <t>4 building types</t>
+  </si>
+  <si>
+    <t>3 major construction materials</t>
+  </si>
+  <si>
+    <t>country-level average/aggregate</t>
+  </si>
+  <si>
+    <t>1800-1980</t>
+  </si>
+  <si>
+    <t>three age-cohort ranges</t>
+  </si>
+  <si>
+    <t>Material composition of glass measured in mass per area for strategy refurbishment (R5) applied to service building of age-cohort 1946-1980 in use phase - buildings in Austria is 3.35 kg/m², for energy related renovation.</t>
+  </si>
+  <si>
+    <t>[Data type] of [Aspect 5] measured in [Aspect 7] for strategy [Aspect 6] applied to [Aspect 2] of age-cohort [Aspect 3] in [Aspect 1] in [Aspect 4] is [Value], [comment].</t>
+  </si>
+  <si>
+    <t>Jakob LEDERER</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jclepro.2020.125566</t>
+  </si>
+  <si>
+    <t>3_MC_Wind_Turbines_Farina_Anctil_2020</t>
+  </si>
+  <si>
+    <t>Mass per capacity</t>
+  </si>
+  <si>
+    <t>1 end use sector for electricity generation</t>
+  </si>
+  <si>
+    <t>wind turbines</t>
+  </si>
+  <si>
+    <t>onshore and offshore wind turbine technology, global average/representative values by age-cohort</t>
+  </si>
+  <si>
+    <t>13 major construction materials and technology metals</t>
+  </si>
+  <si>
+    <t>Global-level average/aggregate</t>
+  </si>
+  <si>
+    <t>1991-2016</t>
+  </si>
+  <si>
+    <t>single-year values for a number of age-cohorts within the range.</t>
+  </si>
+  <si>
+    <t>Specific material requirement (in t/GW of installed capacity) of wind turbines, onshore and offshore.</t>
+  </si>
+  <si>
+    <t>material requirement; material content; material composition; energy system; wind turbines; electricity generation; wind power</t>
+  </si>
+  <si>
+    <t>Data were provided as xlsx (supplement of DOI https://doi.org/10.1016/j.jclepro.2025.145794) by Fernanda Godoy Leon from original pdf report/dataset and converted from there. For additional conversion and assumption done by Fernanda Leon, see the comment for each data point.</t>
+  </si>
+  <si>
+    <t>Value(U,g,c,r,m)</t>
+  </si>
+  <si>
+    <t>Material composition measured as mass per capacity of aluminium contained in capacity of wind turbines, onshoreof age-cohort 1992 in use phase - electricity generation in Global is 2,334 t/MW.</t>
+  </si>
+  <si>
+    <t>[Data type] measured as [Layer] of [Aspect 5] contained in capacity of [Aspect 2] of age-cohort [Aspect 3] in [Aspect 1] in [Aspect 4] is [Value].</t>
+  </si>
+  <si>
+    <t>Angela FARINA</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.resconrec.2021.105938</t>
+  </si>
+  <si>
+    <t>Data were provided as xlsx (supplement of DOI https://doi.org/10.1016/j.jclepro.2025.145794) by Fernanda Godoy Leon from original pdf report/dataset.</t>
+  </si>
+  <si>
+    <t>Data extracted from xlsx (supplement of DOI https://doi.org/10.1016/j.jclepro.2025.145794 compiled by Fernanda Godoy Leon from original pdf) and manually copied to Excel spreadsheet.</t>
+  </si>
+  <si>
+    <t>3_MC_Wind_Turbines_Carrara_2020</t>
+  </si>
+  <si>
+    <t>four different wind turbine technologies</t>
+  </si>
+  <si>
+    <t>20 major construction materials and technology metals</t>
+  </si>
+  <si>
+    <t>EU-level average/aggregate</t>
+  </si>
+  <si>
+    <t>one representative value for the age-cohort range</t>
+  </si>
+  <si>
+    <t>Specific material requirement (in t/GW of installed capacity) of wind turbines, by technology.</t>
+  </si>
+  <si>
+    <t>Data were provided as xlsx (supplement of DOI https://doi.org/10.1016/j.jclepro.2025.145794) by Fernanda Godoy Leon from original pdf report/dataset and converted from there.</t>
+  </si>
+  <si>
+    <t>Material composition measured as mass per capacity of zinc contained in capacity of wind turbines, direct drive turbines include low-speed EESG (type D-EE) of age-cohort ca. 2020 in use phase - electricity generation in EU is 5500 t/GW.</t>
+  </si>
+  <si>
+    <t>Samuel CARRARA</t>
+  </si>
+  <si>
+    <t>https://doi.org/doi:10.2760/160859</t>
+  </si>
+  <si>
+    <t>4_PY_Buildings_CIRCOMOD</t>
+  </si>
+  <si>
+    <t>product manufacturing processes: construction sector</t>
+  </si>
+  <si>
+    <t>one aggregate manufacturing sector</t>
+  </si>
+  <si>
+    <t>buildings and infrastructure</t>
+  </si>
+  <si>
+    <t>one aggregate construction sector/process</t>
+  </si>
+  <si>
+    <t>cement, steel, wood, aluminium, copper</t>
+  </si>
+  <si>
+    <t>aggregate global values, some country-specific values for China</t>
+  </si>
+  <si>
+    <t>region specific</t>
+  </si>
+  <si>
+    <t>Material yield factors for the construction stage in the construction sector</t>
+  </si>
+  <si>
+    <t>material efficiency; construction yield; material efficiency; buildings; construction; process efficiency</t>
+  </si>
+  <si>
+    <t>Value(m,g,t,r,v,p)</t>
+  </si>
+  <si>
+    <t>Yield coefficient measured as mass ratio of concrete manufactured into buildings in process manufacturing of buildings and infrastructure in Global in 2015 for strategy fabrication yield improvement is 0.985.</t>
+  </si>
+  <si>
+    <t>[Data type] measured as [data layer] of [Aspect 1] manufactured into [Aspect 2] in process [Aspect 6] in [Aspect 4] in [Aspect 3] for strategy [Aspect 5] is [Value].</t>
+  </si>
+  <si>
+    <t>3_MC_Wind_Turbines_Godoy_Leon_2025</t>
+  </si>
+  <si>
+    <t>four different wind turbine technologies, partly divided into onshore and offshore</t>
+  </si>
+  <si>
+    <t>9 major construction and technology metals</t>
+  </si>
+  <si>
+    <t>2016-2021</t>
+  </si>
+  <si>
+    <t>Material composition measured as mass per capacity of steel, chromium contained in capacity of wind turbines, offshore, medium/high-speed permanent magnet synchronous generator (PMSG) (type E-PM) of age-cohort 2016-2021 in use phase - electricity generation in EU is 4740 t/GW.</t>
+  </si>
+  <si>
+    <t>María Fernanda GODOY LEON</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jclepro.2025.145794</t>
+  </si>
+  <si>
+    <t>pdf journal paper</t>
+  </si>
+  <si>
+    <t>4_SHR_ReMeasures_Buildings_CIRCOMOD</t>
+  </si>
+  <si>
+    <t>waste management industries</t>
+  </si>
+  <si>
+    <t>one aggregate building type</t>
+  </si>
+  <si>
+    <t>major building materials including steel, concrete, wood but also copper and aluminium</t>
+  </si>
+  <si>
+    <t>Global, EU</t>
+  </si>
+  <si>
+    <t>region/global average</t>
+  </si>
+  <si>
+    <t>potential for reuse and recycling of different components, commodities, and materials of buildings</t>
+  </si>
+  <si>
+    <t>buildings; reuse; recycling; circular economy potential;</t>
+  </si>
+  <si>
+    <t>Value(m,B,U,p,v,t,r,L)</t>
+  </si>
+  <si>
+    <t>General ratio of flows linked to a process measured as recycling potential of materials or components extracted from end-of-life goods, expressed as mass ratio of bricks in buildings from use phase - buildings handled in waste management for strategy recycle (R8) in the European Union in 2020 is 79%.</t>
+  </si>
+  <si>
+    <t>[Data type] measured as [Aspect 8] of [Aspect 1] in [Aspect 2] from [Aspect 3] handled in [Aspect 4] for strategy [Aspect 5] in [Aspect 6] in [Aspect 7] is [Value].</t>
+  </si>
+  <si>
+    <t>August 24, 2025 update</t>
+  </si>
+  <si>
+    <t>5_PP_buildings_EoL_mgmt_costs_and_labor_requirements_CARO_2024</t>
+  </si>
+  <si>
+    <t>EoL processes</t>
+  </si>
+  <si>
+    <t>recycling, landfilling, incineration</t>
+  </si>
+  <si>
+    <t>waste engineering materials</t>
+  </si>
+  <si>
+    <t>12 different waste material groups</t>
+  </si>
+  <si>
+    <t>CAPEX, OPEX, and FTE (full-time equivalent) of treating 12 construction and demolition waste material fractions in three different waste treatment processes, expressed in Indicator/ton.
+pathways and treatment technologies</t>
+  </si>
+  <si>
+    <t>waste treatment; recycling, landfilling; incineration; waste management; CAPEX; OPEX; EoL; end-of-life; waste</t>
+  </si>
+  <si>
+    <t>Value(M,p,r,t,E)</t>
+  </si>
+  <si>
+    <t>Process parameter for the treatment of aluminium scrap in recycling in European Union in 2020 has CAPEX of 19.14 EUR/ton.</t>
+  </si>
+  <si>
+    <t>[Data type] for the treatment of [Aspect 1] in [Aspect 2] in [Aspect 3] in [Aspect 4] has [Aspect 5] of [Value].</t>
+  </si>
+  <si>
+    <t>Dario CARO</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.scitotenv.2023.168295</t>
+  </si>
+  <si>
+    <t>Appendix. Supplementary materials</t>
+  </si>
+  <si>
+    <t>4_PC_Investment_Costs_Building_Renovations_EU_2019</t>
+  </si>
+  <si>
+    <t>Process costs</t>
+  </si>
+  <si>
+    <t>monetary (constant prices)</t>
+  </si>
+  <si>
+    <t>building use phase - renovation</t>
+  </si>
+  <si>
+    <t>on aggregate process</t>
+  </si>
+  <si>
+    <t>building type</t>
+  </si>
+  <si>
+    <t>residential and non-residential building</t>
+  </si>
+  <si>
+    <t>EU country level</t>
+  </si>
+  <si>
+    <t>2012-2016</t>
+  </si>
+  <si>
+    <t>Average values für period 2012-2016</t>
+  </si>
+  <si>
+    <t>CAPEX per m² for various renovation types with specific energy savings/target energy standards</t>
+  </si>
+  <si>
+    <t>CAPEX; costs; renovation; energy; primary energy savings; buildigs; EU; retrofit</t>
+  </si>
+  <si>
+    <t>Value(E,r,t,g,p)</t>
+  </si>
+  <si>
+    <t>Process costs measured as costs (CAPEX) for achieving 3-30% primary energy saving on monetary (constant prices) layer for residential buildings in use phase - buildings in Czech Republic in 2012-2016 is 62 EUR/m².</t>
+  </si>
+  <si>
+    <t>[Data type] measured as [Aspect 1] on [Layer] for [Aspect 4] in [Aspect 5] in [Aspect 2] in [Aspect 3] is [Value].</t>
+  </si>
+  <si>
+    <t>https://energy.ec.europa.eu/publications/comprehensive-study-building-energy-renovation-activities-and-uptake-nearly-zero-energy-buildings-eu_en</t>
+  </si>
+  <si>
+    <t>doi: 10.2833/14675</t>
+  </si>
+  <si>
+    <t>Numbers extracted from report and converted to IEDC template</t>
+  </si>
+  <si>
+    <t>August 28, 2025 update</t>
+  </si>
+  <si>
+    <t>1_F_Lithium_and_Cobalt_Ore_Extraction_Refining_TAN_2024</t>
+  </si>
+  <si>
+    <t>mining, smelting, refining</t>
+  </si>
+  <si>
+    <t>three aggregate process steps</t>
+  </si>
+  <si>
+    <t>lithium and cobalt as ore, oxide, carbonates, chlorides, etc.</t>
+  </si>
+  <si>
+    <t>individual values for main producing countries</t>
+  </si>
+  <si>
+    <t>extraction and refining of metal ores of lithium and cobalt, 2019, by country</t>
+  </si>
+  <si>
+    <t>mining; metals; production; extraction; lithium; cobalt; 2019; global; refining</t>
+  </si>
+  <si>
+    <t>Metal in ore is counted</t>
+  </si>
+  <si>
+    <t>Value(z,o,d,m,r,t)</t>
+  </si>
+  <si>
+    <t>Mass of flow of cobalt flowing from Murrin Murrin in mining (reserves) to market for extracted resources in Australia in 2019 is 3.04 kt/yr.</t>
+  </si>
+  <si>
+    <t>[Layer] of [Data type] of [Aspect 4] flowing from [Aspect 1] in [Aspect 2] to [Aspect 3] in [Aspect 5] in [Aspect 6] is [Value].</t>
+  </si>
+  <si>
+    <t>Juan TAN</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.resconrec.2024.107788</t>
+  </si>
+  <si>
+    <t>1_F_Neodymium_Global_Qiance_LIU_2022</t>
+  </si>
+  <si>
+    <t>mining, benefication, purification, semi-product manufacturing</t>
+  </si>
+  <si>
+    <t>different material life cycle processes</t>
+  </si>
+  <si>
+    <t>major end-use goods</t>
+  </si>
+  <si>
+    <t>ca. 20 semi-finished and finished goods</t>
+  </si>
+  <si>
+    <t>neodymium</t>
+  </si>
+  <si>
+    <t>Global, China, EU, Japan, US, RoW</t>
+  </si>
+  <si>
+    <t>1990-2020</t>
+  </si>
+  <si>
+    <t>Values aggregated for three decades</t>
+  </si>
+  <si>
+    <t>Neodymium flows across different life cycle stages, aggregated by decade. From Liu et al. (2022): "Tracking Three Decades of Global Neodymium Stocks and Flows with a Trade-Linked Multiregional Material Flow Analysis"</t>
+  </si>
+  <si>
+    <t>mining; metals; production; extraction; neodymium; MFA; trade</t>
+  </si>
+  <si>
+    <t>Compiled from SI of the study</t>
+  </si>
+  <si>
+    <t>Value(o,B,d,F,M,t,O,D)</t>
+  </si>
+  <si>
+    <t>Mass of flow of neodymium flowing in form of rare earth elements (REE) metal from fabrication in China to semi-products; NiMH battery in manufacturing in China in 1990-1999 is 0.1 kt/yr.</t>
+  </si>
+  <si>
+    <t>[Layer] of [Data type] of [Aspect 5] flowing in form of [Aspect 2] from [Aspect 1] in [Aspect 7] to [Aspect 4] in [Aspect 3] in [Aspect 8] in [Aspect 6] is [value].</t>
+  </si>
+  <si>
+    <t>All rights reserved</t>
+  </si>
+  <si>
+    <t>Qiance LIU</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1021/acs.est.2c02247</t>
+  </si>
+  <si>
+    <t>12..6.25</t>
   </si>
 </sst>
 </file>
@@ -9808,7 +10364,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -10196,7 +10752,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -10575,6 +11131,41 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10929,7 +11520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3"/>
   <cols>
     <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33" style="51" customWidth="1"/>
@@ -10938,14 +11529,14 @@
     <col min="8" max="8" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11">
       <c r="B2" s="34" t="s">
         <v>186</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11">
       <c r="B3" s="32"/>
       <c r="C3" s="31" t="s">
         <v>181</v>
@@ -10975,8 +11566,8 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="221" t="s">
+    <row r="4" spans="2:11">
+      <c r="B4" s="234" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="28" t="s">
@@ -11007,8 +11598,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="221"/>
+    <row r="5" spans="2:11">
+      <c r="B5" s="234"/>
       <c r="C5" s="26" t="s">
         <v>422</v>
       </c>
@@ -11037,8 +11628,8 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="222" t="s">
+    <row r="6" spans="2:11" ht="13.3" customHeight="1">
+      <c r="B6" s="235" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="26" t="s">
@@ -11053,8 +11644,8 @@
       <c r="J6" s="121"/>
       <c r="K6" s="121"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="222"/>
+    <row r="7" spans="2:11">
+      <c r="B7" s="235"/>
       <c r="C7" s="26" t="s">
         <v>424</v>
       </c>
@@ -11067,8 +11658,8 @@
       <c r="J7" s="121"/>
       <c r="K7" s="121"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="222"/>
+    <row r="8" spans="2:11">
+      <c r="B8" s="235"/>
       <c r="C8" s="26" t="s">
         <v>425</v>
       </c>
@@ -11081,8 +11672,8 @@
       <c r="J8" s="121"/>
       <c r="K8" s="121"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B9" s="222"/>
+    <row r="9" spans="2:11">
+      <c r="B9" s="235"/>
       <c r="C9" s="28" t="s">
         <v>426</v>
       </c>
@@ -11095,8 +11686,8 @@
       <c r="J9" s="121"/>
       <c r="K9" s="121"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B10" s="222"/>
+    <row r="10" spans="2:11">
+      <c r="B10" s="235"/>
       <c r="C10" s="27" t="s">
         <v>427</v>
       </c>
@@ -11109,8 +11700,8 @@
       <c r="J10" s="121"/>
       <c r="K10" s="121"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B11" s="222"/>
+    <row r="11" spans="2:11">
+      <c r="B11" s="235"/>
       <c r="C11" s="27" t="s">
         <v>428</v>
       </c>
@@ -11123,8 +11714,8 @@
       <c r="J11" s="121"/>
       <c r="K11" s="121"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B12" s="222"/>
+    <row r="12" spans="2:11">
+      <c r="B12" s="235"/>
       <c r="C12" s="27" t="s">
         <v>429</v>
       </c>
@@ -11137,8 +11728,8 @@
       <c r="J12" s="121"/>
       <c r="K12" s="121"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B13" s="222"/>
+    <row r="13" spans="2:11">
+      <c r="B13" s="235"/>
       <c r="C13" s="27" t="s">
         <v>430</v>
       </c>
@@ -11151,8 +11742,8 @@
       <c r="J13" s="121"/>
       <c r="K13" s="121"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B14" s="222"/>
+    <row r="14" spans="2:11">
+      <c r="B14" s="235"/>
       <c r="C14" s="27" t="s">
         <v>431</v>
       </c>
@@ -11165,8 +11756,8 @@
       <c r="J14" s="121"/>
       <c r="K14" s="121"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B15" s="222"/>
+    <row r="15" spans="2:11">
+      <c r="B15" s="235"/>
       <c r="C15" s="27" t="s">
         <v>432</v>
       </c>
@@ -11179,8 +11770,8 @@
       <c r="J15" s="121"/>
       <c r="K15" s="121"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B16" s="222"/>
+    <row r="16" spans="2:11">
+      <c r="B16" s="235"/>
       <c r="C16" s="27" t="s">
         <v>433</v>
       </c>
@@ -11193,8 +11784,8 @@
       <c r="J16" s="121"/>
       <c r="K16" s="121"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B17" s="222"/>
+    <row r="17" spans="2:11">
+      <c r="B17" s="235"/>
       <c r="C17" s="27" t="s">
         <v>434</v>
       </c>
@@ -11207,8 +11798,8 @@
       <c r="J17" s="121"/>
       <c r="K17" s="121"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B18" s="222"/>
+    <row r="18" spans="2:11">
+      <c r="B18" s="235"/>
       <c r="C18" s="27" t="s">
         <v>435</v>
       </c>
@@ -11221,8 +11812,8 @@
       <c r="J18" s="121"/>
       <c r="K18" s="121"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B19" s="223" t="s">
+    <row r="19" spans="2:11">
+      <c r="B19" s="236" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="27" t="s">
@@ -11249,8 +11840,8 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B20" s="223"/>
+    <row r="20" spans="2:11">
+      <c r="B20" s="236"/>
       <c r="C20" s="27" t="s">
         <v>437</v>
       </c>
@@ -11279,8 +11870,8 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B21" s="223"/>
+    <row r="21" spans="2:11">
+      <c r="B21" s="236"/>
       <c r="C21" s="27" t="s">
         <v>438</v>
       </c>
@@ -11305,8 +11896,8 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="224" t="s">
+    <row r="22" spans="2:11" ht="13.3" customHeight="1">
+      <c r="B22" s="237" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="26" t="s">
@@ -11335,8 +11926,8 @@
         <v>860</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B23" s="224"/>
+    <row r="23" spans="2:11">
+      <c r="B23" s="237"/>
       <c r="C23" s="26" t="s">
         <v>440</v>
       </c>
@@ -11349,8 +11940,8 @@
       <c r="J23" s="121"/>
       <c r="K23" s="121"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B24" s="224"/>
+    <row r="24" spans="2:11">
+      <c r="B24" s="237"/>
       <c r="C24" s="25" t="s">
         <v>441</v>
       </c>
@@ -11363,8 +11954,8 @@
       <c r="J24" s="121"/>
       <c r="K24" s="121"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B25" s="224"/>
+    <row r="25" spans="2:11">
+      <c r="B25" s="237"/>
       <c r="C25" s="25" t="s">
         <v>443</v>
       </c>
@@ -11389,8 +11980,8 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B26" s="224"/>
+    <row r="26" spans="2:11">
+      <c r="B26" s="237"/>
       <c r="C26" s="25" t="s">
         <v>444</v>
       </c>
@@ -11405,8 +11996,8 @@
       <c r="J26" s="121"/>
       <c r="K26" s="121"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B27" s="224"/>
+    <row r="27" spans="2:11">
+      <c r="B27" s="237"/>
       <c r="C27" s="25" t="s">
         <v>445</v>
       </c>
@@ -11419,8 +12010,8 @@
       <c r="J27" s="121"/>
       <c r="K27" s="121"/>
     </row>
-    <row r="28" spans="2:11" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="225" t="s">
+    <row r="28" spans="2:11" ht="13.3" customHeight="1">
+      <c r="B28" s="238" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="25" t="s">
@@ -11451,8 +12042,8 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B29" s="225"/>
+    <row r="29" spans="2:11">
+      <c r="B29" s="238"/>
       <c r="C29" s="25" t="s">
         <v>447</v>
       </c>
@@ -11481,8 +12072,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B30" s="218" t="s">
+    <row r="30" spans="2:11">
+      <c r="B30" s="231" t="s">
         <v>185</v>
       </c>
       <c r="C30" s="107" t="s">
@@ -11497,8 +12088,8 @@
       <c r="J30" s="181"/>
       <c r="K30" s="181"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B31" s="219"/>
+    <row r="31" spans="2:11">
+      <c r="B31" s="232"/>
       <c r="C31" s="108" t="s">
         <v>449</v>
       </c>
@@ -11511,8 +12102,8 @@
       <c r="J31" s="164"/>
       <c r="K31" s="164"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B32" s="220"/>
+    <row r="32" spans="2:11">
+      <c r="B32" s="233"/>
       <c r="C32" s="109" t="s">
         <v>450</v>
       </c>
@@ -11541,7 +12132,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:AF39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3"/>
   <cols>
     <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
@@ -11563,7 +12154,7 @@
     <col min="23" max="23" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:32">
       <c r="B2" s="34" t="s">
         <v>184</v>
       </c>
@@ -11580,7 +12171,7 @@
       <c r="AE2" s="105"/>
       <c r="AF2" s="105"/>
     </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:32">
       <c r="B3" s="32"/>
       <c r="C3" s="17" t="s">
         <v>181</v>
@@ -11671,8 +12262,8 @@
       </c>
       <c r="AF3" s="105"/>
     </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B4" s="226" t="s">
+    <row r="4" spans="2:32">
+      <c r="B4" s="239" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="53" t="s">
@@ -11764,8 +12355,8 @@
       </c>
       <c r="AF4" s="105"/>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B5" s="227"/>
+    <row r="5" spans="2:32">
+      <c r="B5" s="240"/>
       <c r="C5" s="54" t="s">
         <v>452</v>
       </c>
@@ -11855,7 +12446,7 @@
       </c>
       <c r="AF5" s="105"/>
     </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:32">
       <c r="B6" s="33"/>
       <c r="C6" s="54" t="s">
         <v>453</v>
@@ -11944,7 +12535,7 @@
       </c>
       <c r="AF6" s="105"/>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:32">
       <c r="B7" s="50" t="s">
         <v>3</v>
       </c>
@@ -12035,8 +12626,8 @@
       </c>
       <c r="AF7" s="105"/>
     </row>
-    <row r="8" spans="2:32" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="222" t="s">
+    <row r="8" spans="2:32" ht="13.3" customHeight="1">
+      <c r="B8" s="235" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
@@ -12126,8 +12717,8 @@
       </c>
       <c r="AF8" s="105"/>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B9" s="222"/>
+    <row r="9" spans="2:32">
+      <c r="B9" s="235"/>
       <c r="C9" s="54" t="s">
         <v>424</v>
       </c>
@@ -12215,8 +12806,8 @@
       </c>
       <c r="AF9" s="105"/>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B10" s="222"/>
+    <row r="10" spans="2:32">
+      <c r="B10" s="235"/>
       <c r="C10" s="54" t="s">
         <v>425</v>
       </c>
@@ -12304,8 +12895,8 @@
       </c>
       <c r="AF10" s="105"/>
     </row>
-    <row r="11" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B11" s="222"/>
+    <row r="11" spans="2:32" ht="13.8">
+      <c r="B11" s="235"/>
       <c r="C11" s="55" t="s">
         <v>426</v>
       </c>
@@ -12393,8 +12984,8 @@
       </c>
       <c r="AF11" s="105"/>
     </row>
-    <row r="12" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B12" s="222"/>
+    <row r="12" spans="2:32" ht="13.8">
+      <c r="B12" s="235"/>
       <c r="C12" s="56" t="s">
         <v>427</v>
       </c>
@@ -12482,8 +13073,8 @@
       </c>
       <c r="AF12" s="105"/>
     </row>
-    <row r="13" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B13" s="222"/>
+    <row r="13" spans="2:32" ht="13.8">
+      <c r="B13" s="235"/>
       <c r="C13" s="56" t="s">
         <v>428</v>
       </c>
@@ -12571,8 +13162,8 @@
       </c>
       <c r="AF13" s="105"/>
     </row>
-    <row r="14" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="222"/>
+    <row r="14" spans="2:32" ht="13.8">
+      <c r="B14" s="235"/>
       <c r="C14" s="56" t="s">
         <v>429</v>
       </c>
@@ -12660,8 +13251,8 @@
       </c>
       <c r="AF14" s="105"/>
     </row>
-    <row r="15" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="222"/>
+    <row r="15" spans="2:32" ht="13.8">
+      <c r="B15" s="235"/>
       <c r="C15" s="56" t="s">
         <v>430</v>
       </c>
@@ -12749,8 +13340,8 @@
       </c>
       <c r="AF15" s="105"/>
     </row>
-    <row r="16" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="222"/>
+    <row r="16" spans="2:32" ht="13.8">
+      <c r="B16" s="235"/>
       <c r="C16" s="56" t="s">
         <v>431</v>
       </c>
@@ -12838,8 +13429,8 @@
       </c>
       <c r="AF16" s="105"/>
     </row>
-    <row r="17" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B17" s="222"/>
+    <row r="17" spans="2:32" ht="13.8">
+      <c r="B17" s="235"/>
       <c r="C17" s="56" t="s">
         <v>432</v>
       </c>
@@ -12927,8 +13518,8 @@
       </c>
       <c r="AF17" s="105"/>
     </row>
-    <row r="18" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B18" s="222"/>
+    <row r="18" spans="2:32" ht="13.8">
+      <c r="B18" s="235"/>
       <c r="C18" s="56" t="s">
         <v>433</v>
       </c>
@@ -13016,8 +13607,8 @@
       </c>
       <c r="AF18" s="105"/>
     </row>
-    <row r="19" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B19" s="222"/>
+    <row r="19" spans="2:32">
+      <c r="B19" s="235"/>
       <c r="C19" s="56" t="s">
         <v>434</v>
       </c>
@@ -13105,8 +13696,8 @@
       </c>
       <c r="AF19" s="105"/>
     </row>
-    <row r="20" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B20" s="222"/>
+    <row r="20" spans="2:32" ht="13.8">
+      <c r="B20" s="235"/>
       <c r="C20" s="56" t="s">
         <v>435</v>
       </c>
@@ -13194,8 +13785,8 @@
       </c>
       <c r="AF20" s="105"/>
     </row>
-    <row r="21" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B21" s="223" t="s">
+    <row r="21" spans="2:32" ht="13.8">
+      <c r="B21" s="236" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="56" t="s">
@@ -13285,8 +13876,8 @@
       </c>
       <c r="AF21" s="105"/>
     </row>
-    <row r="22" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B22" s="223"/>
+    <row r="22" spans="2:32" ht="13.8">
+      <c r="B22" s="236"/>
       <c r="C22" s="56" t="s">
         <v>437</v>
       </c>
@@ -13376,8 +13967,8 @@
       </c>
       <c r="AF22" s="105"/>
     </row>
-    <row r="23" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B23" s="223"/>
+    <row r="23" spans="2:32">
+      <c r="B23" s="236"/>
       <c r="C23" s="56" t="s">
         <v>454</v>
       </c>
@@ -13465,8 +14056,8 @@
       </c>
       <c r="AF23" s="105"/>
     </row>
-    <row r="24" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B24" s="223"/>
+    <row r="24" spans="2:32" ht="13.8">
+      <c r="B24" s="236"/>
       <c r="C24" s="56" t="s">
         <v>438</v>
       </c>
@@ -13548,8 +14139,8 @@
       <c r="AE24" s="164"/>
       <c r="AF24" s="105"/>
     </row>
-    <row r="25" spans="2:32" ht="13.3" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="224" t="s">
+    <row r="25" spans="2:32" ht="13.3" customHeight="1">
+      <c r="B25" s="237" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="54" t="s">
@@ -13639,8 +14230,8 @@
       </c>
       <c r="AF25" s="105"/>
     </row>
-    <row r="26" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B26" s="224"/>
+    <row r="26" spans="2:32">
+      <c r="B26" s="237"/>
       <c r="C26" s="54" t="s">
         <v>440</v>
       </c>
@@ -13728,8 +14319,8 @@
       </c>
       <c r="AF26" s="105"/>
     </row>
-    <row r="27" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B27" s="224"/>
+    <row r="27" spans="2:32">
+      <c r="B27" s="237"/>
       <c r="C27" s="13" t="s">
         <v>441</v>
       </c>
@@ -13817,8 +14408,8 @@
       </c>
       <c r="AF27" s="105"/>
     </row>
-    <row r="28" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B28" s="224"/>
+    <row r="28" spans="2:32">
+      <c r="B28" s="237"/>
       <c r="C28" s="13" t="s">
         <v>443</v>
       </c>
@@ -13906,8 +14497,8 @@
       </c>
       <c r="AF28" s="105"/>
     </row>
-    <row r="29" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B29" s="224"/>
+    <row r="29" spans="2:32" ht="13.8">
+      <c r="B29" s="237"/>
       <c r="C29" s="13" t="s">
         <v>444</v>
       </c>
@@ -13995,8 +14586,8 @@
       </c>
       <c r="AF29" s="105"/>
     </row>
-    <row r="30" spans="2:32" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B30" s="224"/>
+    <row r="30" spans="2:32" ht="13.8">
+      <c r="B30" s="237"/>
       <c r="C30" s="13" t="s">
         <v>445</v>
       </c>
@@ -14084,8 +14675,8 @@
       </c>
       <c r="AF30" s="105"/>
     </row>
-    <row r="31" spans="2:32" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="225" t="s">
+    <row r="31" spans="2:32" ht="13.3" customHeight="1">
+      <c r="B31" s="238" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="13" t="s">
@@ -14177,8 +14768,8 @@
       </c>
       <c r="AF31" s="105"/>
     </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B32" s="228"/>
+    <row r="32" spans="2:32">
+      <c r="B32" s="241"/>
       <c r="C32" s="86" t="s">
         <v>447</v>
       </c>
@@ -14268,8 +14859,8 @@
       </c>
       <c r="AF32" s="105"/>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B33" s="218" t="s">
+    <row r="33" spans="2:32">
+      <c r="B33" s="231" t="s">
         <v>185</v>
       </c>
       <c r="C33" s="83" t="s">
@@ -14305,8 +14896,8 @@
       <c r="AE33" s="164"/>
       <c r="AF33" s="105"/>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B34" s="219"/>
+    <row r="34" spans="2:32">
+      <c r="B34" s="232"/>
       <c r="C34" s="15" t="s">
         <v>449</v>
       </c>
@@ -14340,8 +14931,8 @@
       <c r="AE34" s="164"/>
       <c r="AF34" s="105"/>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B35" s="220"/>
+    <row r="35" spans="2:32">
+      <c r="B35" s="233"/>
       <c r="C35" s="16" t="s">
         <v>450</v>
       </c>
@@ -14375,10 +14966,10 @@
       <c r="AE35" s="166"/>
       <c r="AF35" s="105"/>
     </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:32">
       <c r="W36" s="105"/>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:32">
       <c r="I39" s="12"/>
     </row>
   </sheetData>
@@ -14398,7 +14989,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IU74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="12.3"/>
   <cols>
     <col min="1" max="2" width="11.5546875" style="41"/>
     <col min="3" max="3" width="33.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -14456,7 +15047,7 @@
     <col min="70" max="16384" width="11.5546875" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:207" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:221">
       <c r="C1" s="73" t="s">
         <v>269</v>
       </c>
@@ -14967,8 +15558,22 @@
       <c r="GW1" s="174"/>
       <c r="GX1" s="174"/>
       <c r="GY1" s="174"/>
+      <c r="GZ1" s="174"/>
+      <c r="HA1" s="174"/>
+      <c r="HB1" s="174"/>
+      <c r="HC1" s="174"/>
+      <c r="HD1" s="174"/>
+      <c r="HE1" s="174"/>
+      <c r="HF1" s="174"/>
+      <c r="HG1" s="174"/>
+      <c r="HH1" s="174"/>
+      <c r="HI1" s="174"/>
+      <c r="HJ1" s="174"/>
+      <c r="HK1" s="174"/>
+      <c r="HL1" s="174"/>
+      <c r="HM1" s="174"/>
     </row>
-    <row r="2" spans="1:207" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:221" ht="13.8">
       <c r="B2" s="34" t="s">
         <v>183</v>
       </c>
@@ -15405,8 +16010,50 @@
       <c r="GY2" s="154" t="s">
         <v>3255</v>
       </c>
+      <c r="GZ2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HA2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HB2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HC2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HD2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HE2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HF2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HG2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HH2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HI2" s="154" t="s">
+        <v>3376</v>
+      </c>
+      <c r="HJ2" s="154" t="s">
+        <v>3408</v>
+      </c>
+      <c r="HK2" s="154" t="s">
+        <v>3408</v>
+      </c>
+      <c r="HL2" s="154" t="s">
+        <v>3408</v>
+      </c>
+      <c r="HM2" s="154" t="s">
+        <v>3408</v>
+      </c>
     </row>
-    <row r="3" spans="1:207" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:221">
       <c r="B3" s="58"/>
       <c r="C3" s="17" t="s">
         <v>181</v>
@@ -15659,11 +16306,11 @@
       <c r="DS3" s="105"/>
       <c r="DT3" s="105"/>
     </row>
-    <row r="4" spans="1:207" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:221">
       <c r="A4" s="41">
         <v>1</v>
       </c>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="244" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="55" t="s">
@@ -15917,11 +16564,11 @@
       <c r="DS4" s="105"/>
       <c r="DT4" s="105"/>
     </row>
-    <row r="5" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:221" ht="14.4">
       <c r="A5" s="41">
         <v>2</v>
       </c>
-      <c r="B5" s="232"/>
+      <c r="B5" s="245"/>
       <c r="C5" s="54" t="s">
         <v>456</v>
       </c>
@@ -16537,8 +17184,50 @@
       <c r="GY5" s="115" t="s">
         <v>3247</v>
       </c>
+      <c r="GZ5" s="187" t="s">
+        <v>3256</v>
+      </c>
+      <c r="HA5" s="159" t="s">
+        <v>3270</v>
+      </c>
+      <c r="HB5" s="159" t="s">
+        <v>3284</v>
+      </c>
+      <c r="HC5" s="159" t="s">
+        <v>3299</v>
+      </c>
+      <c r="HD5" s="115" t="s">
+        <v>3305</v>
+      </c>
+      <c r="HE5" s="115" t="s">
+        <v>3315</v>
+      </c>
+      <c r="HF5" s="115" t="s">
+        <v>3334</v>
+      </c>
+      <c r="HG5" s="187" t="s">
+        <v>3344</v>
+      </c>
+      <c r="HH5" s="115" t="s">
+        <v>3357</v>
+      </c>
+      <c r="HI5" s="200" t="s">
+        <v>3365</v>
+      </c>
+      <c r="HJ5" s="115" t="s">
+        <v>3377</v>
+      </c>
+      <c r="HK5" s="115" t="s">
+        <v>3390</v>
+      </c>
+      <c r="HL5" s="159" t="s">
+        <v>3409</v>
+      </c>
+      <c r="HM5" s="115" t="s">
+        <v>3422</v>
+      </c>
     </row>
-    <row r="6" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:221" ht="14.4">
       <c r="A6" s="92">
         <v>3</v>
       </c>
@@ -17156,12 +17845,54 @@
       <c r="GY6" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ6" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA6" s="159" t="s">
+        <v>2106</v>
+      </c>
+      <c r="HB6" s="159" t="s">
+        <v>1150</v>
+      </c>
+      <c r="HC6" s="159" t="s">
+        <v>2106</v>
+      </c>
+      <c r="HD6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG6" s="187" t="s">
+        <v>1150</v>
+      </c>
+      <c r="HH6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI6" s="200" t="s">
+        <v>1150</v>
+      </c>
+      <c r="HJ6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM6" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:221" ht="14.4">
       <c r="A7" s="92">
         <v>4</v>
       </c>
-      <c r="B7" s="233" t="s">
+      <c r="B7" s="246" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="54" t="s">
@@ -17777,12 +18508,54 @@
       <c r="GY7" s="115" t="s">
         <v>845</v>
       </c>
+      <c r="GZ7" s="187" t="s">
+        <v>845</v>
+      </c>
+      <c r="HA7" s="159" t="s">
+        <v>845</v>
+      </c>
+      <c r="HB7" s="159">
+        <v>21</v>
+      </c>
+      <c r="HC7" s="159" t="s">
+        <v>845</v>
+      </c>
+      <c r="HD7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="HE7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="HF7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="HG7" s="187">
+        <v>21</v>
+      </c>
+      <c r="HH7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="HI7" s="200">
+        <v>21</v>
+      </c>
+      <c r="HJ7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="HK7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="HL7" s="115">
+        <v>24</v>
+      </c>
+      <c r="HM7" s="115">
+        <v>24</v>
+      </c>
     </row>
-    <row r="8" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:221" ht="14.4">
       <c r="A8" s="92">
         <v>5</v>
       </c>
-      <c r="B8" s="233"/>
+      <c r="B8" s="246"/>
       <c r="C8" s="54" t="s">
         <v>458</v>
       </c>
@@ -18398,12 +19171,54 @@
       <c r="GY8" s="115">
         <v>3</v>
       </c>
+      <c r="GZ8" s="187">
+        <v>3</v>
+      </c>
+      <c r="HA8" s="159">
+        <v>1</v>
+      </c>
+      <c r="HB8" s="159">
+        <v>3</v>
+      </c>
+      <c r="HC8" s="159">
+        <v>1</v>
+      </c>
+      <c r="HD8" s="187">
+        <v>3</v>
+      </c>
+      <c r="HE8" s="115">
+        <v>3</v>
+      </c>
+      <c r="HF8" s="115">
+        <v>3</v>
+      </c>
+      <c r="HG8" s="187">
+        <v>4</v>
+      </c>
+      <c r="HH8" s="115">
+        <v>3</v>
+      </c>
+      <c r="HI8" s="200">
+        <v>4</v>
+      </c>
+      <c r="HJ8" s="115">
+        <v>5</v>
+      </c>
+      <c r="HK8" s="115">
+        <v>4</v>
+      </c>
+      <c r="HL8" s="115">
+        <v>1</v>
+      </c>
+      <c r="HM8" s="115">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:221" ht="28.2">
       <c r="A9" s="92">
         <v>6</v>
       </c>
-      <c r="B9" s="233"/>
+      <c r="B9" s="246"/>
       <c r="C9" s="54" t="s">
         <v>459</v>
       </c>
@@ -19019,12 +19834,54 @@
       <c r="GY9" s="115" t="s">
         <v>57</v>
       </c>
+      <c r="GZ9" s="187" t="s">
+        <v>846</v>
+      </c>
+      <c r="HA9" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="HB9" s="159" t="s">
+        <v>846</v>
+      </c>
+      <c r="HC9" s="159" t="s">
+        <v>1</v>
+      </c>
+      <c r="HD9" s="187" t="s">
+        <v>846</v>
+      </c>
+      <c r="HE9" s="115" t="s">
+        <v>846</v>
+      </c>
+      <c r="HF9" s="115" t="s">
+        <v>846</v>
+      </c>
+      <c r="HG9" s="187" t="s">
+        <v>94</v>
+      </c>
+      <c r="HH9" s="115" t="s">
+        <v>846</v>
+      </c>
+      <c r="HI9" s="200" t="s">
+        <v>2904</v>
+      </c>
+      <c r="HJ9" s="229" t="s">
+        <v>1693</v>
+      </c>
+      <c r="HK9" s="229" t="s">
+        <v>3391</v>
+      </c>
+      <c r="HL9" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="HM9" s="115" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:221" ht="14.4">
       <c r="A10" s="92">
         <v>7</v>
       </c>
-      <c r="B10" s="233"/>
+      <c r="B10" s="246"/>
       <c r="C10" s="54" t="s">
         <v>460</v>
       </c>
@@ -19640,12 +20497,54 @@
       <c r="GY10" s="115" t="s">
         <v>57</v>
       </c>
+      <c r="GZ10" s="208" t="s">
+        <v>1025</v>
+      </c>
+      <c r="HA10" s="159" t="s">
+        <v>412</v>
+      </c>
+      <c r="HB10" s="159" t="s">
+        <v>824</v>
+      </c>
+      <c r="HC10" s="159" t="s">
+        <v>412</v>
+      </c>
+      <c r="HD10" s="208" t="s">
+        <v>1025</v>
+      </c>
+      <c r="HE10" s="159" t="s">
+        <v>3316</v>
+      </c>
+      <c r="HF10" s="159" t="s">
+        <v>3316</v>
+      </c>
+      <c r="HG10" s="187" t="s">
+        <v>5</v>
+      </c>
+      <c r="HH10" s="159" t="s">
+        <v>3316</v>
+      </c>
+      <c r="HI10" s="200" t="s">
+        <v>5</v>
+      </c>
+      <c r="HJ10" s="115" t="s">
+        <v>1025</v>
+      </c>
+      <c r="HK10" s="115" t="s">
+        <v>3392</v>
+      </c>
+      <c r="HL10" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="HM10" s="115" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="11" spans="1:207" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:221" ht="14.5" customHeight="1">
       <c r="A11" s="92">
         <v>8</v>
       </c>
-      <c r="B11" s="234" t="s">
+      <c r="B11" s="247" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="55" t="s">
@@ -20261,12 +21160,54 @@
       <c r="GY11" s="115" t="s">
         <v>32</v>
       </c>
+      <c r="GZ11" s="188" t="s">
+        <v>782</v>
+      </c>
+      <c r="HA11" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="HB11" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="HC11" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="HD11" s="188" t="s">
+        <v>782</v>
+      </c>
+      <c r="HE11" s="184" t="s">
+        <v>782</v>
+      </c>
+      <c r="HF11" s="184" t="s">
+        <v>782</v>
+      </c>
+      <c r="HG11" s="188" t="s">
+        <v>3345</v>
+      </c>
+      <c r="HH11" s="184" t="s">
+        <v>782</v>
+      </c>
+      <c r="HI11" s="202" t="s">
+        <v>3366</v>
+      </c>
+      <c r="HJ11" s="115" t="s">
+        <v>3378</v>
+      </c>
+      <c r="HK11" s="115" t="s">
+        <v>3393</v>
+      </c>
+      <c r="HL11" s="115" t="s">
+        <v>3410</v>
+      </c>
+      <c r="HM11" s="115" t="s">
+        <v>3423</v>
+      </c>
     </row>
-    <row r="12" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:221" ht="14.4">
       <c r="A12" s="92">
         <v>9</v>
       </c>
-      <c r="B12" s="235"/>
+      <c r="B12" s="248"/>
       <c r="C12" s="56" t="s">
         <v>427</v>
       </c>
@@ -20880,12 +21821,54 @@
       <c r="GY12" s="115" t="s">
         <v>152</v>
       </c>
+      <c r="GZ12" s="187" t="s">
+        <v>152</v>
+      </c>
+      <c r="HA12" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="HB12" s="159" t="s">
+        <v>3285</v>
+      </c>
+      <c r="HC12" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="HD12" s="187" t="s">
+        <v>152</v>
+      </c>
+      <c r="HE12" s="115" t="s">
+        <v>3317</v>
+      </c>
+      <c r="HF12" s="115" t="s">
+        <v>3317</v>
+      </c>
+      <c r="HG12" s="187" t="s">
+        <v>3346</v>
+      </c>
+      <c r="HH12" s="115" t="s">
+        <v>3317</v>
+      </c>
+      <c r="HI12" s="200" t="s">
+        <v>2274</v>
+      </c>
+      <c r="HJ12" s="115" t="s">
+        <v>3379</v>
+      </c>
+      <c r="HK12" s="115" t="s">
+        <v>3394</v>
+      </c>
+      <c r="HL12" s="115" t="s">
+        <v>3411</v>
+      </c>
+      <c r="HM12" s="115" t="s">
+        <v>3424</v>
+      </c>
     </row>
-    <row r="13" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:221" ht="14.4">
       <c r="A13" s="92">
         <v>10</v>
       </c>
-      <c r="B13" s="235"/>
+      <c r="B13" s="248"/>
       <c r="C13" s="56" t="s">
         <v>428</v>
       </c>
@@ -21499,12 +22482,54 @@
       <c r="GY13" s="115" t="s">
         <v>3199</v>
       </c>
+      <c r="GZ13" s="187" t="s">
+        <v>563</v>
+      </c>
+      <c r="HA13" s="159" t="s">
+        <v>3271</v>
+      </c>
+      <c r="HB13" s="159" t="s">
+        <v>597</v>
+      </c>
+      <c r="HC13" s="159" t="s">
+        <v>3271</v>
+      </c>
+      <c r="HD13" s="187" t="s">
+        <v>563</v>
+      </c>
+      <c r="HE13" s="115" t="s">
+        <v>3318</v>
+      </c>
+      <c r="HF13" s="115" t="s">
+        <v>3318</v>
+      </c>
+      <c r="HG13" s="187" t="s">
+        <v>3347</v>
+      </c>
+      <c r="HH13" s="115" t="s">
+        <v>3318</v>
+      </c>
+      <c r="HI13" s="202" t="s">
+        <v>563</v>
+      </c>
+      <c r="HJ13" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK13" s="115" t="s">
+        <v>3395</v>
+      </c>
+      <c r="HL13" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM13" s="115" t="s">
+        <v>3425</v>
+      </c>
     </row>
-    <row r="14" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:221" ht="14.4">
       <c r="A14" s="92">
         <v>11</v>
       </c>
-      <c r="B14" s="235"/>
+      <c r="B14" s="248"/>
       <c r="C14" s="56" t="s">
         <v>429</v>
       </c>
@@ -22118,12 +23143,54 @@
       <c r="GY14" s="115" t="s">
         <v>3200</v>
       </c>
+      <c r="GZ14" s="187" t="s">
+        <v>3257</v>
+      </c>
+      <c r="HA14" s="159" t="s">
+        <v>3272</v>
+      </c>
+      <c r="HB14" s="159" t="s">
+        <v>3286</v>
+      </c>
+      <c r="HC14" s="159" t="s">
+        <v>3300</v>
+      </c>
+      <c r="HD14" s="187" t="s">
+        <v>3306</v>
+      </c>
+      <c r="HE14" s="115" t="s">
+        <v>3319</v>
+      </c>
+      <c r="HF14" s="115" t="s">
+        <v>3335</v>
+      </c>
+      <c r="HG14" s="225" t="s">
+        <v>3348</v>
+      </c>
+      <c r="HH14" s="115" t="s">
+        <v>3358</v>
+      </c>
+      <c r="HI14" s="200" t="s">
+        <v>3367</v>
+      </c>
+      <c r="HJ14" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK14" s="115" t="s">
+        <v>3396</v>
+      </c>
+      <c r="HL14" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM14" s="115" t="s">
+        <v>3426</v>
+      </c>
     </row>
-    <row r="15" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:221" ht="14.4">
       <c r="A15" s="92">
         <v>12</v>
       </c>
-      <c r="B15" s="235"/>
+      <c r="B15" s="248"/>
       <c r="C15" s="56" t="s">
         <v>430</v>
       </c>
@@ -22737,12 +23804,54 @@
       <c r="GY15" s="115" t="s">
         <v>3201</v>
       </c>
+      <c r="GZ15" s="187" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HA15" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB15" s="159" t="s">
+        <v>3287</v>
+      </c>
+      <c r="HC15" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD15" s="187" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HE15" s="115" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HF15" s="115" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HG15" s="187" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HH15" s="115" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HI15" s="200" t="s">
+        <v>2345</v>
+      </c>
+      <c r="HJ15" s="115" t="s">
+        <v>3380</v>
+      </c>
+      <c r="HK15" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL15" s="115" t="s">
+        <v>2656</v>
+      </c>
+      <c r="HM15" s="115" t="s">
+        <v>3427</v>
+      </c>
     </row>
-    <row r="16" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:221" ht="14.4">
       <c r="A16" s="92">
         <v>13</v>
       </c>
-      <c r="B16" s="235"/>
+      <c r="B16" s="248"/>
       <c r="C16" s="56" t="s">
         <v>431</v>
       </c>
@@ -23356,12 +24465,54 @@
       <c r="GY16" s="115" t="s">
         <v>3202</v>
       </c>
+      <c r="GZ16" s="187" t="s">
+        <v>3258</v>
+      </c>
+      <c r="HA16" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB16" s="159" t="s">
+        <v>3288</v>
+      </c>
+      <c r="HC16" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD16" s="187" t="s">
+        <v>3307</v>
+      </c>
+      <c r="HE16" s="115" t="s">
+        <v>3320</v>
+      </c>
+      <c r="HF16" s="115" t="s">
+        <v>3336</v>
+      </c>
+      <c r="HG16" s="187" t="s">
+        <v>3349</v>
+      </c>
+      <c r="HH16" s="115" t="s">
+        <v>3359</v>
+      </c>
+      <c r="HI16" s="200" t="s">
+        <v>3368</v>
+      </c>
+      <c r="HJ16" s="115" t="s">
+        <v>3381</v>
+      </c>
+      <c r="HK16" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL16" s="159" t="s">
+        <v>3412</v>
+      </c>
+      <c r="HM16" s="115" t="s">
+        <v>1680</v>
+      </c>
     </row>
-    <row r="17" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:221" ht="14.4">
       <c r="A17" s="92">
         <v>14</v>
       </c>
-      <c r="B17" s="235"/>
+      <c r="B17" s="248"/>
       <c r="C17" s="56" t="s">
         <v>432</v>
       </c>
@@ -23975,12 +25126,54 @@
       <c r="GY17" s="115" t="s">
         <v>19</v>
       </c>
+      <c r="GZ17" s="187" t="s">
+        <v>3259</v>
+      </c>
+      <c r="HA17" s="159" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HB17" s="159" t="s">
+        <v>19</v>
+      </c>
+      <c r="HC17" s="159" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HD17" s="187" t="s">
+        <v>650</v>
+      </c>
+      <c r="HE17" s="115" t="s">
+        <v>19</v>
+      </c>
+      <c r="HF17" s="115" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HG17" s="187" t="s">
+        <v>819</v>
+      </c>
+      <c r="HH17" s="115" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HI17" s="200" t="s">
+        <v>3369</v>
+      </c>
+      <c r="HJ17" s="115" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HK17" s="115" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HL17" s="115" t="s">
+        <v>19</v>
+      </c>
+      <c r="HM17" s="115" t="s">
+        <v>3428</v>
+      </c>
     </row>
-    <row r="18" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:221" ht="14.4">
       <c r="A18" s="92">
         <v>15</v>
       </c>
-      <c r="B18" s="235"/>
+      <c r="B18" s="248"/>
       <c r="C18" s="56" t="s">
         <v>433</v>
       </c>
@@ -24594,12 +25787,54 @@
       <c r="GY18" s="115" t="s">
         <v>3203</v>
       </c>
+      <c r="GZ18" s="187" t="s">
+        <v>3260</v>
+      </c>
+      <c r="HA18" s="159" t="s">
+        <v>1845</v>
+      </c>
+      <c r="HB18" s="159" t="s">
+        <v>3289</v>
+      </c>
+      <c r="HC18" s="159" t="s">
+        <v>1845</v>
+      </c>
+      <c r="HD18" s="187" t="s">
+        <v>3308</v>
+      </c>
+      <c r="HE18" s="115" t="s">
+        <v>3321</v>
+      </c>
+      <c r="HF18" s="115" t="s">
+        <v>3337</v>
+      </c>
+      <c r="HG18" s="187" t="s">
+        <v>3350</v>
+      </c>
+      <c r="HH18" s="115" t="s">
+        <v>3337</v>
+      </c>
+      <c r="HI18" s="200" t="s">
+        <v>3370</v>
+      </c>
+      <c r="HJ18" s="115" t="s">
+        <v>1422</v>
+      </c>
+      <c r="HK18" s="115" t="s">
+        <v>3397</v>
+      </c>
+      <c r="HL18" s="115" t="s">
+        <v>3413</v>
+      </c>
+      <c r="HM18" s="115" t="s">
+        <v>2658</v>
+      </c>
     </row>
-    <row r="19" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:221" ht="14.4">
       <c r="A19" s="92">
         <v>16</v>
       </c>
-      <c r="B19" s="235"/>
+      <c r="B19" s="248"/>
       <c r="C19" s="56" t="s">
         <v>434</v>
       </c>
@@ -25213,12 +26448,54 @@
       <c r="GY19" s="115" t="s">
         <v>3248</v>
       </c>
+      <c r="GZ19" s="187" t="s">
+        <v>1410</v>
+      </c>
+      <c r="HA19" s="159" t="s">
+        <v>1518</v>
+      </c>
+      <c r="HB19" s="159" t="s">
+        <v>3290</v>
+      </c>
+      <c r="HC19" s="159" t="s">
+        <v>1518</v>
+      </c>
+      <c r="HD19" s="187" t="s">
+        <v>3309</v>
+      </c>
+      <c r="HE19" s="115" t="s">
+        <v>3322</v>
+      </c>
+      <c r="HF19" s="115" t="s">
+        <v>2154</v>
+      </c>
+      <c r="HG19" s="187" t="s">
+        <v>1424</v>
+      </c>
+      <c r="HH19" s="115" t="s">
+        <v>3360</v>
+      </c>
+      <c r="HI19" s="200" t="s">
+        <v>2644</v>
+      </c>
+      <c r="HJ19" s="115">
+        <v>2020</v>
+      </c>
+      <c r="HK19" s="115" t="s">
+        <v>3398</v>
+      </c>
+      <c r="HL19" s="115">
+        <v>2019</v>
+      </c>
+      <c r="HM19" s="115" t="s">
+        <v>3429</v>
+      </c>
     </row>
-    <row r="20" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:221" ht="14.4">
       <c r="A20" s="92">
         <v>17</v>
       </c>
-      <c r="B20" s="235"/>
+      <c r="B20" s="248"/>
       <c r="C20" s="56" t="s">
         <v>435</v>
       </c>
@@ -25832,12 +27109,54 @@
       <c r="GY20" s="115" t="s">
         <v>3249</v>
       </c>
+      <c r="GZ20" s="187" t="s">
+        <v>3261</v>
+      </c>
+      <c r="HA20" s="159" t="s">
+        <v>1278</v>
+      </c>
+      <c r="HB20" s="159" t="s">
+        <v>3291</v>
+      </c>
+      <c r="HC20" s="159" t="s">
+        <v>1278</v>
+      </c>
+      <c r="HD20" s="187" t="s">
+        <v>3310</v>
+      </c>
+      <c r="HE20" s="115" t="s">
+        <v>3323</v>
+      </c>
+      <c r="HF20" s="115" t="s">
+        <v>3338</v>
+      </c>
+      <c r="HG20" s="187" t="s">
+        <v>3351</v>
+      </c>
+      <c r="HH20" s="115" t="s">
+        <v>3338</v>
+      </c>
+      <c r="HI20" s="200" t="s">
+        <v>1583</v>
+      </c>
+      <c r="HJ20" s="115" t="s">
+        <v>1145</v>
+      </c>
+      <c r="HK20" s="115" t="s">
+        <v>3399</v>
+      </c>
+      <c r="HL20" s="115" t="s">
+        <v>2337</v>
+      </c>
+      <c r="HM20" s="115" t="s">
+        <v>3430</v>
+      </c>
     </row>
-    <row r="21" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:221" ht="14.4">
       <c r="A21" s="92">
         <v>18</v>
       </c>
-      <c r="B21" s="236" t="s">
+      <c r="B21" s="249" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="56" t="s">
@@ -26447,12 +27766,54 @@
       <c r="GY21" s="115" t="s">
         <v>3250</v>
       </c>
+      <c r="GZ21" s="187" t="s">
+        <v>3262</v>
+      </c>
+      <c r="HA21" s="159" t="s">
+        <v>3273</v>
+      </c>
+      <c r="HB21" s="159" t="s">
+        <v>3292</v>
+      </c>
+      <c r="HC21" s="159" t="s">
+        <v>3301</v>
+      </c>
+      <c r="HD21" s="187" t="s">
+        <v>3262</v>
+      </c>
+      <c r="HE21" s="115" t="s">
+        <v>3324</v>
+      </c>
+      <c r="HF21" s="115" t="s">
+        <v>3339</v>
+      </c>
+      <c r="HG21" s="187" t="s">
+        <v>3352</v>
+      </c>
+      <c r="HH21" s="115" t="s">
+        <v>3324</v>
+      </c>
+      <c r="HI21" s="200" t="s">
+        <v>3371</v>
+      </c>
+      <c r="HJ21" s="115" t="s">
+        <v>3382</v>
+      </c>
+      <c r="HK21" s="115" t="s">
+        <v>3400</v>
+      </c>
+      <c r="HL21" s="115" t="s">
+        <v>3414</v>
+      </c>
+      <c r="HM21" s="115" t="s">
+        <v>3431</v>
+      </c>
     </row>
-    <row r="22" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:221" ht="14.4">
       <c r="A22" s="92">
         <v>19</v>
       </c>
-      <c r="B22" s="236"/>
+      <c r="B22" s="249"/>
       <c r="C22" s="56" t="s">
         <v>437</v>
       </c>
@@ -27068,12 +28429,54 @@
       <c r="GY22" s="115" t="s">
         <v>3251</v>
       </c>
+      <c r="GZ22" s="187" t="s">
+        <v>3263</v>
+      </c>
+      <c r="HA22" s="159" t="s">
+        <v>3274</v>
+      </c>
+      <c r="HB22" s="159" t="s">
+        <v>3293</v>
+      </c>
+      <c r="HC22" s="159" t="s">
+        <v>3302</v>
+      </c>
+      <c r="HD22" s="187" t="s">
+        <v>3263</v>
+      </c>
+      <c r="HE22" s="115" t="s">
+        <v>3325</v>
+      </c>
+      <c r="HF22" s="115" t="s">
+        <v>3325</v>
+      </c>
+      <c r="HG22" s="187" t="s">
+        <v>3353</v>
+      </c>
+      <c r="HH22" s="115" t="s">
+        <v>3325</v>
+      </c>
+      <c r="HI22" s="200" t="s">
+        <v>3372</v>
+      </c>
+      <c r="HJ22" s="115" t="s">
+        <v>3383</v>
+      </c>
+      <c r="HK22" s="115" t="s">
+        <v>3401</v>
+      </c>
+      <c r="HL22" s="115" t="s">
+        <v>3415</v>
+      </c>
+      <c r="HM22" s="115" t="s">
+        <v>3432</v>
+      </c>
     </row>
-    <row r="23" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:221" ht="14.4">
       <c r="A23" s="92">
         <v>20</v>
       </c>
-      <c r="B23" s="236"/>
+      <c r="B23" s="249"/>
       <c r="C23" s="55" t="s">
         <v>461</v>
       </c>
@@ -27689,12 +29092,54 @@
       <c r="GY23" s="115" t="s">
         <v>24</v>
       </c>
+      <c r="GZ23" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="HA23" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="HB23" s="159" t="s">
+        <v>24</v>
+      </c>
+      <c r="HC23" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="HD23" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="HE23" s="169" t="s">
+        <v>24</v>
+      </c>
+      <c r="HF23" s="169" t="s">
+        <v>24</v>
+      </c>
+      <c r="HG23" s="156" t="s">
+        <v>24</v>
+      </c>
+      <c r="HH23" s="169" t="s">
+        <v>24</v>
+      </c>
+      <c r="HI23" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="HJ23" s="115" t="s">
+        <v>313</v>
+      </c>
+      <c r="HK23" s="115" t="s">
+        <v>313</v>
+      </c>
+      <c r="HL23" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="HM23" s="115" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="24" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:221" ht="14.4">
       <c r="A24" s="92">
         <v>21</v>
       </c>
-      <c r="B24" s="236"/>
+      <c r="B24" s="249"/>
       <c r="C24" s="55" t="s">
         <v>462</v>
       </c>
@@ -28310,12 +29755,54 @@
       <c r="GY24" s="115">
         <v>59</v>
       </c>
+      <c r="GZ24" s="187">
+        <v>122</v>
+      </c>
+      <c r="HA24" s="183">
+        <v>1220</v>
+      </c>
+      <c r="HB24" s="159">
+        <v>1890</v>
+      </c>
+      <c r="HC24" s="183">
+        <v>1561</v>
+      </c>
+      <c r="HD24" s="115">
+        <v>72</v>
+      </c>
+      <c r="HE24" s="115">
+        <v>340</v>
+      </c>
+      <c r="HF24" s="115">
+        <v>84</v>
+      </c>
+      <c r="HG24" s="155">
+        <v>12</v>
+      </c>
+      <c r="HH24" s="115">
+        <v>52</v>
+      </c>
+      <c r="HI24" s="226">
+        <v>117</v>
+      </c>
+      <c r="HJ24" s="185">
+        <v>108</v>
+      </c>
+      <c r="HK24" s="185">
+        <v>232</v>
+      </c>
+      <c r="HL24" s="212">
+        <v>144</v>
+      </c>
+      <c r="HM24" s="155">
+        <v>709</v>
+      </c>
     </row>
-    <row r="25" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:221" ht="14.4">
       <c r="A25" s="92">
         <v>22</v>
       </c>
-      <c r="B25" s="236"/>
+      <c r="B25" s="249"/>
       <c r="C25" s="56" t="s">
         <v>438</v>
       </c>
@@ -28924,12 +30411,54 @@
       <c r="GY25" s="115" t="s">
         <v>3208</v>
       </c>
+      <c r="GZ25" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA25" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB25" s="115" t="s">
+        <v>3294</v>
+      </c>
+      <c r="HC25" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD25" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE25" s="185" t="s">
+        <v>3326</v>
+      </c>
+      <c r="HF25" s="185" t="s">
+        <v>3340</v>
+      </c>
+      <c r="HG25" s="187" t="s">
+        <v>3294</v>
+      </c>
+      <c r="HH25" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI25" s="200" t="s">
+        <v>3294</v>
+      </c>
+      <c r="HJ25" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK25" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL25" s="115" t="s">
+        <v>3416</v>
+      </c>
+      <c r="HM25" s="115" t="s">
+        <v>3433</v>
+      </c>
     </row>
-    <row r="26" spans="1:207" s="68" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:221" s="68" customFormat="1" ht="13.8" customHeight="1">
       <c r="A26" s="92">
         <v>23</v>
       </c>
-      <c r="B26" s="237" t="s">
+      <c r="B26" s="250" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="64" t="s">
@@ -29547,12 +31076,54 @@
       <c r="GY26" s="115" t="s">
         <v>849</v>
       </c>
+      <c r="GZ26" s="218" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HA26" s="159" t="s">
+        <v>853</v>
+      </c>
+      <c r="HB26" s="159" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HC26" s="159" t="s">
+        <v>853</v>
+      </c>
+      <c r="HD26" s="222" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HE26" s="224" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HF26" s="224" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HG26" s="187" t="s">
+        <v>849</v>
+      </c>
+      <c r="HH26" s="224" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HI26" s="47" t="s">
+        <v>849</v>
+      </c>
+      <c r="HJ26" s="115" t="s">
+        <v>1033</v>
+      </c>
+      <c r="HK26" s="115" t="s">
+        <v>1697</v>
+      </c>
+      <c r="HL26" s="159" t="s">
+        <v>2911</v>
+      </c>
+      <c r="HM26" s="115" t="s">
+        <v>699</v>
+      </c>
     </row>
-    <row r="27" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A27" s="92">
         <v>24</v>
       </c>
-      <c r="B27" s="237"/>
+      <c r="B27" s="250"/>
       <c r="C27" s="64" t="s">
         <v>464</v>
       </c>
@@ -30168,12 +31739,54 @@
       <c r="GY27" s="115">
         <v>4</v>
       </c>
+      <c r="GZ27" s="218">
+        <v>6</v>
+      </c>
+      <c r="HA27" s="159">
+        <v>12</v>
+      </c>
+      <c r="HB27" s="159">
+        <v>6</v>
+      </c>
+      <c r="HC27" s="159">
+        <v>12</v>
+      </c>
+      <c r="HD27" s="222">
+        <v>6</v>
+      </c>
+      <c r="HE27" s="224">
+        <v>6</v>
+      </c>
+      <c r="HF27" s="224">
+        <v>6</v>
+      </c>
+      <c r="HG27" s="187">
+        <v>4</v>
+      </c>
+      <c r="HH27" s="224">
+        <v>6</v>
+      </c>
+      <c r="HI27" s="201">
+        <v>4</v>
+      </c>
+      <c r="HJ27" s="115">
+        <v>4</v>
+      </c>
+      <c r="HK27" s="115">
+        <v>28</v>
+      </c>
+      <c r="HL27" s="159">
+        <v>92</v>
+      </c>
+      <c r="HM27" s="115">
+        <v>6</v>
+      </c>
     </row>
-    <row r="28" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A28" s="92">
         <v>25</v>
       </c>
-      <c r="B28" s="237"/>
+      <c r="B28" s="250"/>
       <c r="C28" s="64" t="s">
         <v>465</v>
       </c>
@@ -30787,12 +32400,54 @@
       <c r="GY28" s="115" t="s">
         <v>1640</v>
       </c>
+      <c r="GZ28" s="191" t="s">
+        <v>851</v>
+      </c>
+      <c r="HA28" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="HB28" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="HC28" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="HD28" s="156" t="s">
+        <v>851</v>
+      </c>
+      <c r="HE28" s="169" t="s">
+        <v>696</v>
+      </c>
+      <c r="HF28" s="169" t="s">
+        <v>696</v>
+      </c>
+      <c r="HG28" s="187" t="s">
+        <v>696</v>
+      </c>
+      <c r="HH28" s="169" t="s">
+        <v>696</v>
+      </c>
+      <c r="HI28" s="47" t="s">
+        <v>707</v>
+      </c>
+      <c r="HJ28" s="115" t="s">
+        <v>697</v>
+      </c>
+      <c r="HK28" s="115" t="s">
+        <v>698</v>
+      </c>
+      <c r="HL28" s="159" t="s">
+        <v>699</v>
+      </c>
+      <c r="HM28" s="115" t="s">
+        <v>707</v>
+      </c>
     </row>
-    <row r="29" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A29" s="92">
         <v>26</v>
       </c>
-      <c r="B29" s="237"/>
+      <c r="B29" s="250"/>
       <c r="C29" s="64" t="s">
         <v>466</v>
       </c>
@@ -31406,12 +33061,54 @@
       <c r="GY29" s="115">
         <v>90</v>
       </c>
+      <c r="GZ29" s="187">
+        <v>13</v>
+      </c>
+      <c r="HA29" s="159">
+        <v>7</v>
+      </c>
+      <c r="HB29" s="182">
+        <v>7</v>
+      </c>
+      <c r="HC29" s="159">
+        <v>7</v>
+      </c>
+      <c r="HD29" s="187">
+        <v>13</v>
+      </c>
+      <c r="HE29" s="115">
+        <v>7</v>
+      </c>
+      <c r="HF29" s="115">
+        <v>7</v>
+      </c>
+      <c r="HG29" s="187">
+        <v>7</v>
+      </c>
+      <c r="HH29" s="115">
+        <v>7</v>
+      </c>
+      <c r="HI29" s="201">
+        <v>7</v>
+      </c>
+      <c r="HJ29" s="185">
+        <v>6</v>
+      </c>
+      <c r="HK29" s="115">
+        <v>2</v>
+      </c>
+      <c r="HL29" s="159">
+        <v>6</v>
+      </c>
+      <c r="HM29" s="155">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A30" s="92">
         <v>27</v>
       </c>
-      <c r="B30" s="237"/>
+      <c r="B30" s="250"/>
       <c r="C30" s="64" t="s">
         <v>467</v>
       </c>
@@ -32025,12 +33722,54 @@
       <c r="GY30" s="115" t="s">
         <v>697</v>
       </c>
+      <c r="GZ30" s="191" t="s">
+        <v>704</v>
+      </c>
+      <c r="HA30" s="159" t="s">
+        <v>697</v>
+      </c>
+      <c r="HB30" s="159" t="s">
+        <v>704</v>
+      </c>
+      <c r="HC30" s="159" t="s">
+        <v>697</v>
+      </c>
+      <c r="HD30" s="156" t="s">
+        <v>704</v>
+      </c>
+      <c r="HE30" s="169" t="s">
+        <v>704</v>
+      </c>
+      <c r="HF30" s="169" t="s">
+        <v>704</v>
+      </c>
+      <c r="HG30" s="187" t="s">
+        <v>702</v>
+      </c>
+      <c r="HH30" s="169" t="s">
+        <v>704</v>
+      </c>
+      <c r="HI30" s="200" t="s">
+        <v>1440</v>
+      </c>
+      <c r="HJ30" s="115" t="s">
+        <v>698</v>
+      </c>
+      <c r="HK30" s="115" t="s">
+        <v>702</v>
+      </c>
+      <c r="HL30" s="159" t="s">
+        <v>700</v>
+      </c>
+      <c r="HM30" s="115" t="s">
+        <v>700</v>
+      </c>
     </row>
-    <row r="31" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A31" s="92">
         <v>28</v>
       </c>
-      <c r="B31" s="237"/>
+      <c r="B31" s="250"/>
       <c r="C31" s="64" t="s">
         <v>468</v>
       </c>
@@ -32644,12 +34383,54 @@
       <c r="GY31" s="184">
         <v>6</v>
       </c>
+      <c r="GZ31" s="188">
+        <v>14</v>
+      </c>
+      <c r="HA31" s="182">
+        <v>6</v>
+      </c>
+      <c r="HB31" s="159">
+        <v>14</v>
+      </c>
+      <c r="HC31" s="182">
+        <v>6</v>
+      </c>
+      <c r="HD31" s="188">
+        <v>14</v>
+      </c>
+      <c r="HE31" s="184">
+        <v>14</v>
+      </c>
+      <c r="HF31" s="184">
+        <v>9</v>
+      </c>
+      <c r="HG31" s="187">
+        <v>3</v>
+      </c>
+      <c r="HH31" s="184">
+        <v>14</v>
+      </c>
+      <c r="HI31" s="200">
+        <v>6</v>
+      </c>
+      <c r="HJ31" s="184">
+        <v>2</v>
+      </c>
+      <c r="HK31" s="185">
+        <v>14</v>
+      </c>
+      <c r="HL31" s="184">
+        <v>6</v>
+      </c>
+      <c r="HM31" s="184">
+        <v>6</v>
+      </c>
     </row>
-    <row r="32" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A32" s="92">
         <v>29</v>
       </c>
-      <c r="B32" s="237"/>
+      <c r="B32" s="250"/>
       <c r="C32" s="64" t="s">
         <v>469</v>
       </c>
@@ -33263,12 +35044,54 @@
       <c r="GY32" s="115" t="s">
         <v>698</v>
       </c>
+      <c r="GZ32" s="188" t="s">
+        <v>698</v>
+      </c>
+      <c r="HA32" s="159" t="s">
+        <v>698</v>
+      </c>
+      <c r="HB32" s="182" t="s">
+        <v>698</v>
+      </c>
+      <c r="HC32" s="159" t="s">
+        <v>698</v>
+      </c>
+      <c r="HD32" s="188" t="s">
+        <v>698</v>
+      </c>
+      <c r="HE32" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="HF32" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="HG32" s="187" t="s">
+        <v>698</v>
+      </c>
+      <c r="HH32" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="HI32" s="200" t="s">
+        <v>697</v>
+      </c>
+      <c r="HJ32" s="115" t="s">
+        <v>702</v>
+      </c>
+      <c r="HK32" s="115" t="s">
+        <v>696</v>
+      </c>
+      <c r="HL32" s="159" t="s">
+        <v>1033</v>
+      </c>
+      <c r="HM32" s="115" t="s">
+        <v>799</v>
+      </c>
     </row>
-    <row r="33" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A33" s="92">
         <v>30</v>
       </c>
-      <c r="B33" s="237"/>
+      <c r="B33" s="250"/>
       <c r="C33" s="64" t="s">
         <v>470</v>
       </c>
@@ -33882,12 +35705,54 @@
       <c r="GY33" s="115">
         <v>2</v>
       </c>
+      <c r="GZ33" s="188">
+        <v>2</v>
+      </c>
+      <c r="HA33" s="182">
+        <v>2</v>
+      </c>
+      <c r="HB33" s="159">
+        <v>2</v>
+      </c>
+      <c r="HC33" s="182">
+        <v>2</v>
+      </c>
+      <c r="HD33" s="188">
+        <v>2</v>
+      </c>
+      <c r="HE33" s="184">
+        <v>2</v>
+      </c>
+      <c r="HF33" s="184">
+        <v>2</v>
+      </c>
+      <c r="HG33" s="187">
+        <v>2</v>
+      </c>
+      <c r="HH33" s="184">
+        <v>2</v>
+      </c>
+      <c r="HI33" s="200">
+        <v>6</v>
+      </c>
+      <c r="HJ33" s="185">
+        <v>3</v>
+      </c>
+      <c r="HK33" s="185">
+        <v>13</v>
+      </c>
+      <c r="HL33" s="159">
+        <v>4</v>
+      </c>
+      <c r="HM33" s="185">
+        <v>7</v>
+      </c>
     </row>
-    <row r="34" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A34" s="92">
         <v>31</v>
       </c>
-      <c r="B34" s="237"/>
+      <c r="B34" s="250"/>
       <c r="C34" s="64" t="s">
         <v>471</v>
       </c>
@@ -34501,12 +36366,54 @@
       <c r="GY34" s="184" t="s">
         <v>704</v>
       </c>
+      <c r="GZ34" s="191" t="s">
+        <v>849</v>
+      </c>
+      <c r="HA34" s="159" t="s">
+        <v>702</v>
+      </c>
+      <c r="HB34" s="182" t="s">
+        <v>1640</v>
+      </c>
+      <c r="HC34" s="159" t="s">
+        <v>702</v>
+      </c>
+      <c r="HD34" s="156" t="s">
+        <v>849</v>
+      </c>
+      <c r="HE34" s="169" t="s">
+        <v>849</v>
+      </c>
+      <c r="HF34" s="169" t="s">
+        <v>849</v>
+      </c>
+      <c r="HG34" s="187" t="s">
+        <v>1441</v>
+      </c>
+      <c r="HH34" s="169" t="s">
+        <v>849</v>
+      </c>
+      <c r="HI34" s="200" t="s">
+        <v>1441</v>
+      </c>
+      <c r="HJ34" s="115" t="s">
+        <v>1697</v>
+      </c>
+      <c r="HK34" s="115" t="s">
+        <v>697</v>
+      </c>
+      <c r="HL34" s="159" t="s">
+        <v>698</v>
+      </c>
+      <c r="HM34" s="115" t="s">
+        <v>1033</v>
+      </c>
     </row>
-    <row r="35" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A35" s="92">
         <v>32</v>
       </c>
-      <c r="B35" s="237"/>
+      <c r="B35" s="250"/>
       <c r="C35" s="64" t="s">
         <v>472</v>
       </c>
@@ -35120,12 +37027,54 @@
       <c r="GY35" s="115">
         <v>14</v>
       </c>
+      <c r="GZ35" s="69">
+        <v>4</v>
+      </c>
+      <c r="HA35" s="159">
+        <v>3</v>
+      </c>
+      <c r="HB35" s="182">
+        <v>90</v>
+      </c>
+      <c r="HC35" s="159">
+        <v>3</v>
+      </c>
+      <c r="HD35" s="155">
+        <v>4</v>
+      </c>
+      <c r="HE35" s="185">
+        <v>4</v>
+      </c>
+      <c r="HF35" s="185">
+        <v>4</v>
+      </c>
+      <c r="HG35" s="187">
+        <v>86</v>
+      </c>
+      <c r="HH35" s="185">
+        <v>4</v>
+      </c>
+      <c r="HI35" s="200">
+        <v>86</v>
+      </c>
+      <c r="HJ35" s="115">
+        <v>28</v>
+      </c>
+      <c r="HK35" s="185">
+        <v>6</v>
+      </c>
+      <c r="HL35" s="159">
+        <v>2</v>
+      </c>
+      <c r="HM35" s="115">
+        <v>4</v>
+      </c>
     </row>
-    <row r="36" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A36" s="92">
         <v>33</v>
       </c>
-      <c r="B36" s="237"/>
+      <c r="B36" s="250"/>
       <c r="C36" s="64" t="s">
         <v>473</v>
       </c>
@@ -35739,12 +37688,54 @@
       <c r="GY36" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ36" s="188" t="s">
+        <v>1441</v>
+      </c>
+      <c r="HA36" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB36" s="159" t="s">
+        <v>849</v>
+      </c>
+      <c r="HC36" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD36" s="188" t="s">
+        <v>1441</v>
+      </c>
+      <c r="HE36" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF36" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG36" s="187" t="s">
+        <v>697</v>
+      </c>
+      <c r="HH36" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI36" s="200" t="s">
+        <v>702</v>
+      </c>
+      <c r="HJ36" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK36" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL36" s="159" t="s">
+        <v>702</v>
+      </c>
+      <c r="HM36" s="115" t="s">
+        <v>702</v>
+      </c>
     </row>
-    <row r="37" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A37" s="92">
         <v>34</v>
       </c>
-      <c r="B37" s="237"/>
+      <c r="B37" s="250"/>
       <c r="C37" s="64" t="s">
         <v>474</v>
       </c>
@@ -36358,12 +38349,54 @@
       <c r="GY37" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ37" s="188">
+        <v>86</v>
+      </c>
+      <c r="HA37" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB37" s="159">
+        <v>4</v>
+      </c>
+      <c r="HC37" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD37" s="188">
+        <v>86</v>
+      </c>
+      <c r="HE37" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF37" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG37" s="187">
+        <v>6</v>
+      </c>
+      <c r="HH37" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI37" s="200">
+        <v>14</v>
+      </c>
+      <c r="HJ37" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK37" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL37" s="159">
+        <v>3</v>
+      </c>
+      <c r="HM37" s="115">
+        <v>14</v>
+      </c>
     </row>
-    <row r="38" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A38" s="92">
         <v>35</v>
       </c>
-      <c r="B38" s="237"/>
+      <c r="B38" s="250"/>
       <c r="C38" s="64" t="s">
         <v>475</v>
       </c>
@@ -36977,12 +39010,54 @@
       <c r="GY38" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ38" s="191" t="s">
+        <v>1034</v>
+      </c>
+      <c r="HA38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB38" s="159" t="s">
+        <v>1441</v>
+      </c>
+      <c r="HC38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD38" s="156" t="s">
+        <v>1034</v>
+      </c>
+      <c r="HE38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG38" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI38" s="200" t="s">
+        <v>698</v>
+      </c>
+      <c r="HJ38" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK38" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM38" s="184" t="s">
+        <v>804</v>
+      </c>
     </row>
-    <row r="39" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A39" s="92">
         <v>36</v>
       </c>
-      <c r="B39" s="237"/>
+      <c r="B39" s="250"/>
       <c r="C39" s="64" t="s">
         <v>476</v>
       </c>
@@ -37596,12 +39671,54 @@
       <c r="GY39" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ39" s="188">
+        <v>20</v>
+      </c>
+      <c r="HA39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB39" s="159">
+        <v>86</v>
+      </c>
+      <c r="HC39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD39" s="188">
+        <v>20</v>
+      </c>
+      <c r="HE39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG39" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI39" s="200">
+        <v>2</v>
+      </c>
+      <c r="HJ39" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK39" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM39" s="184">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A40" s="92">
         <v>37</v>
       </c>
-      <c r="B40" s="237"/>
+      <c r="B40" s="250"/>
       <c r="C40" s="64" t="s">
         <v>477</v>
       </c>
@@ -38215,12 +40332,54 @@
       <c r="GY40" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ40" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB40" s="159" t="s">
+        <v>1034</v>
+      </c>
+      <c r="HC40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD40" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE40" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF40" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG40" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH40" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI40" s="200" t="s">
+        <v>1034</v>
+      </c>
+      <c r="HJ40" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK40" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM40" s="169" t="s">
+        <v>805</v>
+      </c>
     </row>
-    <row r="41" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A41" s="92">
         <v>38</v>
       </c>
-      <c r="B41" s="237"/>
+      <c r="B41" s="250"/>
       <c r="C41" s="64" t="s">
         <v>478</v>
       </c>
@@ -38834,12 +40993,54 @@
       <c r="GY41" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ41" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB41" s="159">
+        <v>20</v>
+      </c>
+      <c r="HC41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD41" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE41" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF41" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG41" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH41" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI41" s="200">
+        <v>20</v>
+      </c>
+      <c r="HJ41" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK41" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM41" s="185">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A42" s="92">
         <v>39</v>
       </c>
-      <c r="B42" s="237"/>
+      <c r="B42" s="250"/>
       <c r="C42" s="64" t="s">
         <v>479</v>
       </c>
@@ -39453,12 +41654,54 @@
       <c r="GY42" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ42" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG42" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI42" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ42" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK42" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM42" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="43" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A43" s="92">
         <v>40</v>
       </c>
-      <c r="B43" s="237"/>
+      <c r="B43" s="250"/>
       <c r="C43" s="64" t="s">
         <v>480</v>
       </c>
@@ -40072,12 +42315,54 @@
       <c r="GY43" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ43" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG43" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI43" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ43" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK43" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM43" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="44" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A44" s="92">
         <v>41</v>
       </c>
-      <c r="B44" s="237"/>
+      <c r="B44" s="250"/>
       <c r="C44" s="64" t="s">
         <v>481</v>
       </c>
@@ -40691,12 +42976,54 @@
       <c r="GY44" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ44" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG44" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI44" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ44" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK44" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM44" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="45" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A45" s="92">
         <v>42</v>
       </c>
-      <c r="B45" s="237"/>
+      <c r="B45" s="250"/>
       <c r="C45" s="64" t="s">
         <v>482</v>
       </c>
@@ -41310,12 +43637,54 @@
       <c r="GY45" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ45" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG45" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI45" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ45" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK45" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM45" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="46" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A46" s="92">
         <v>43</v>
       </c>
-      <c r="B46" s="237"/>
+      <c r="B46" s="250"/>
       <c r="C46" s="64" t="s">
         <v>483</v>
       </c>
@@ -41929,12 +44298,54 @@
       <c r="GY46" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ46" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG46" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI46" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ46" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK46" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM46" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="47" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A47" s="92">
         <v>44</v>
       </c>
-      <c r="B47" s="237"/>
+      <c r="B47" s="250"/>
       <c r="C47" s="64" t="s">
         <v>484</v>
       </c>
@@ -42548,12 +44959,54 @@
       <c r="GY47" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ47" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG47" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI47" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ47" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK47" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM47" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="48" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A48" s="92">
         <v>45</v>
       </c>
-      <c r="B48" s="237"/>
+      <c r="B48" s="250"/>
       <c r="C48" s="64" t="s">
         <v>485</v>
       </c>
@@ -43167,12 +45620,54 @@
       <c r="GY48" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ48" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG48" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI48" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ48" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK48" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM48" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="49" spans="1:207" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:221" s="68" customFormat="1" ht="14.4">
       <c r="A49" s="92">
         <v>46</v>
       </c>
-      <c r="B49" s="237"/>
+      <c r="B49" s="250"/>
       <c r="C49" s="64" t="s">
         <v>486</v>
       </c>
@@ -43786,12 +46281,54 @@
       <c r="GY49" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="GZ49" s="208" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG49" s="187" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI49" s="200" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ49" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK49" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM49" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="50" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:221" ht="14.4">
       <c r="A50" s="92">
         <v>47</v>
       </c>
-      <c r="B50" s="237"/>
+      <c r="B50" s="250"/>
       <c r="C50" s="55" t="s">
         <v>487</v>
       </c>
@@ -44407,12 +46944,54 @@
       <c r="GY50" s="115" t="s">
         <v>3252</v>
       </c>
+      <c r="GZ50" s="187" t="s">
+        <v>3264</v>
+      </c>
+      <c r="HA50" s="159" t="s">
+        <v>3275</v>
+      </c>
+      <c r="HB50" s="159" t="s">
+        <v>3295</v>
+      </c>
+      <c r="HC50" s="159" t="s">
+        <v>3275</v>
+      </c>
+      <c r="HD50" s="187" t="s">
+        <v>3264</v>
+      </c>
+      <c r="HE50" s="115" t="s">
+        <v>3327</v>
+      </c>
+      <c r="HF50" s="115" t="s">
+        <v>3327</v>
+      </c>
+      <c r="HG50" s="155" t="s">
+        <v>3354</v>
+      </c>
+      <c r="HH50" s="115" t="s">
+        <v>3327</v>
+      </c>
+      <c r="HI50" s="200" t="s">
+        <v>3373</v>
+      </c>
+      <c r="HJ50" s="115" t="s">
+        <v>3384</v>
+      </c>
+      <c r="HK50" s="115" t="s">
+        <v>3402</v>
+      </c>
+      <c r="HL50" s="115" t="s">
+        <v>3417</v>
+      </c>
+      <c r="HM50" s="115" t="s">
+        <v>3434</v>
+      </c>
     </row>
-    <row r="51" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:221" ht="14.4">
       <c r="A51" s="92">
         <v>48</v>
       </c>
-      <c r="B51" s="237"/>
+      <c r="B51" s="250"/>
       <c r="C51" s="55" t="s">
         <v>488</v>
       </c>
@@ -45028,12 +47607,54 @@
       <c r="GY51" s="115" t="s">
         <v>3253</v>
       </c>
+      <c r="GZ51" s="69" t="s">
+        <v>3265</v>
+      </c>
+      <c r="HA51" s="159" t="s">
+        <v>3276</v>
+      </c>
+      <c r="HB51" s="159" t="s">
+        <v>3296</v>
+      </c>
+      <c r="HC51" s="159" t="s">
+        <v>3303</v>
+      </c>
+      <c r="HD51" s="69" t="s">
+        <v>3311</v>
+      </c>
+      <c r="HE51" s="185" t="s">
+        <v>3328</v>
+      </c>
+      <c r="HF51" s="185" t="s">
+        <v>3341</v>
+      </c>
+      <c r="HG51" s="187" t="s">
+        <v>3355</v>
+      </c>
+      <c r="HH51" s="185" t="s">
+        <v>3361</v>
+      </c>
+      <c r="HI51" s="155" t="s">
+        <v>3374</v>
+      </c>
+      <c r="HJ51" s="115" t="s">
+        <v>3385</v>
+      </c>
+      <c r="HK51" s="115" t="s">
+        <v>3403</v>
+      </c>
+      <c r="HL51" s="115" t="s">
+        <v>3418</v>
+      </c>
+      <c r="HM51" s="115" t="s">
+        <v>3435</v>
+      </c>
     </row>
-    <row r="52" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:221" ht="14.4">
       <c r="A52" s="92">
         <v>49</v>
       </c>
-      <c r="B52" s="237"/>
+      <c r="B52" s="250"/>
       <c r="C52" s="55" t="s">
         <v>489</v>
       </c>
@@ -45649,12 +48270,54 @@
       <c r="GY52" s="115" t="s">
         <v>3254</v>
       </c>
+      <c r="GZ52" s="69" t="s">
+        <v>3266</v>
+      </c>
+      <c r="HA52" s="159" t="s">
+        <v>3277</v>
+      </c>
+      <c r="HB52" s="159" t="s">
+        <v>3297</v>
+      </c>
+      <c r="HC52" s="159" t="s">
+        <v>3277</v>
+      </c>
+      <c r="HD52" s="69" t="s">
+        <v>3312</v>
+      </c>
+      <c r="HE52" s="185" t="s">
+        <v>3329</v>
+      </c>
+      <c r="HF52" s="185" t="s">
+        <v>3329</v>
+      </c>
+      <c r="HG52" s="187" t="s">
+        <v>3356</v>
+      </c>
+      <c r="HH52" s="185" t="s">
+        <v>3329</v>
+      </c>
+      <c r="HI52" s="155" t="s">
+        <v>3375</v>
+      </c>
+      <c r="HJ52" s="115" t="s">
+        <v>3386</v>
+      </c>
+      <c r="HK52" s="115" t="s">
+        <v>3404</v>
+      </c>
+      <c r="HL52" s="115" t="s">
+        <v>3419</v>
+      </c>
+      <c r="HM52" s="115" t="s">
+        <v>3436</v>
+      </c>
     </row>
-    <row r="53" spans="1:207" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:221" ht="14.05" customHeight="1">
       <c r="A53" s="92">
         <v>50</v>
       </c>
-      <c r="B53" s="238" t="s">
+      <c r="B53" s="251" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="54" t="s">
@@ -46272,12 +48935,54 @@
       <c r="GY53" s="185" t="s">
         <v>206</v>
       </c>
+      <c r="GZ53" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="HA53" s="183" t="s">
+        <v>861</v>
+      </c>
+      <c r="HB53" s="183" t="s">
+        <v>206</v>
+      </c>
+      <c r="HC53" s="183" t="s">
+        <v>861</v>
+      </c>
+      <c r="HD53" s="155" t="s">
+        <v>206</v>
+      </c>
+      <c r="HE53" s="185" t="s">
+        <v>207</v>
+      </c>
+      <c r="HF53" s="185" t="s">
+        <v>206</v>
+      </c>
+      <c r="HG53" s="155" t="s">
+        <v>206</v>
+      </c>
+      <c r="HH53" s="185" t="s">
+        <v>207</v>
+      </c>
+      <c r="HI53" s="201" t="s">
+        <v>206</v>
+      </c>
+      <c r="HJ53" s="185" t="s">
+        <v>206</v>
+      </c>
+      <c r="HK53" s="185" t="s">
+        <v>206</v>
+      </c>
+      <c r="HL53" s="185" t="s">
+        <v>207</v>
+      </c>
+      <c r="HM53" s="185" t="s">
+        <v>207</v>
+      </c>
     </row>
-    <row r="54" spans="1:207" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:221" ht="13.8">
       <c r="A54" s="92">
         <v>51</v>
       </c>
-      <c r="B54" s="238"/>
+      <c r="B54" s="251"/>
       <c r="C54" s="54" t="s">
         <v>440</v>
       </c>
@@ -46893,12 +49598,54 @@
       <c r="GY54" s="115" t="s">
         <v>61</v>
       </c>
+      <c r="GZ54" s="191" t="s">
+        <v>61</v>
+      </c>
+      <c r="HA54" s="159" t="s">
+        <v>61</v>
+      </c>
+      <c r="HB54" s="185" t="s">
+        <v>858</v>
+      </c>
+      <c r="HC54" s="159" t="s">
+        <v>61</v>
+      </c>
+      <c r="HD54" s="191" t="s">
+        <v>61</v>
+      </c>
+      <c r="HE54" s="169" t="s">
+        <v>728</v>
+      </c>
+      <c r="HF54" s="169" t="s">
+        <v>61</v>
+      </c>
+      <c r="HG54" s="155" t="s">
+        <v>858</v>
+      </c>
+      <c r="HH54" s="169" t="s">
+        <v>728</v>
+      </c>
+      <c r="HI54" s="201" t="s">
+        <v>858</v>
+      </c>
+      <c r="HJ54" s="185" t="s">
+        <v>61</v>
+      </c>
+      <c r="HK54" s="185" t="s">
+        <v>61</v>
+      </c>
+      <c r="HL54" s="185" t="s">
+        <v>728</v>
+      </c>
+      <c r="HM54" s="185" t="s">
+        <v>3437</v>
+      </c>
     </row>
-    <row r="55" spans="1:207" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:221" ht="13.8">
       <c r="A55" s="92">
         <v>52</v>
       </c>
-      <c r="B55" s="238"/>
+      <c r="B55" s="251"/>
       <c r="C55" s="13" t="s">
         <v>441</v>
       </c>
@@ -47514,12 +50261,54 @@
       <c r="GY55" s="115" t="s">
         <v>3212</v>
       </c>
+      <c r="GZ55" s="69" t="s">
+        <v>3267</v>
+      </c>
+      <c r="HA55" s="159" t="s">
+        <v>1511</v>
+      </c>
+      <c r="HB55" s="185" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HC55" s="159" t="s">
+        <v>1511</v>
+      </c>
+      <c r="HD55" s="69" t="s">
+        <v>3313</v>
+      </c>
+      <c r="HE55" s="185" t="s">
+        <v>3330</v>
+      </c>
+      <c r="HF55" s="185" t="s">
+        <v>3342</v>
+      </c>
+      <c r="HG55" s="155" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HH55" s="185" t="s">
+        <v>3362</v>
+      </c>
+      <c r="HI55" s="201" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HJ55" s="185" t="s">
+        <v>3387</v>
+      </c>
+      <c r="HK55" s="185" t="s">
+        <v>2606</v>
+      </c>
+      <c r="HL55" s="185" t="s">
+        <v>3420</v>
+      </c>
+      <c r="HM55" s="185" t="s">
+        <v>3438</v>
+      </c>
     </row>
-    <row r="56" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:221" ht="14.4">
       <c r="A56" s="92">
         <v>53</v>
       </c>
-      <c r="B56" s="238"/>
+      <c r="B56" s="251"/>
       <c r="C56" s="13" t="s">
         <v>490</v>
       </c>
@@ -48133,12 +50922,54 @@
       <c r="GY56" s="115" t="s">
         <v>3213</v>
       </c>
+      <c r="GZ56" s="69" t="s">
+        <v>3268</v>
+      </c>
+      <c r="HA56" s="220" t="s">
+        <v>3278</v>
+      </c>
+      <c r="HB56" s="185" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HC56" s="159" t="s">
+        <v>3304</v>
+      </c>
+      <c r="HD56" s="69" t="s">
+        <v>3314</v>
+      </c>
+      <c r="HE56" s="185" t="s">
+        <v>3331</v>
+      </c>
+      <c r="HF56" s="185" t="s">
+        <v>3343</v>
+      </c>
+      <c r="HG56" s="155" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HH56" s="185" t="s">
+        <v>3363</v>
+      </c>
+      <c r="HI56" s="201" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HJ56" s="194" t="s">
+        <v>3388</v>
+      </c>
+      <c r="HK56" s="186" t="s">
+        <v>3405</v>
+      </c>
+      <c r="HL56" s="185" t="s">
+        <v>3421</v>
+      </c>
+      <c r="HM56" s="194" t="s">
+        <v>3439</v>
+      </c>
     </row>
-    <row r="57" spans="1:207" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:221" ht="13.8">
       <c r="A57" s="92">
         <v>54</v>
       </c>
-      <c r="B57" s="238"/>
+      <c r="B57" s="251"/>
       <c r="C57" s="56" t="s">
         <v>491</v>
       </c>
@@ -48754,12 +51585,54 @@
       <c r="GY57" s="115" t="s">
         <v>3214</v>
       </c>
+      <c r="GZ57" s="69" t="s">
+        <v>3269</v>
+      </c>
+      <c r="HA57" s="159" t="s">
+        <v>3279</v>
+      </c>
+      <c r="HB57" s="185" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HC57" s="159" t="s">
+        <v>3279</v>
+      </c>
+      <c r="HD57" s="69" t="s">
+        <v>3269</v>
+      </c>
+      <c r="HE57" s="185" t="s">
+        <v>3332</v>
+      </c>
+      <c r="HF57" s="185" t="s">
+        <v>3332</v>
+      </c>
+      <c r="HG57" s="155" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HH57" s="185" t="s">
+        <v>3364</v>
+      </c>
+      <c r="HI57" s="201" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HJ57" s="115" t="s">
+        <v>3389</v>
+      </c>
+      <c r="HK57" s="115" t="s">
+        <v>3389</v>
+      </c>
+      <c r="HL57" s="115" t="s">
+        <v>3389</v>
+      </c>
+      <c r="HM57" s="115" t="s">
+        <v>3389</v>
+      </c>
     </row>
-    <row r="58" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:221" ht="14.4">
       <c r="A58" s="92">
         <v>55</v>
       </c>
-      <c r="B58" s="238"/>
+      <c r="B58" s="251"/>
       <c r="C58" s="13" t="s">
         <v>444</v>
       </c>
@@ -49346,12 +52219,54 @@
       <c r="GY58" s="115" t="s">
         <v>3213</v>
       </c>
+      <c r="GZ58" s="69" t="s">
+        <v>3268</v>
+      </c>
+      <c r="HA58" s="159" t="s">
+        <v>3280</v>
+      </c>
+      <c r="HB58" s="185" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HC58" s="159" t="s">
+        <v>3280</v>
+      </c>
+      <c r="HD58" s="69" t="s">
+        <v>3314</v>
+      </c>
+      <c r="HE58" s="185" t="s">
+        <v>3331</v>
+      </c>
+      <c r="HF58" s="185" t="s">
+        <v>3343</v>
+      </c>
+      <c r="HG58" s="155" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HH58" s="185" t="s">
+        <v>3363</v>
+      </c>
+      <c r="HI58" s="201" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HJ58" s="194" t="s">
+        <v>3388</v>
+      </c>
+      <c r="HK58" s="185" t="s">
+        <v>3406</v>
+      </c>
+      <c r="HL58" s="185" t="s">
+        <v>3421</v>
+      </c>
+      <c r="HM58" s="194" t="s">
+        <v>3439</v>
+      </c>
     </row>
-    <row r="59" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:221" ht="14.4">
       <c r="A59" s="92">
         <v>56</v>
       </c>
-      <c r="B59" s="238"/>
+      <c r="B59" s="251"/>
       <c r="C59" s="13" t="s">
         <v>445</v>
       </c>
@@ -49967,12 +52882,54 @@
       <c r="GY59" s="115" t="s">
         <v>3213</v>
       </c>
+      <c r="GZ59" s="69" t="s">
+        <v>3268</v>
+      </c>
+      <c r="HA59" s="159" t="s">
+        <v>3281</v>
+      </c>
+      <c r="HB59" s="185" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HC59" s="159" t="s">
+        <v>3281</v>
+      </c>
+      <c r="HD59" s="69" t="s">
+        <v>3314</v>
+      </c>
+      <c r="HE59" s="185" t="s">
+        <v>3331</v>
+      </c>
+      <c r="HF59" s="185" t="s">
+        <v>3343</v>
+      </c>
+      <c r="HG59" s="155" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HH59" s="185" t="s">
+        <v>3363</v>
+      </c>
+      <c r="HI59" s="201" t="s">
+        <v>2330</v>
+      </c>
+      <c r="HJ59" s="194" t="s">
+        <v>3388</v>
+      </c>
+      <c r="HK59" s="185" t="s">
+        <v>3406</v>
+      </c>
+      <c r="HL59" s="185" t="s">
+        <v>3421</v>
+      </c>
+      <c r="HM59" s="194" t="s">
+        <v>3439</v>
+      </c>
     </row>
-    <row r="60" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:221" ht="14.4">
       <c r="A60" s="92">
         <v>57</v>
       </c>
-      <c r="B60" s="238"/>
+      <c r="B60" s="251"/>
       <c r="C60" s="54" t="s">
         <v>492</v>
       </c>
@@ -50588,12 +53545,54 @@
       <c r="GY60" s="184">
         <v>1</v>
       </c>
+      <c r="GZ60" s="188">
+        <v>1</v>
+      </c>
+      <c r="HA60" s="182">
+        <v>1</v>
+      </c>
+      <c r="HB60" s="184">
+        <v>1</v>
+      </c>
+      <c r="HC60" s="182">
+        <v>1</v>
+      </c>
+      <c r="HD60" s="188">
+        <v>1</v>
+      </c>
+      <c r="HE60" s="184">
+        <v>1</v>
+      </c>
+      <c r="HF60" s="184">
+        <v>1</v>
+      </c>
+      <c r="HG60" s="188">
+        <v>1</v>
+      </c>
+      <c r="HH60" s="184">
+        <v>1</v>
+      </c>
+      <c r="HI60" s="202">
+        <v>1</v>
+      </c>
+      <c r="HJ60" s="184">
+        <v>1</v>
+      </c>
+      <c r="HK60" s="184">
+        <v>1</v>
+      </c>
+      <c r="HL60" s="65">
+        <v>1</v>
+      </c>
+      <c r="HM60" s="184">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:207" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:221" ht="14.05" customHeight="1">
       <c r="A61" s="92">
         <v>58</v>
       </c>
-      <c r="B61" s="239" t="s">
+      <c r="B61" s="252" t="s">
         <v>342</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -51209,12 +54208,54 @@
       <c r="GY61" s="157">
         <v>45870</v>
       </c>
+      <c r="GZ61" s="205">
+        <v>45392</v>
+      </c>
+      <c r="HA61" s="192">
+        <v>45413</v>
+      </c>
+      <c r="HB61" s="192">
+        <v>45413</v>
+      </c>
+      <c r="HC61" s="192">
+        <v>45413</v>
+      </c>
+      <c r="HD61" s="205">
+        <v>45392</v>
+      </c>
+      <c r="HE61" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HF61" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HG61" s="189">
+        <v>45413</v>
+      </c>
+      <c r="HH61" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HI61" s="203">
+        <v>45413</v>
+      </c>
+      <c r="HJ61" s="192">
+        <v>45894</v>
+      </c>
+      <c r="HK61" s="192">
+        <v>45894</v>
+      </c>
+      <c r="HL61" s="193">
+        <v>45820</v>
+      </c>
+      <c r="HM61" s="193" t="s">
+        <v>3440</v>
+      </c>
     </row>
-    <row r="62" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:221" ht="14.4">
       <c r="A62" s="92">
         <v>59</v>
       </c>
-      <c r="B62" s="239"/>
+      <c r="B62" s="252"/>
       <c r="C62" s="13" t="s">
         <v>446</v>
       </c>
@@ -51830,12 +54871,54 @@
       <c r="GY62" s="157">
         <v>45871</v>
       </c>
+      <c r="GZ62" s="219">
+        <v>45709</v>
+      </c>
+      <c r="HA62" s="221">
+        <v>45765</v>
+      </c>
+      <c r="HB62" s="221">
+        <v>45771</v>
+      </c>
+      <c r="HC62" s="221">
+        <v>45765</v>
+      </c>
+      <c r="HD62" s="223">
+        <v>45709</v>
+      </c>
+      <c r="HE62" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HF62" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HG62" s="223">
+        <v>45709</v>
+      </c>
+      <c r="HH62" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HI62" s="227">
+        <v>45709</v>
+      </c>
+      <c r="HJ62" s="192">
+        <v>45894</v>
+      </c>
+      <c r="HK62" s="192">
+        <v>45894</v>
+      </c>
+      <c r="HL62" s="193">
+        <v>45897</v>
+      </c>
+      <c r="HM62" s="230">
+        <v>45894</v>
+      </c>
     </row>
-    <row r="63" spans="1:207" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:221" ht="14.4">
       <c r="A63" s="92">
         <v>60</v>
       </c>
-      <c r="B63" s="239"/>
+      <c r="B63" s="252"/>
       <c r="C63" s="13" t="s">
         <v>447</v>
       </c>
@@ -52451,12 +55534,54 @@
       <c r="GY63" s="115" t="s">
         <v>30</v>
       </c>
+      <c r="GZ63" s="69" t="s">
+        <v>2386</v>
+      </c>
+      <c r="HA63" s="159" t="s">
+        <v>3282</v>
+      </c>
+      <c r="HB63" s="159" t="s">
+        <v>2386</v>
+      </c>
+      <c r="HC63" s="159" t="s">
+        <v>3282</v>
+      </c>
+      <c r="HD63" s="155" t="s">
+        <v>2386</v>
+      </c>
+      <c r="HE63" s="185" t="s">
+        <v>30</v>
+      </c>
+      <c r="HF63" s="185" t="s">
+        <v>30</v>
+      </c>
+      <c r="HG63" s="187" t="s">
+        <v>2386</v>
+      </c>
+      <c r="HH63" s="185" t="s">
+        <v>30</v>
+      </c>
+      <c r="HI63" s="228" t="s">
+        <v>2386</v>
+      </c>
+      <c r="HJ63" s="115" t="s">
+        <v>2653</v>
+      </c>
+      <c r="HK63" s="115" t="s">
+        <v>2653</v>
+      </c>
+      <c r="HL63" s="115" t="s">
+        <v>2085</v>
+      </c>
+      <c r="HM63" s="115" t="s">
+        <v>2085</v>
+      </c>
     </row>
-    <row r="64" spans="1:207" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:221" ht="14.4">
       <c r="A64" s="92">
         <v>61</v>
       </c>
-      <c r="B64" s="239"/>
+      <c r="B64" s="252"/>
       <c r="C64" s="13" t="s">
         <v>494</v>
       </c>
@@ -53072,12 +56197,54 @@
       <c r="GY64" s="115" t="s">
         <v>2698</v>
       </c>
+      <c r="GZ64" s="69" t="s">
+        <v>2332</v>
+      </c>
+      <c r="HA64" s="159" t="s">
+        <v>3283</v>
+      </c>
+      <c r="HB64" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="HC64" s="159" t="s">
+        <v>3283</v>
+      </c>
+      <c r="HD64" s="155" t="s">
+        <v>2332</v>
+      </c>
+      <c r="HE64" s="185" t="s">
+        <v>3333</v>
+      </c>
+      <c r="HF64" s="185" t="s">
+        <v>3333</v>
+      </c>
+      <c r="HG64" s="187" t="s">
+        <v>2332</v>
+      </c>
+      <c r="HH64" s="185" t="s">
+        <v>2332</v>
+      </c>
+      <c r="HI64" s="228" t="s">
+        <v>2332</v>
+      </c>
+      <c r="HJ64" s="115" t="s">
+        <v>2669</v>
+      </c>
+      <c r="HK64" s="115" t="s">
+        <v>3407</v>
+      </c>
+      <c r="HL64" s="115" t="s">
+        <v>2669</v>
+      </c>
+      <c r="HM64" s="115" t="s">
+        <v>3407</v>
+      </c>
     </row>
-    <row r="65" spans="1:255" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:255" ht="14.4">
       <c r="A65" s="92">
         <v>62</v>
       </c>
-      <c r="B65" s="239"/>
+      <c r="B65" s="252"/>
       <c r="C65" s="54" t="s">
         <v>495</v>
       </c>
@@ -53396,12 +56563,54 @@
       <c r="GY65" s="157">
         <v>45871</v>
       </c>
+      <c r="GZ65" s="205">
+        <v>45798</v>
+      </c>
+      <c r="HA65" s="221">
+        <v>45782</v>
+      </c>
+      <c r="HB65" s="221">
+        <v>45771</v>
+      </c>
+      <c r="HC65" s="221">
+        <v>45782</v>
+      </c>
+      <c r="HD65" s="189">
+        <v>45798</v>
+      </c>
+      <c r="HE65" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HF65" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HG65" s="223">
+        <v>45798</v>
+      </c>
+      <c r="HH65" s="192">
+        <v>45893</v>
+      </c>
+      <c r="HI65" s="227">
+        <v>45803</v>
+      </c>
+      <c r="HJ65" s="192">
+        <v>45894</v>
+      </c>
+      <c r="HK65" s="192">
+        <v>45894</v>
+      </c>
+      <c r="HL65" s="193">
+        <v>45897</v>
+      </c>
+      <c r="HM65" s="230">
+        <v>45894</v>
+      </c>
     </row>
-    <row r="66" spans="1:255" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:255" ht="13.8">
       <c r="A66" s="92">
         <v>63</v>
       </c>
-      <c r="B66" s="239"/>
+      <c r="B66" s="252"/>
       <c r="C66" s="54" t="s">
         <v>496</v>
       </c>
@@ -53718,12 +56927,54 @@
       <c r="GY66" s="115" t="s">
         <v>30</v>
       </c>
+      <c r="GZ66" s="191" t="s">
+        <v>3051</v>
+      </c>
+      <c r="HA66" s="194" t="s">
+        <v>1843</v>
+      </c>
+      <c r="HB66" s="194" t="s">
+        <v>1843</v>
+      </c>
+      <c r="HC66" s="194" t="s">
+        <v>1843</v>
+      </c>
+      <c r="HD66" s="156" t="s">
+        <v>3051</v>
+      </c>
+      <c r="HE66" s="185" t="s">
+        <v>30</v>
+      </c>
+      <c r="HF66" s="185" t="s">
+        <v>30</v>
+      </c>
+      <c r="HG66" s="156" t="s">
+        <v>3051</v>
+      </c>
+      <c r="HH66" s="185" t="s">
+        <v>30</v>
+      </c>
+      <c r="HI66" s="179" t="s">
+        <v>3051</v>
+      </c>
+      <c r="HJ66" s="185" t="s">
+        <v>2653</v>
+      </c>
+      <c r="HK66" s="185" t="s">
+        <v>2653</v>
+      </c>
+      <c r="HL66" s="115" t="s">
+        <v>2653</v>
+      </c>
+      <c r="HM66" s="169" t="s">
+        <v>2653</v>
+      </c>
     </row>
-    <row r="67" spans="1:255" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:255" ht="14.4">
       <c r="A67" s="92">
         <v>64</v>
       </c>
-      <c r="B67" s="239"/>
+      <c r="B67" s="252"/>
       <c r="C67" s="13" t="s">
         <v>497</v>
       </c>
@@ -53850,12 +57101,28 @@
       <c r="GW67" s="206"/>
       <c r="GX67" s="156"/>
       <c r="GY67" s="156"/>
+      <c r="GZ67" s="191"/>
+      <c r="HA67" s="194"/>
+      <c r="HB67" s="194" t="s">
+        <v>3298</v>
+      </c>
+      <c r="HC67" s="194"/>
+      <c r="HD67" s="169"/>
+      <c r="HE67" s="169"/>
+      <c r="HF67" s="169"/>
+      <c r="HG67" s="156"/>
+      <c r="HH67" s="169"/>
+      <c r="HI67" s="47"/>
+      <c r="HJ67" s="185"/>
+      <c r="HK67" s="185"/>
+      <c r="HL67" s="156"/>
+      <c r="HM67" s="169"/>
     </row>
-    <row r="68" spans="1:255" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:255" ht="13.8">
       <c r="A68" s="92">
         <v>65</v>
       </c>
-      <c r="B68" s="229" t="s">
+      <c r="B68" s="242" t="s">
         <v>185</v>
       </c>
       <c r="C68" s="15" t="s">
@@ -53927,12 +57194,22 @@
       <c r="GW68" s="206"/>
       <c r="GX68" s="156"/>
       <c r="GY68" s="156"/>
+      <c r="GZ68" s="191"/>
+      <c r="HB68" s="215"/>
+      <c r="HD68" s="169"/>
+      <c r="HE68" s="169"/>
+      <c r="HG68" s="156"/>
+      <c r="HH68" s="169"/>
+      <c r="HJ68" s="185"/>
+      <c r="HK68" s="185"/>
+      <c r="HL68" s="156"/>
+      <c r="HM68" s="169"/>
     </row>
-    <row r="69" spans="1:255" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:255" ht="13.8">
       <c r="A69" s="92">
         <v>66</v>
       </c>
-      <c r="B69" s="229"/>
+      <c r="B69" s="242"/>
       <c r="C69" s="15" t="s">
         <v>449</v>
       </c>
@@ -53977,12 +57254,16 @@
       <c r="FV69" s="196"/>
       <c r="GC69" s="156"/>
       <c r="GW69" s="206"/>
+      <c r="HB69" s="215"/>
+      <c r="HE69" s="169"/>
+      <c r="HK69" s="185"/>
+      <c r="HM69" s="156"/>
     </row>
-    <row r="70" spans="1:255" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:255" ht="13.8">
       <c r="A70" s="92">
         <v>67</v>
       </c>
-      <c r="B70" s="229"/>
+      <c r="B70" s="242"/>
       <c r="C70" s="15" t="s">
         <v>450</v>
       </c>
@@ -54017,12 +57298,13 @@
       <c r="ER70" s="169"/>
       <c r="GC70" s="156"/>
       <c r="GW70" s="206"/>
+      <c r="HK70" s="156"/>
     </row>
-    <row r="71" spans="1:255" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:255" ht="13.8">
       <c r="A71" s="92">
         <v>68</v>
       </c>
-      <c r="B71" s="229"/>
+      <c r="B71" s="242"/>
       <c r="C71" s="15" t="s">
         <v>498</v>
       </c>
@@ -54053,11 +57335,11 @@
       <c r="EG71" s="156"/>
       <c r="ER71" s="169"/>
     </row>
-    <row r="72" spans="1:255" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:255">
       <c r="A72" s="92">
         <v>69</v>
       </c>
-      <c r="B72" s="230"/>
+      <c r="B72" s="243"/>
       <c r="C72" s="16" t="s">
         <v>499</v>
       </c>
@@ -54085,7 +57367,7 @@
       <c r="BY72" s="158"/>
       <c r="BZ72" s="158"/>
     </row>
-    <row r="73" spans="1:255" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:255">
       <c r="U73" s="12"/>
       <c r="AF73" s="48"/>
       <c r="AG73" s="49"/>
@@ -54107,7 +57389,7 @@
       <c r="BY73" s="90"/>
       <c r="BZ73" s="90"/>
     </row>
-    <row r="74" spans="1:255" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:255">
       <c r="A74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="105"/>
@@ -54770,7 +58052,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:BT110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="12.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="104" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="104"/>
@@ -54791,7 +58073,7 @@
     <col min="17" max="16384" width="11.5546875" style="104"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:72" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:72">
       <c r="E1" s="104" t="s">
         <v>694</v>
       </c>
@@ -54928,7 +58210,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="2" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:72" ht="13.8">
       <c r="B2" s="34" t="s">
         <v>183</v>
       </c>
@@ -54938,7 +58220,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="2:72" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:72">
       <c r="B3" s="58"/>
       <c r="C3" s="17" t="s">
         <v>181</v>
@@ -55105,8 +58387,8 @@
       <c r="BS3" s="36"/>
       <c r="BT3" s="36"/>
     </row>
-    <row r="4" spans="2:72" x14ac:dyDescent="0.4">
-      <c r="B4" s="231" t="s">
+    <row r="4" spans="2:72">
+      <c r="B4" s="244" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="55" t="s">
@@ -55274,8 +58556,8 @@
       <c r="BS4" s="12"/>
       <c r="BT4" s="12"/>
     </row>
-    <row r="5" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="232"/>
+    <row r="5" spans="2:72" ht="13.8">
+      <c r="B5" s="245"/>
       <c r="C5" s="54" t="s">
         <v>456</v>
       </c>
@@ -55441,7 +58723,7 @@
       <c r="BS5" s="106"/>
       <c r="BT5" s="106"/>
     </row>
-    <row r="6" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:72" ht="13.8">
       <c r="B6" s="59"/>
       <c r="C6" s="54" t="s">
         <v>457</v>
@@ -55606,8 +58888,8 @@
       <c r="BS6" s="2"/>
       <c r="BT6" s="2"/>
     </row>
-    <row r="7" spans="2:72" x14ac:dyDescent="0.4">
-      <c r="B7" s="233" t="s">
+    <row r="7" spans="2:72">
+      <c r="B7" s="246" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="54" t="s">
@@ -55773,8 +59055,8 @@
       <c r="BS7" s="37"/>
       <c r="BT7" s="37"/>
     </row>
-    <row r="8" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B8" s="233"/>
+    <row r="8" spans="2:72" ht="13.8">
+      <c r="B8" s="246"/>
       <c r="C8" s="54" t="s">
         <v>458</v>
       </c>
@@ -55940,8 +59222,8 @@
       <c r="BS8" s="1"/>
       <c r="BT8" s="1"/>
     </row>
-    <row r="9" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="233"/>
+    <row r="9" spans="2:72" ht="13.8">
+      <c r="B9" s="246"/>
       <c r="C9" s="54" t="s">
         <v>459</v>
       </c>
@@ -56107,8 +59389,8 @@
       <c r="BS9" s="1"/>
       <c r="BT9" s="1"/>
     </row>
-    <row r="10" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B10" s="233"/>
+    <row r="10" spans="2:72" ht="13.8">
+      <c r="B10" s="246"/>
       <c r="C10" s="54" t="s">
         <v>460</v>
       </c>
@@ -56274,8 +59556,8 @@
       <c r="BS10" s="1"/>
       <c r="BT10" s="1"/>
     </row>
-    <row r="11" spans="2:72" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="234" t="s">
+    <row r="11" spans="2:72" ht="14.05" customHeight="1">
+      <c r="B11" s="247" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="55" t="s">
@@ -56441,8 +59723,8 @@
       <c r="BS11" s="106"/>
       <c r="BT11" s="106"/>
     </row>
-    <row r="12" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B12" s="235"/>
+    <row r="12" spans="2:72" ht="13.8">
+      <c r="B12" s="248"/>
       <c r="C12" s="56" t="s">
         <v>427</v>
       </c>
@@ -56606,8 +59888,8 @@
       <c r="BS12" s="2"/>
       <c r="BT12" s="2"/>
     </row>
-    <row r="13" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B13" s="235"/>
+    <row r="13" spans="2:72" ht="13.8">
+      <c r="B13" s="248"/>
       <c r="C13" s="56" t="s">
         <v>428</v>
       </c>
@@ -56771,8 +60053,8 @@
       <c r="BS13" s="106"/>
       <c r="BT13" s="106"/>
     </row>
-    <row r="14" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="235"/>
+    <row r="14" spans="2:72" ht="13.8">
+      <c r="B14" s="248"/>
       <c r="C14" s="56" t="s">
         <v>429</v>
       </c>
@@ -56936,8 +60218,8 @@
       <c r="BS14" s="2"/>
       <c r="BT14" s="2"/>
     </row>
-    <row r="15" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="235"/>
+    <row r="15" spans="2:72" ht="13.8">
+      <c r="B15" s="248"/>
       <c r="C15" s="56" t="s">
         <v>430</v>
       </c>
@@ -57101,8 +60383,8 @@
       <c r="BS15" s="2"/>
       <c r="BT15" s="2"/>
     </row>
-    <row r="16" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="235"/>
+    <row r="16" spans="2:72" ht="13.8">
+      <c r="B16" s="248"/>
       <c r="C16" s="56" t="s">
         <v>431</v>
       </c>
@@ -57266,8 +60548,8 @@
       <c r="BS16" s="2"/>
       <c r="BT16" s="2"/>
     </row>
-    <row r="17" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B17" s="235"/>
+    <row r="17" spans="2:72" ht="13.8">
+      <c r="B17" s="248"/>
       <c r="C17" s="56" t="s">
         <v>432</v>
       </c>
@@ -57431,8 +60713,8 @@
       <c r="BS17" s="2"/>
       <c r="BT17" s="2"/>
     </row>
-    <row r="18" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B18" s="235"/>
+    <row r="18" spans="2:72" ht="13.8">
+      <c r="B18" s="248"/>
       <c r="C18" s="56" t="s">
         <v>433</v>
       </c>
@@ -57596,8 +60878,8 @@
       <c r="BS18" s="2"/>
       <c r="BT18" s="2"/>
     </row>
-    <row r="19" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B19" s="235"/>
+    <row r="19" spans="2:72" ht="13.8">
+      <c r="B19" s="248"/>
       <c r="C19" s="56" t="s">
         <v>434</v>
       </c>
@@ -57761,8 +61043,8 @@
       <c r="BS19" s="2"/>
       <c r="BT19" s="2"/>
     </row>
-    <row r="20" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B20" s="235"/>
+    <row r="20" spans="2:72" ht="13.8">
+      <c r="B20" s="248"/>
       <c r="C20" s="56" t="s">
         <v>435</v>
       </c>
@@ -57926,8 +61208,8 @@
       <c r="BS20" s="2"/>
       <c r="BT20" s="2"/>
     </row>
-    <row r="21" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B21" s="236" t="s">
+    <row r="21" spans="2:72" ht="13.8">
+      <c r="B21" s="249" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="56" t="s">
@@ -58134,8 +61416,8 @@
       <c r="BS21" s="106"/>
       <c r="BT21" s="106"/>
     </row>
-    <row r="22" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B22" s="236"/>
+    <row r="22" spans="2:72" ht="13.8">
+      <c r="B22" s="249"/>
       <c r="C22" s="56" t="s">
         <v>437</v>
       </c>
@@ -58342,8 +61624,8 @@
       <c r="BS22" s="106"/>
       <c r="BT22" s="106"/>
     </row>
-    <row r="23" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B23" s="236"/>
+    <row r="23" spans="2:72" ht="13.8">
+      <c r="B23" s="249"/>
       <c r="C23" s="55" t="s">
         <v>461</v>
       </c>
@@ -58509,8 +61791,8 @@
       <c r="BS23" s="2"/>
       <c r="BT23" s="2"/>
     </row>
-    <row r="24" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B24" s="236"/>
+    <row r="24" spans="2:72" ht="13.8">
+      <c r="B24" s="249"/>
       <c r="C24" s="55" t="s">
         <v>462</v>
       </c>
@@ -58676,8 +61958,8 @@
       <c r="BS24" s="105"/>
       <c r="BT24" s="105"/>
     </row>
-    <row r="25" spans="2:72" ht="14.1" x14ac:dyDescent="0.5">
-      <c r="B25" s="236"/>
+    <row r="25" spans="2:72" ht="14.1">
+      <c r="B25" s="249"/>
       <c r="C25" s="56" t="s">
         <v>438</v>
       </c>
@@ -58841,8 +62123,8 @@
       <c r="BS25" s="6"/>
       <c r="BT25" s="6"/>
     </row>
-    <row r="26" spans="2:72" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="237" t="s">
+    <row r="26" spans="2:72" ht="14.05" customHeight="1">
+      <c r="B26" s="250" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="55" t="s">
@@ -59010,8 +62292,8 @@
       <c r="BS26" s="38"/>
       <c r="BT26" s="38"/>
     </row>
-    <row r="27" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B27" s="237"/>
+    <row r="27" spans="2:72" ht="13.8">
+      <c r="B27" s="250"/>
       <c r="C27" s="55" t="s">
         <v>464</v>
       </c>
@@ -59177,8 +62459,8 @@
       <c r="BS27" s="42"/>
       <c r="BT27" s="42"/>
     </row>
-    <row r="28" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B28" s="237"/>
+    <row r="28" spans="2:72" ht="13.8">
+      <c r="B28" s="250"/>
       <c r="C28" s="55" t="s">
         <v>465</v>
       </c>
@@ -59342,8 +62624,8 @@
       <c r="BS28" s="66"/>
       <c r="BT28" s="66"/>
     </row>
-    <row r="29" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B29" s="237"/>
+    <row r="29" spans="2:72" ht="13.8">
+      <c r="B29" s="250"/>
       <c r="C29" s="55" t="s">
         <v>466</v>
       </c>
@@ -59507,8 +62789,8 @@
       <c r="BS29" s="42"/>
       <c r="BT29" s="42"/>
     </row>
-    <row r="30" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B30" s="237"/>
+    <row r="30" spans="2:72" ht="13.8">
+      <c r="B30" s="250"/>
       <c r="C30" s="55" t="s">
         <v>467</v>
       </c>
@@ -59672,8 +62954,8 @@
       <c r="BS30" s="38"/>
       <c r="BT30" s="38"/>
     </row>
-    <row r="31" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B31" s="237"/>
+    <row r="31" spans="2:72" ht="13.8">
+      <c r="B31" s="250"/>
       <c r="C31" s="55" t="s">
         <v>468</v>
       </c>
@@ -59837,8 +63119,8 @@
       <c r="BS31" s="42"/>
       <c r="BT31" s="42"/>
     </row>
-    <row r="32" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B32" s="237"/>
+    <row r="32" spans="2:72" ht="13.8">
+      <c r="B32" s="250"/>
       <c r="C32" s="55" t="s">
         <v>469</v>
       </c>
@@ -60002,8 +63284,8 @@
       <c r="BS32" s="88"/>
       <c r="BT32" s="88"/>
     </row>
-    <row r="33" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B33" s="237"/>
+    <row r="33" spans="2:72" ht="13.8">
+      <c r="B33" s="250"/>
       <c r="C33" s="55" t="s">
         <v>470</v>
       </c>
@@ -60167,8 +63449,8 @@
       <c r="BS33" s="28"/>
       <c r="BT33" s="28"/>
     </row>
-    <row r="34" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B34" s="237"/>
+    <row r="34" spans="2:72" ht="13.8">
+      <c r="B34" s="250"/>
       <c r="C34" s="55" t="s">
         <v>471</v>
       </c>
@@ -60332,8 +63614,8 @@
       <c r="BS34" s="38"/>
       <c r="BT34" s="38"/>
     </row>
-    <row r="35" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B35" s="237"/>
+    <row r="35" spans="2:72" ht="13.8">
+      <c r="B35" s="250"/>
       <c r="C35" s="55" t="s">
         <v>472</v>
       </c>
@@ -60497,8 +63779,8 @@
       <c r="BS35" s="42"/>
       <c r="BT35" s="42"/>
     </row>
-    <row r="36" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B36" s="237"/>
+    <row r="36" spans="2:72" ht="13.8">
+      <c r="B36" s="250"/>
       <c r="C36" s="55" t="s">
         <v>473</v>
       </c>
@@ -60662,8 +63944,8 @@
       <c r="BS36" s="38"/>
       <c r="BT36" s="38"/>
     </row>
-    <row r="37" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B37" s="237"/>
+    <row r="37" spans="2:72" ht="13.8">
+      <c r="B37" s="250"/>
       <c r="C37" s="55" t="s">
         <v>474</v>
       </c>
@@ -60827,8 +64109,8 @@
       <c r="BS37" s="42"/>
       <c r="BT37" s="42"/>
     </row>
-    <row r="38" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B38" s="237"/>
+    <row r="38" spans="2:72" ht="13.8">
+      <c r="B38" s="250"/>
       <c r="C38" s="55" t="s">
         <v>475</v>
       </c>
@@ -60992,8 +64274,8 @@
       <c r="BS38" s="38"/>
       <c r="BT38" s="38"/>
     </row>
-    <row r="39" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B39" s="237"/>
+    <row r="39" spans="2:72" ht="13.8">
+      <c r="B39" s="250"/>
       <c r="C39" s="55" t="s">
         <v>476</v>
       </c>
@@ -61157,8 +64439,8 @@
       <c r="BS39" s="38"/>
       <c r="BT39" s="38"/>
     </row>
-    <row r="40" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B40" s="237"/>
+    <row r="40" spans="2:72" ht="13.8">
+      <c r="B40" s="250"/>
       <c r="C40" s="55" t="s">
         <v>477</v>
       </c>
@@ -61322,8 +64604,8 @@
       <c r="BS40" s="38"/>
       <c r="BT40" s="38"/>
     </row>
-    <row r="41" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B41" s="237"/>
+    <row r="41" spans="2:72" ht="13.8">
+      <c r="B41" s="250"/>
       <c r="C41" s="55" t="s">
         <v>478</v>
       </c>
@@ -61487,8 +64769,8 @@
       <c r="BS41" s="38"/>
       <c r="BT41" s="38"/>
     </row>
-    <row r="42" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B42" s="237"/>
+    <row r="42" spans="2:72" ht="13.8">
+      <c r="B42" s="250"/>
       <c r="C42" s="55" t="s">
         <v>479</v>
       </c>
@@ -61652,8 +64934,8 @@
       <c r="BS42" s="38"/>
       <c r="BT42" s="38"/>
     </row>
-    <row r="43" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B43" s="237"/>
+    <row r="43" spans="2:72" ht="13.8">
+      <c r="B43" s="250"/>
       <c r="C43" s="55" t="s">
         <v>480</v>
       </c>
@@ -61817,8 +65099,8 @@
       <c r="BS43" s="38"/>
       <c r="BT43" s="38"/>
     </row>
-    <row r="44" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B44" s="237"/>
+    <row r="44" spans="2:72" ht="13.8">
+      <c r="B44" s="250"/>
       <c r="C44" s="55" t="s">
         <v>481</v>
       </c>
@@ -61982,8 +65264,8 @@
       <c r="BS44" s="38"/>
       <c r="BT44" s="38"/>
     </row>
-    <row r="45" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B45" s="237"/>
+    <row r="45" spans="2:72" ht="13.8">
+      <c r="B45" s="250"/>
       <c r="C45" s="55" t="s">
         <v>482</v>
       </c>
@@ -62147,8 +65429,8 @@
       <c r="BS45" s="38"/>
       <c r="BT45" s="38"/>
     </row>
-    <row r="46" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B46" s="237"/>
+    <row r="46" spans="2:72" ht="13.8">
+      <c r="B46" s="250"/>
       <c r="C46" s="55" t="s">
         <v>483</v>
       </c>
@@ -62312,8 +65594,8 @@
       <c r="BS46" s="38"/>
       <c r="BT46" s="38"/>
     </row>
-    <row r="47" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B47" s="237"/>
+    <row r="47" spans="2:72" ht="13.8">
+      <c r="B47" s="250"/>
       <c r="C47" s="55" t="s">
         <v>484</v>
       </c>
@@ -62477,8 +65759,8 @@
       <c r="BS47" s="38"/>
       <c r="BT47" s="38"/>
     </row>
-    <row r="48" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B48" s="237"/>
+    <row r="48" spans="2:72" ht="13.8">
+      <c r="B48" s="250"/>
       <c r="C48" s="55" t="s">
         <v>485</v>
       </c>
@@ -62642,8 +65924,8 @@
       <c r="BS48" s="38"/>
       <c r="BT48" s="38"/>
     </row>
-    <row r="49" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B49" s="237"/>
+    <row r="49" spans="2:72" ht="13.8">
+      <c r="B49" s="250"/>
       <c r="C49" s="55" t="s">
         <v>486</v>
       </c>
@@ -62807,8 +66089,8 @@
       <c r="BS49" s="38"/>
       <c r="BT49" s="38"/>
     </row>
-    <row r="50" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B50" s="237"/>
+    <row r="50" spans="2:72" ht="13.8">
+      <c r="B50" s="250"/>
       <c r="C50" s="55" t="s">
         <v>487</v>
       </c>
@@ -62974,8 +66256,8 @@
       <c r="BS50" s="2"/>
       <c r="BT50" s="2"/>
     </row>
-    <row r="51" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B51" s="237"/>
+    <row r="51" spans="2:72" ht="13.8">
+      <c r="B51" s="250"/>
       <c r="C51" s="55" t="s">
         <v>488</v>
       </c>
@@ -63141,8 +66423,8 @@
       <c r="BS51" s="2"/>
       <c r="BT51" s="2"/>
     </row>
-    <row r="52" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B52" s="237"/>
+    <row r="52" spans="2:72" ht="13.8">
+      <c r="B52" s="250"/>
       <c r="C52" s="55" t="s">
         <v>489</v>
       </c>
@@ -63308,8 +66590,8 @@
       <c r="BS52" s="2"/>
       <c r="BT52" s="2"/>
     </row>
-    <row r="53" spans="2:72" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B53" s="238" t="s">
+    <row r="53" spans="2:72" ht="14.05" customHeight="1">
+      <c r="B53" s="251" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="54" t="s">
@@ -63477,8 +66759,8 @@
       <c r="BS53" s="105"/>
       <c r="BT53" s="105"/>
     </row>
-    <row r="54" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B54" s="238"/>
+    <row r="54" spans="2:72" ht="13.8">
+      <c r="B54" s="251"/>
       <c r="C54" s="54" t="s">
         <v>440</v>
       </c>
@@ -63644,8 +66926,8 @@
       <c r="BS54" s="5"/>
       <c r="BT54" s="5"/>
     </row>
-    <row r="55" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B55" s="238"/>
+    <row r="55" spans="2:72" ht="13.8">
+      <c r="B55" s="251"/>
       <c r="C55" s="13" t="s">
         <v>441</v>
       </c>
@@ -63811,8 +67093,8 @@
       <c r="BS55" s="5"/>
       <c r="BT55" s="5"/>
     </row>
-    <row r="56" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B56" s="238"/>
+    <row r="56" spans="2:72" ht="13.8">
+      <c r="B56" s="251"/>
       <c r="C56" s="13" t="s">
         <v>490</v>
       </c>
@@ -63976,8 +67258,8 @@
       <c r="BS56" s="3"/>
       <c r="BT56" s="3"/>
     </row>
-    <row r="57" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B57" s="238"/>
+    <row r="57" spans="2:72" ht="13.8">
+      <c r="B57" s="251"/>
       <c r="C57" s="56" t="s">
         <v>491</v>
       </c>
@@ -64143,8 +67425,8 @@
       <c r="BS57" s="2"/>
       <c r="BT57" s="2"/>
     </row>
-    <row r="58" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B58" s="238"/>
+    <row r="58" spans="2:72" ht="13.8">
+      <c r="B58" s="251"/>
       <c r="C58" s="13" t="s">
         <v>444</v>
       </c>
@@ -64308,8 +67590,8 @@
       <c r="BS58" s="7"/>
       <c r="BT58" s="7"/>
     </row>
-    <row r="59" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B59" s="238"/>
+    <row r="59" spans="2:72" ht="13.8">
+      <c r="B59" s="251"/>
       <c r="C59" s="13" t="s">
         <v>445</v>
       </c>
@@ -64475,8 +67757,8 @@
       <c r="BS59" s="5"/>
       <c r="BT59" s="5"/>
     </row>
-    <row r="60" spans="2:72" x14ac:dyDescent="0.4">
-      <c r="B60" s="238"/>
+    <row r="60" spans="2:72">
+      <c r="B60" s="251"/>
       <c r="C60" s="54" t="s">
         <v>492</v>
       </c>
@@ -64642,8 +67924,8 @@
       <c r="BS60" s="12"/>
       <c r="BT60" s="12"/>
     </row>
-    <row r="61" spans="2:72" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B61" s="239" t="s">
+    <row r="61" spans="2:72" ht="14.05" customHeight="1">
+      <c r="B61" s="252" t="s">
         <v>342</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -64809,8 +68091,8 @@
       <c r="BS61" s="9"/>
       <c r="BT61" s="9"/>
     </row>
-    <row r="62" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B62" s="239"/>
+    <row r="62" spans="2:72" ht="13.8">
+      <c r="B62" s="252"/>
       <c r="C62" s="13" t="s">
         <v>446</v>
       </c>
@@ -64976,8 +68258,8 @@
       <c r="BS62" s="9"/>
       <c r="BT62" s="9"/>
     </row>
-    <row r="63" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B63" s="239"/>
+    <row r="63" spans="2:72" ht="13.8">
+      <c r="B63" s="252"/>
       <c r="C63" s="13" t="s">
         <v>447</v>
       </c>
@@ -65143,8 +68425,8 @@
       <c r="BS63" s="5"/>
       <c r="BT63" s="5"/>
     </row>
-    <row r="64" spans="2:72" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B64" s="239"/>
+    <row r="64" spans="2:72" ht="13.8">
+      <c r="B64" s="252"/>
       <c r="C64" s="13" t="s">
         <v>494</v>
       </c>
@@ -65310,8 +68592,8 @@
       <c r="BS64" s="2"/>
       <c r="BT64" s="2"/>
     </row>
-    <row r="65" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B65" s="239"/>
+    <row r="65" spans="2:16" ht="13.8">
+      <c r="B65" s="252"/>
       <c r="C65" s="54" t="s">
         <v>495</v>
       </c>
@@ -65327,8 +68609,8 @@
       <c r="O65" s="5"/>
       <c r="P65" s="5"/>
     </row>
-    <row r="66" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B66" s="239"/>
+    <row r="66" spans="2:16" ht="13.8">
+      <c r="B66" s="252"/>
       <c r="C66" s="54" t="s">
         <v>496</v>
       </c>
@@ -65346,8 +68628,8 @@
       <c r="O66" s="5"/>
       <c r="P66" s="5"/>
     </row>
-    <row r="67" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B67" s="239"/>
+    <row r="67" spans="2:16" ht="13.8">
+      <c r="B67" s="252"/>
       <c r="C67" s="13" t="s">
         <v>497</v>
       </c>
@@ -65365,8 +68647,8 @@
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B68" s="229" t="s">
+    <row r="68" spans="2:16">
+      <c r="B68" s="242" t="s">
         <v>185</v>
       </c>
       <c r="C68" s="15" t="s">
@@ -65375,24 +68657,24 @@
       <c r="D68" s="29"/>
       <c r="L68" s="105"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B69" s="229"/>
+    <row r="69" spans="2:16">
+      <c r="B69" s="242"/>
       <c r="C69" s="15" t="s">
         <v>449</v>
       </c>
       <c r="D69" s="29"/>
       <c r="K69" s="12"/>
     </row>
-    <row r="70" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B70" s="229"/>
+    <row r="70" spans="2:16" ht="13.8">
+      <c r="B70" s="242"/>
       <c r="C70" s="15" t="s">
         <v>450</v>
       </c>
       <c r="D70" s="29"/>
       <c r="G70" s="2"/>
     </row>
-    <row r="71" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B71" s="229"/>
+    <row r="71" spans="2:16" ht="13.8">
+      <c r="B71" s="242"/>
       <c r="C71" s="15" t="s">
         <v>498</v>
       </c>
@@ -65403,8 +68685,8 @@
       <c r="K71" s="105"/>
       <c r="L71" s="105"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B72" s="230"/>
+    <row r="72" spans="2:16">
+      <c r="B72" s="243"/>
       <c r="C72" s="16" t="s">
         <v>499</v>
       </c>
@@ -65416,7 +68698,7 @@
       <c r="K72" s="105"/>
       <c r="L72" s="105"/>
     </row>
-    <row r="73" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:16" ht="13.8">
       <c r="F73" s="105"/>
       <c r="G73" s="38"/>
       <c r="H73" s="105"/>
@@ -65424,14 +68706,14 @@
       <c r="K73" s="105"/>
       <c r="L73" s="105"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:16">
       <c r="F74" s="105"/>
       <c r="G74" s="42"/>
       <c r="H74" s="105"/>
       <c r="K74" s="105"/>
       <c r="L74" s="105"/>
     </row>
-    <row r="75" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:16" ht="13.8">
       <c r="F75" s="105"/>
       <c r="G75" s="38"/>
       <c r="H75" s="105"/>
@@ -65439,7 +68721,7 @@
       <c r="K75" s="105"/>
       <c r="L75" s="105"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:16">
       <c r="F76" s="105"/>
       <c r="G76" s="42"/>
       <c r="H76" s="105"/>
@@ -65447,14 +68729,14 @@
       <c r="K76" s="105"/>
       <c r="L76" s="105"/>
     </row>
-    <row r="77" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:16" ht="13.8">
       <c r="F77" s="105"/>
       <c r="G77" s="38"/>
       <c r="H77" s="105"/>
       <c r="K77" s="105"/>
       <c r="L77" s="105"/>
     </row>
-    <row r="78" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:16" ht="13.8">
       <c r="F78" s="105"/>
       <c r="G78" s="38"/>
       <c r="H78" s="105"/>
@@ -65462,7 +68744,7 @@
       <c r="K78" s="105"/>
       <c r="L78" s="105"/>
     </row>
-    <row r="79" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:16" ht="13.8">
       <c r="F79" s="105"/>
       <c r="G79" s="38"/>
       <c r="H79" s="105"/>
@@ -65470,7 +68752,7 @@
       <c r="K79" s="105"/>
       <c r="L79" s="105"/>
     </row>
-    <row r="80" spans="2:16" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:16" ht="13.8">
       <c r="F80" s="105"/>
       <c r="G80" s="38"/>
       <c r="H80" s="105"/>
@@ -65478,7 +68760,7 @@
       <c r="K80" s="105"/>
       <c r="L80" s="105"/>
     </row>
-    <row r="81" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="81" spans="6:12" ht="13.8">
       <c r="F81" s="105"/>
       <c r="G81" s="38"/>
       <c r="H81" s="105"/>
@@ -65486,35 +68768,35 @@
       <c r="K81" s="105"/>
       <c r="L81" s="105"/>
     </row>
-    <row r="82" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="82" spans="6:12" ht="13.8">
       <c r="F82" s="105"/>
       <c r="G82" s="38"/>
       <c r="H82" s="105"/>
       <c r="K82" s="105"/>
       <c r="L82" s="105"/>
     </row>
-    <row r="83" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="83" spans="6:12" ht="13.8">
       <c r="F83" s="105"/>
       <c r="G83" s="38"/>
       <c r="H83" s="105"/>
       <c r="K83" s="105"/>
       <c r="L83" s="105"/>
     </row>
-    <row r="84" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="84" spans="6:12" ht="13.8">
       <c r="F84" s="105"/>
       <c r="G84" s="38"/>
       <c r="H84" s="105"/>
       <c r="K84" s="105"/>
       <c r="L84" s="105"/>
     </row>
-    <row r="85" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="85" spans="6:12" ht="13.8">
       <c r="F85" s="105"/>
       <c r="G85" s="38"/>
       <c r="H85" s="105"/>
       <c r="K85" s="105"/>
       <c r="L85" s="105"/>
     </row>
-    <row r="86" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="86" spans="6:12" ht="13.8">
       <c r="F86" s="105"/>
       <c r="G86" s="38"/>
       <c r="H86" s="105"/>
@@ -65522,7 +68804,7 @@
       <c r="K86" s="105"/>
       <c r="L86" s="105"/>
     </row>
-    <row r="87" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="87" spans="6:12" ht="13.8">
       <c r="F87" s="105"/>
       <c r="G87" s="38"/>
       <c r="H87" s="105"/>
@@ -65530,7 +68812,7 @@
       <c r="K87" s="105"/>
       <c r="L87" s="105"/>
     </row>
-    <row r="88" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="88" spans="6:12" ht="13.8">
       <c r="F88" s="105"/>
       <c r="G88" s="38"/>
       <c r="H88" s="105"/>
@@ -65538,7 +68820,7 @@
       <c r="K88" s="105"/>
       <c r="L88" s="105"/>
     </row>
-    <row r="89" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="89" spans="6:12" ht="13.8">
       <c r="F89" s="105"/>
       <c r="G89" s="38"/>
       <c r="H89" s="105"/>
@@ -65546,7 +68828,7 @@
       <c r="K89" s="105"/>
       <c r="L89" s="105"/>
     </row>
-    <row r="90" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="90" spans="6:12" ht="13.8">
       <c r="F90" s="105"/>
       <c r="G90" s="38"/>
       <c r="H90" s="105"/>
@@ -65554,7 +68836,7 @@
       <c r="K90" s="105"/>
       <c r="L90" s="105"/>
     </row>
-    <row r="91" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="91" spans="6:12" ht="13.8">
       <c r="F91" s="105"/>
       <c r="G91" s="38"/>
       <c r="H91" s="105"/>
@@ -65562,7 +68844,7 @@
       <c r="K91" s="105"/>
       <c r="L91" s="105"/>
     </row>
-    <row r="92" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="92" spans="6:12" ht="13.8">
       <c r="F92" s="105"/>
       <c r="G92" s="38"/>
       <c r="H92" s="105"/>
@@ -65570,7 +68852,7 @@
       <c r="K92" s="105"/>
       <c r="L92" s="105"/>
     </row>
-    <row r="93" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="93" spans="6:12" ht="13.8">
       <c r="F93" s="105"/>
       <c r="G93" s="38"/>
       <c r="H93" s="105"/>
@@ -65578,7 +68860,7 @@
       <c r="K93" s="105"/>
       <c r="L93" s="105"/>
     </row>
-    <row r="94" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="94" spans="6:12" ht="13.8">
       <c r="F94" s="105"/>
       <c r="G94" s="38"/>
       <c r="H94" s="105"/>
@@ -65586,7 +68868,7 @@
       <c r="K94" s="105"/>
       <c r="L94" s="105"/>
     </row>
-    <row r="95" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="95" spans="6:12" ht="13.8">
       <c r="F95" s="105"/>
       <c r="G95" s="2"/>
       <c r="H95" s="105"/>
@@ -65594,7 +68876,7 @@
       <c r="K95" s="105"/>
       <c r="L95" s="105"/>
     </row>
-    <row r="96" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="96" spans="6:12" ht="13.8">
       <c r="F96" s="105"/>
       <c r="G96" s="2"/>
       <c r="H96" s="105"/>
@@ -65602,7 +68884,7 @@
       <c r="K96" s="105"/>
       <c r="L96" s="105"/>
     </row>
-    <row r="97" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="97" spans="6:12" ht="13.8">
       <c r="F97" s="105"/>
       <c r="G97" s="2"/>
       <c r="H97" s="105"/>
@@ -65610,7 +68892,7 @@
       <c r="K97" s="105"/>
       <c r="L97" s="105"/>
     </row>
-    <row r="98" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="98" spans="6:12" ht="13.8">
       <c r="F98" s="105"/>
       <c r="G98" s="2"/>
       <c r="H98" s="105"/>
@@ -65618,7 +68900,7 @@
       <c r="K98" s="105"/>
       <c r="L98" s="105"/>
     </row>
-    <row r="99" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="99" spans="6:12" ht="13.8">
       <c r="F99" s="105"/>
       <c r="G99" s="2"/>
       <c r="H99" s="105"/>
@@ -65626,7 +68908,7 @@
       <c r="K99" s="105"/>
       <c r="L99" s="105"/>
     </row>
-    <row r="100" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="100" spans="6:12" ht="13.8">
       <c r="F100" s="105"/>
       <c r="G100" s="2"/>
       <c r="H100" s="105"/>
@@ -65634,7 +68916,7 @@
       <c r="K100" s="105"/>
       <c r="L100" s="105"/>
     </row>
-    <row r="101" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="101" spans="6:12" ht="13.8">
       <c r="F101" s="105"/>
       <c r="G101" s="2"/>
       <c r="H101" s="105"/>
@@ -65642,7 +68924,7 @@
       <c r="K101" s="105"/>
       <c r="L101" s="105"/>
     </row>
-    <row r="102" spans="6:12" x14ac:dyDescent="0.4">
+    <row r="102" spans="6:12">
       <c r="F102" s="105"/>
       <c r="G102" s="12"/>
       <c r="H102" s="105"/>
@@ -65650,7 +68932,7 @@
       <c r="K102" s="105"/>
       <c r="L102" s="105"/>
     </row>
-    <row r="103" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="103" spans="6:12" ht="13.8">
       <c r="F103" s="105"/>
       <c r="G103" s="2"/>
       <c r="H103" s="105"/>
@@ -65658,7 +68940,7 @@
       <c r="K103" s="105"/>
       <c r="L103" s="105"/>
     </row>
-    <row r="104" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="104" spans="6:12" ht="13.8">
       <c r="F104" s="105"/>
       <c r="G104" s="2"/>
       <c r="H104" s="105"/>
@@ -65666,7 +68948,7 @@
       <c r="K104" s="105"/>
       <c r="L104" s="105"/>
     </row>
-    <row r="105" spans="6:12" x14ac:dyDescent="0.4">
+    <row r="105" spans="6:12">
       <c r="F105" s="105"/>
       <c r="G105" s="12"/>
       <c r="H105" s="105"/>
@@ -65674,7 +68956,7 @@
       <c r="K105" s="105"/>
       <c r="L105" s="105"/>
     </row>
-    <row r="106" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="106" spans="6:12" ht="13.8">
       <c r="F106" s="105"/>
       <c r="G106" s="8"/>
       <c r="H106" s="105"/>
@@ -65682,7 +68964,7 @@
       <c r="K106" s="105"/>
       <c r="L106" s="105"/>
     </row>
-    <row r="107" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="107" spans="6:12" ht="13.8">
       <c r="F107" s="105"/>
       <c r="G107" s="8"/>
       <c r="H107" s="105"/>
@@ -65690,7 +68972,7 @@
       <c r="K107" s="105"/>
       <c r="L107" s="105"/>
     </row>
-    <row r="108" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="108" spans="6:12" ht="13.8">
       <c r="F108" s="105"/>
       <c r="G108" s="2"/>
       <c r="H108" s="105"/>
@@ -65698,7 +68980,7 @@
       <c r="K108" s="105"/>
       <c r="L108" s="105"/>
     </row>
-    <row r="109" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="109" spans="6:12" ht="13.8">
       <c r="F109" s="105"/>
       <c r="G109" s="2"/>
       <c r="H109" s="105"/>
@@ -65706,7 +68988,7 @@
       <c r="K109" s="105"/>
       <c r="L109" s="105"/>
     </row>
-    <row r="110" spans="6:12" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="110" spans="6:12" ht="13.8">
       <c r="F110" s="105"/>
       <c r="G110" s="2"/>
       <c r="H110" s="105"/>
@@ -65780,7 +69062,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AA72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3"/>
   <cols>
     <col min="2" max="2" width="11.5546875" style="105"/>
     <col min="3" max="3" width="21.44140625" style="105" bestFit="1" customWidth="1"/>
@@ -65809,7 +69091,7 @@
     <col min="27" max="27" width="35.77734375" style="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:27">
       <c r="E1" s="105" t="s">
         <v>694</v>
       </c>
@@ -65880,7 +69162,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:27" ht="13.8">
       <c r="B2" s="34" t="s">
         <v>183</v>
       </c>
@@ -65897,7 +69179,7 @@
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
     </row>
-    <row r="3" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:27">
       <c r="B3" s="58"/>
       <c r="C3" s="17" t="s">
         <v>181</v>
@@ -65975,8 +69257,8 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B4" s="231" t="s">
+    <row r="4" spans="2:27">
+      <c r="B4" s="244" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="55" t="s">
@@ -66055,8 +69337,8 @@
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="232"/>
+    <row r="5" spans="2:27" ht="13.8">
+      <c r="B5" s="245"/>
       <c r="C5" s="54" t="s">
         <v>456</v>
       </c>
@@ -66133,7 +69415,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:27" ht="13.8">
       <c r="B6" s="59"/>
       <c r="C6" s="54" t="s">
         <v>457</v>
@@ -66209,8 +69491,8 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B7" s="233" t="s">
+    <row r="7" spans="2:27">
+      <c r="B7" s="246" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="54" t="s">
@@ -66287,8 +69569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B8" s="233"/>
+    <row r="8" spans="2:27" ht="13.8">
+      <c r="B8" s="246"/>
       <c r="C8" s="54" t="s">
         <v>458</v>
       </c>
@@ -66365,8 +69647,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="233"/>
+    <row r="9" spans="2:27" ht="13.8">
+      <c r="B9" s="246"/>
       <c r="C9" s="54" t="s">
         <v>459</v>
       </c>
@@ -66443,8 +69725,8 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="10" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B10" s="233"/>
+    <row r="10" spans="2:27" ht="13.8">
+      <c r="B10" s="246"/>
       <c r="C10" s="54" t="s">
         <v>460</v>
       </c>
@@ -66521,8 +69803,8 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="11" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B11" s="234" t="s">
+    <row r="11" spans="2:27" ht="13.8">
+      <c r="B11" s="247" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="55" t="s">
@@ -66599,8 +69881,8 @@
         <v>779</v>
       </c>
     </row>
-    <row r="12" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B12" s="235"/>
+    <row r="12" spans="2:27" ht="13.8">
+      <c r="B12" s="248"/>
       <c r="C12" s="56" t="s">
         <v>427</v>
       </c>
@@ -66675,8 +69957,8 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B13" s="235"/>
+    <row r="13" spans="2:27" ht="13.8">
+      <c r="B13" s="248"/>
       <c r="C13" s="56" t="s">
         <v>428</v>
       </c>
@@ -66751,8 +70033,8 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="235"/>
+    <row r="14" spans="2:27" ht="13.8">
+      <c r="B14" s="248"/>
       <c r="C14" s="56" t="s">
         <v>429</v>
       </c>
@@ -66827,8 +70109,8 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="235"/>
+    <row r="15" spans="2:27" ht="13.8">
+      <c r="B15" s="248"/>
       <c r="C15" s="56" t="s">
         <v>430</v>
       </c>
@@ -66903,8 +70185,8 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="16" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="235"/>
+    <row r="16" spans="2:27" ht="13.8">
+      <c r="B16" s="248"/>
       <c r="C16" s="56" t="s">
         <v>431</v>
       </c>
@@ -66979,8 +70261,8 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="17" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B17" s="235"/>
+    <row r="17" spans="2:27" ht="13.8">
+      <c r="B17" s="248"/>
       <c r="C17" s="56" t="s">
         <v>432</v>
       </c>
@@ -67055,8 +70337,8 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B18" s="235"/>
+    <row r="18" spans="2:27" ht="13.8">
+      <c r="B18" s="248"/>
       <c r="C18" s="56" t="s">
         <v>433</v>
       </c>
@@ -67131,8 +70413,8 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="19" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B19" s="235"/>
+    <row r="19" spans="2:27" ht="13.8">
+      <c r="B19" s="248"/>
       <c r="C19" s="56" t="s">
         <v>434</v>
       </c>
@@ -67207,8 +70489,8 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B20" s="235"/>
+    <row r="20" spans="2:27" ht="13.8">
+      <c r="B20" s="248"/>
       <c r="C20" s="56" t="s">
         <v>435</v>
       </c>
@@ -67283,8 +70565,8 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="21" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B21" s="236" t="s">
+    <row r="21" spans="2:27" ht="13.8">
+      <c r="B21" s="249" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="56" t="s">
@@ -67361,8 +70643,8 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="22" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B22" s="236"/>
+    <row r="22" spans="2:27" ht="13.8">
+      <c r="B22" s="249"/>
       <c r="C22" s="56" t="s">
         <v>437</v>
       </c>
@@ -67439,8 +70721,8 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="23" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B23" s="236"/>
+    <row r="23" spans="2:27" ht="13.8">
+      <c r="B23" s="249"/>
       <c r="C23" s="55" t="s">
         <v>461</v>
       </c>
@@ -67517,8 +70799,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B24" s="236"/>
+    <row r="24" spans="2:27">
+      <c r="B24" s="249"/>
       <c r="C24" s="55" t="s">
         <v>462</v>
       </c>
@@ -67595,8 +70877,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:27" ht="14.1" x14ac:dyDescent="0.5">
-      <c r="B25" s="236"/>
+    <row r="25" spans="2:27" ht="14.1">
+      <c r="B25" s="249"/>
       <c r="C25" s="56" t="s">
         <v>438</v>
       </c>
@@ -67671,8 +70953,8 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="26" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B26" s="237" t="s">
+    <row r="26" spans="2:27" ht="13.8">
+      <c r="B26" s="250" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="55" t="s">
@@ -67751,8 +71033,8 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="27" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B27" s="237"/>
+    <row r="27" spans="2:27" ht="13.8">
+      <c r="B27" s="250"/>
       <c r="C27" s="55" t="s">
         <v>464</v>
       </c>
@@ -67829,8 +71111,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B28" s="237"/>
+    <row r="28" spans="2:27" ht="13.8">
+      <c r="B28" s="250"/>
       <c r="C28" s="55" t="s">
         <v>465</v>
       </c>
@@ -67905,8 +71187,8 @@
         <v>702</v>
       </c>
     </row>
-    <row r="29" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B29" s="237"/>
+    <row r="29" spans="2:27" ht="13.8">
+      <c r="B29" s="250"/>
       <c r="C29" s="55" t="s">
         <v>466</v>
       </c>
@@ -67981,8 +71263,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B30" s="237"/>
+    <row r="30" spans="2:27" ht="13.8">
+      <c r="B30" s="250"/>
       <c r="C30" s="55" t="s">
         <v>467</v>
       </c>
@@ -68057,8 +71339,8 @@
         <v>698</v>
       </c>
     </row>
-    <row r="31" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B31" s="237"/>
+    <row r="31" spans="2:27" ht="13.8">
+      <c r="B31" s="250"/>
       <c r="C31" s="55" t="s">
         <v>468</v>
       </c>
@@ -68133,8 +71415,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B32" s="237"/>
+    <row r="32" spans="2:27" ht="13.8">
+      <c r="B32" s="250"/>
       <c r="C32" s="55" t="s">
         <v>469</v>
       </c>
@@ -68209,8 +71491,8 @@
         <v>697</v>
       </c>
     </row>
-    <row r="33" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B33" s="237"/>
+    <row r="33" spans="2:27" ht="13.8">
+      <c r="B33" s="250"/>
       <c r="C33" s="55" t="s">
         <v>470</v>
       </c>
@@ -68285,8 +71567,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B34" s="237"/>
+    <row r="34" spans="2:27" ht="13.8">
+      <c r="B34" s="250"/>
       <c r="C34" s="55" t="s">
         <v>471</v>
       </c>
@@ -68361,8 +71643,8 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="35" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B35" s="237"/>
+    <row r="35" spans="2:27" ht="13.8">
+      <c r="B35" s="250"/>
       <c r="C35" s="55" t="s">
         <v>472</v>
       </c>
@@ -68437,8 +71719,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B36" s="237"/>
+    <row r="36" spans="2:27" ht="13.8">
+      <c r="B36" s="250"/>
       <c r="C36" s="55" t="s">
         <v>473</v>
       </c>
@@ -68513,8 +71795,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B37" s="237"/>
+    <row r="37" spans="2:27" ht="13.8">
+      <c r="B37" s="250"/>
       <c r="C37" s="55" t="s">
         <v>474</v>
       </c>
@@ -68589,8 +71871,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B38" s="237"/>
+    <row r="38" spans="2:27" ht="13.8">
+      <c r="B38" s="250"/>
       <c r="C38" s="55" t="s">
         <v>475</v>
       </c>
@@ -68665,8 +71947,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B39" s="237"/>
+    <row r="39" spans="2:27" ht="13.8">
+      <c r="B39" s="250"/>
       <c r="C39" s="55" t="s">
         <v>476</v>
       </c>
@@ -68741,8 +72023,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B40" s="237"/>
+    <row r="40" spans="2:27" ht="13.8">
+      <c r="B40" s="250"/>
       <c r="C40" s="55" t="s">
         <v>477</v>
       </c>
@@ -68817,8 +72099,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B41" s="237"/>
+    <row r="41" spans="2:27" ht="13.8">
+      <c r="B41" s="250"/>
       <c r="C41" s="55" t="s">
         <v>478</v>
       </c>
@@ -68893,8 +72175,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B42" s="237"/>
+    <row r="42" spans="2:27" ht="13.8">
+      <c r="B42" s="250"/>
       <c r="C42" s="55" t="s">
         <v>479</v>
       </c>
@@ -68969,8 +72251,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B43" s="237"/>
+    <row r="43" spans="2:27" ht="13.8">
+      <c r="B43" s="250"/>
       <c r="C43" s="55" t="s">
         <v>480</v>
       </c>
@@ -69045,8 +72327,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B44" s="237"/>
+    <row r="44" spans="2:27" ht="13.8">
+      <c r="B44" s="250"/>
       <c r="C44" s="55" t="s">
         <v>481</v>
       </c>
@@ -69121,8 +72403,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B45" s="237"/>
+    <row r="45" spans="2:27" ht="13.8">
+      <c r="B45" s="250"/>
       <c r="C45" s="55" t="s">
         <v>482</v>
       </c>
@@ -69197,8 +72479,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B46" s="237"/>
+    <row r="46" spans="2:27" ht="13.8">
+      <c r="B46" s="250"/>
       <c r="C46" s="55" t="s">
         <v>483</v>
       </c>
@@ -69273,8 +72555,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B47" s="237"/>
+    <row r="47" spans="2:27" ht="13.8">
+      <c r="B47" s="250"/>
       <c r="C47" s="55" t="s">
         <v>484</v>
       </c>
@@ -69349,8 +72631,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B48" s="237"/>
+    <row r="48" spans="2:27" ht="13.8">
+      <c r="B48" s="250"/>
       <c r="C48" s="55" t="s">
         <v>485</v>
       </c>
@@ -69425,8 +72707,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B49" s="237"/>
+    <row r="49" spans="2:27" ht="13.8">
+      <c r="B49" s="250"/>
       <c r="C49" s="55" t="s">
         <v>486</v>
       </c>
@@ -69501,8 +72783,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B50" s="237"/>
+    <row r="50" spans="2:27" ht="13.8">
+      <c r="B50" s="250"/>
       <c r="C50" s="55" t="s">
         <v>487</v>
       </c>
@@ -69579,8 +72861,8 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="51" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B51" s="237"/>
+    <row r="51" spans="2:27" ht="13.8">
+      <c r="B51" s="250"/>
       <c r="C51" s="55" t="s">
         <v>488</v>
       </c>
@@ -69657,8 +72939,8 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="52" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B52" s="237"/>
+    <row r="52" spans="2:27" ht="13.8">
+      <c r="B52" s="250"/>
       <c r="C52" s="55" t="s">
         <v>489</v>
       </c>
@@ -69735,8 +73017,8 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B53" s="238" t="s">
+    <row r="53" spans="2:27">
+      <c r="B53" s="251" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="54" t="s">
@@ -69815,8 +73097,8 @@
         <v>860</v>
       </c>
     </row>
-    <row r="54" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B54" s="238"/>
+    <row r="54" spans="2:27" ht="13.8">
+      <c r="B54" s="251"/>
       <c r="C54" s="54" t="s">
         <v>440</v>
       </c>
@@ -69893,8 +73175,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B55" s="238"/>
+    <row r="55" spans="2:27" ht="13.8">
+      <c r="B55" s="251"/>
       <c r="C55" s="13" t="s">
         <v>441</v>
       </c>
@@ -69971,8 +73253,8 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="56" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B56" s="238"/>
+    <row r="56" spans="2:27" ht="13.8">
+      <c r="B56" s="251"/>
       <c r="C56" s="13" t="s">
         <v>490</v>
       </c>
@@ -70047,8 +73329,8 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="57" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B57" s="238"/>
+    <row r="57" spans="2:27" ht="13.8">
+      <c r="B57" s="251"/>
       <c r="C57" s="56" t="s">
         <v>491</v>
       </c>
@@ -70125,8 +73407,8 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B58" s="238"/>
+    <row r="58" spans="2:27">
+      <c r="B58" s="251"/>
       <c r="C58" s="13" t="s">
         <v>444</v>
       </c>
@@ -70201,8 +73483,8 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="59" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B59" s="238"/>
+    <row r="59" spans="2:27" ht="13.8">
+      <c r="B59" s="251"/>
       <c r="C59" s="13" t="s">
         <v>445</v>
       </c>
@@ -70279,8 +73561,8 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B60" s="238"/>
+    <row r="60" spans="2:27">
+      <c r="B60" s="251"/>
       <c r="C60" s="54" t="s">
         <v>492</v>
       </c>
@@ -70357,8 +73639,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B61" s="239" t="s">
+    <row r="61" spans="2:27" ht="13.8">
+      <c r="B61" s="252" t="s">
         <v>342</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -70435,8 +73717,8 @@
         <v>43629</v>
       </c>
     </row>
-    <row r="62" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B62" s="239"/>
+    <row r="62" spans="2:27" ht="13.8">
+      <c r="B62" s="252"/>
       <c r="C62" s="13" t="s">
         <v>446</v>
       </c>
@@ -70513,8 +73795,8 @@
         <v>43629</v>
       </c>
     </row>
-    <row r="63" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B63" s="239"/>
+    <row r="63" spans="2:27" ht="13.8">
+      <c r="B63" s="252"/>
       <c r="C63" s="13" t="s">
         <v>447</v>
       </c>
@@ -70591,8 +73873,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B64" s="239"/>
+    <row r="64" spans="2:27" ht="13.8">
+      <c r="B64" s="252"/>
       <c r="C64" s="13" t="s">
         <v>494</v>
       </c>
@@ -70669,8 +73951,8 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="65" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B65" s="239"/>
+    <row r="65" spans="2:27" ht="13.8">
+      <c r="B65" s="252"/>
       <c r="C65" s="54" t="s">
         <v>495</v>
       </c>
@@ -70699,8 +73981,8 @@
       <c r="Z65" s="5"/>
       <c r="AA65" s="5"/>
     </row>
-    <row r="66" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B66" s="239"/>
+    <row r="66" spans="2:27" ht="13.8">
+      <c r="B66" s="252"/>
       <c r="C66" s="54" t="s">
         <v>496</v>
       </c>
@@ -70729,8 +74011,8 @@
       <c r="Z66" s="5"/>
       <c r="AA66" s="5"/>
     </row>
-    <row r="67" spans="2:27" ht="13.8" x14ac:dyDescent="0.45">
-      <c r="B67" s="239"/>
+    <row r="67" spans="2:27" ht="13.8">
+      <c r="B67" s="252"/>
       <c r="C67" s="13" t="s">
         <v>497</v>
       </c>
@@ -70759,8 +74041,8 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B68" s="229" t="s">
+    <row r="68" spans="2:27">
+      <c r="B68" s="242" t="s">
         <v>185</v>
       </c>
       <c r="C68" s="15" t="s">
@@ -70780,8 +74062,8 @@
       <c r="P68" s="105"/>
       <c r="Q68" s="105"/>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B69" s="229"/>
+    <row r="69" spans="2:27">
+      <c r="B69" s="242"/>
       <c r="C69" s="15" t="s">
         <v>449</v>
       </c>
@@ -70799,8 +74081,8 @@
       <c r="P69" s="105"/>
       <c r="Q69" s="105"/>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B70" s="229"/>
+    <row r="70" spans="2:27">
+      <c r="B70" s="242"/>
       <c r="C70" s="15" t="s">
         <v>450</v>
       </c>
@@ -70818,8 +74100,8 @@
       <c r="P70" s="105"/>
       <c r="Q70" s="105"/>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B71" s="229"/>
+    <row r="71" spans="2:27">
+      <c r="B71" s="242"/>
       <c r="C71" s="15" t="s">
         <v>498</v>
       </c>
@@ -70837,8 +74119,8 @@
       <c r="P71" s="105"/>
       <c r="Q71" s="105"/>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.4">
-      <c r="B72" s="230"/>
+    <row r="72" spans="2:27">
+      <c r="B72" s="243"/>
       <c r="C72" s="16" t="s">
         <v>499</v>
       </c>

--- a/IEDC_content_fill/IEDC_Prototype_Datasets_Batch1_Upload_MASTER.xlsx
+++ b/IEDC_content_fill/IEDC_Prototype_Datasets_Batch1_Upload_MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stefan Pauliuk\FILES\ARBEIT\PROJECTS\Database\IE_DataCommons\IEDC_software\IEDC_content_fill\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8580A113-F1BB-4BED-85CC-6465981B7080}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC1FDE8-0C64-4F6C-89E9-91FF19A88D34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20448" windowHeight="9684" tabRatio="603" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17611" uniqueCount="3863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18081" uniqueCount="4009">
   <si>
     <t>Description</t>
   </si>
@@ -11620,7 +11620,445 @@
     <t>table in supplement 1-s2.0-S2352550924000885-mmc2.xlsx, sheet "Material intensity of EV"</t>
   </si>
   <si>
-    <t>4 Sankey flow datasets</t>
+    <t>1_F_Economy_wide_MFA_Global_EU27_2005_HAAS</t>
+  </si>
+  <si>
+    <t>six aggregate economic processes: extraction, energy use, material use, final use (use phase), waste management, and recycling</t>
+  </si>
+  <si>
+    <t>all materials and commodities</t>
+  </si>
+  <si>
+    <t>4 MFA resource groups: biomass, fossil fuels, metals and metal ores, non-metallic minerals</t>
+  </si>
+  <si>
+    <t>Global and EU27</t>
+  </si>
+  <si>
+    <t>one global aggregate value and one aggregate value for the EU27 in 2005.</t>
+  </si>
+  <si>
+    <t>Sankey flow data for the economy-wide material flows by broad material category world-wide and in the EU in 2005, by HAAS et al. (2015).</t>
+  </si>
+  <si>
+    <t>economy-wide MFA; material flow accounting; circular economy; material cycle; Sankey; EU; EU27</t>
+  </si>
+  <si>
+    <t>Data are reported twice. Once on each material-type layer separately and once on the 'dry mass' layer to allow for drawing a Sankey that shows all layers at once. The waste rock flow (0.12 Gt/yr in the EU) is a separate flow and not included in the 'use as material' flow. This is a correction compared to the original Sankey diagram, which is why the material use and addition to stocks flows are 0.12 Gt/yr (EU27) smaller than originally reported.</t>
+  </si>
+  <si>
+    <t>Flow of all commodities from use as material to use phase in EU27 in 2005 measured as dry mass, all materials of all materials is 3.33 Gt/yr.</t>
+  </si>
+  <si>
+    <t>Willi HAAS</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/jiec.12244</t>
+  </si>
+  <si>
+    <t>spreadsheet, supplied by author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbers supplied by main author and converted to IEDC templates. </t>
+  </si>
+  <si>
+    <t>SANKEY_LINK</t>
+  </si>
+  <si>
+    <t>1_F_Economy_wide_MFA_EU28_2014_MAYER</t>
+  </si>
+  <si>
+    <t>EU28</t>
+  </si>
+  <si>
+    <t>Aggregate value</t>
+  </si>
+  <si>
+    <t>Sankey flow data for the economy-wide material flows by broad material category in the EU in 2014, by MAYER et al. (2019).</t>
+  </si>
+  <si>
+    <t>economy-wide MFA; material flow accounting; circular economy; material cycle; Sankey; EU; EU28</t>
+  </si>
+  <si>
+    <t>Converted to IEDC template by reformatting data from sheet "All results" in jiec12809-sup-0002-suppmat.xlsx. Flow names were divided into material/commodity, origin process, and destination process. Data are reported twice. Once on each material-type layer separately and once on the 'dry mass' layer to allow for drawing a Sankey that shows all layers at once.</t>
+  </si>
+  <si>
+    <t>Flow of all commodities from use as material to use phase in EU28 in 2014 measured as mass, metal ores and metals of metal ores and metals is 178.39 Mt/yr.</t>
+  </si>
+  <si>
+    <t>Andreas MAYER</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/action/downloadSupplement?doi=10.1111%2Fjiec.12809&amp;file=jiec12809-sup-0002-SuppMat.xlsx</t>
+  </si>
+  <si>
+    <t>supplementary spreadsheet jiec12809-sup-0002-suppmat.xlsx</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/jiec.12809</t>
+  </si>
+  <si>
+    <t>Converted to IEDC template by reformatting data from sheet "All results" in jiec12809-sup-0002-suppmat.xlsx. Flow names were divided into material/commodity, origin process, and destination process.</t>
+  </si>
+  <si>
+    <t>1_F_Sand_Gravel_MFA_Global_184Countries_ZHUANG_2025</t>
+  </si>
+  <si>
+    <t>1_F_Watari_2025_SteelSankeys_30Regions</t>
+  </si>
+  <si>
+    <t>all stages of the steel cycle</t>
+  </si>
+  <si>
+    <t>aggregate industrial and consumer stages of the steel cycle</t>
+  </si>
+  <si>
+    <t>all broad iron-containing commodity groups in the steel cycle</t>
+  </si>
+  <si>
+    <t>from iron ore via steel, manufactured goods, end-of-life goods, to scrap</t>
+  </si>
+  <si>
+    <t>iron/steel</t>
+  </si>
+  <si>
+    <t>Individual values for 30 main producing countries</t>
+  </si>
+  <si>
+    <t>2000-2019</t>
+  </si>
+  <si>
+    <t>Sankey flow data for the steel cycle Sankeys by Takuma Watari et al. (2025)</t>
+  </si>
+  <si>
+    <t>steel; material cycle; Sankey; global</t>
+  </si>
+  <si>
+    <t>Numbers supplied by main author and converted to IEDC templates. For some processes, the balancing difference is indicated as 'mass balance gap'. The IEDC team did not check the mass balance of the reported data.</t>
+  </si>
+  <si>
+    <t>Flow of iron ore from mining to market for iron ore in China in 2000 measured as mass of iron is 63.42 Mt/yr.</t>
+  </si>
+  <si>
+    <t>https://github.com/takumawatari/steel-flows-sankey/tree/main/data</t>
+  </si>
+  <si>
+    <t>spreadsheet</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.resconrec.2025.108363</t>
+  </si>
+  <si>
+    <t>entry needs to be created first!</t>
+  </si>
+  <si>
+    <t>FutuRaM</t>
+  </si>
+  <si>
+    <t>https://futuram.eu/</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.6094/UNIFR/269286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FutuRaM developed the Secondary Raw Materials knowledge base on the availability and recoverability of secondary raw materials (2RMs) within the European Union, with a special focus on critical raw materials (CRMs). </t>
+  </si>
+  <si>
+    <t>raw materials; secondary raw materials; urban mining; critical raw materials; circular economy;</t>
+  </si>
+  <si>
+    <t>FutuRaM_Database</t>
+  </si>
+  <si>
+    <t>Socio_metabolic_inequality_SMI</t>
+  </si>
+  <si>
+    <t>SMI_Lorenz_Curves</t>
+  </si>
+  <si>
+    <t>SMI_Indicators</t>
+  </si>
+  <si>
+    <t>Database of Lorenz curves, Gini cofficients, and other indicators for socio-metabolic inequality (inequality in service, stocks, and flows across society)</t>
+  </si>
+  <si>
+    <t>Inequality; socio-metabolic inequality; socio-economic metabolism; Lorenz curve; Gini index; Gini coefficient;</t>
+  </si>
+  <si>
+    <t>stocks, flows, and intensive product data (3_xxx)</t>
+  </si>
+  <si>
+    <t>in-use stocks, flows, and product material composition</t>
+  </si>
+  <si>
+    <t>many different authors and data suppliers, see the individual datasets</t>
+  </si>
+  <si>
+    <t>FutuRaM project consortium, see the individual datasets</t>
+  </si>
+  <si>
+    <t>Compilation of datasets from different sources</t>
+  </si>
+  <si>
+    <t>mass, units of products</t>
+  </si>
+  <si>
+    <t>main material cycle stages</t>
+  </si>
+  <si>
+    <t>manufacturing, use phase, waste management and recycling</t>
+  </si>
+  <si>
+    <t>major material uses</t>
+  </si>
+  <si>
+    <t>batteries, buildings, mining waste, slag and ashes, vehicles, WEEE, wind turbines</t>
+  </si>
+  <si>
+    <t>major material groups</t>
+  </si>
+  <si>
+    <t>Single country values</t>
+  </si>
+  <si>
+    <t>aluminium, iron, magnesium, steel, copper, concrete, plastics, zinc, critical raw materials</t>
+  </si>
+  <si>
+    <t>single year values, historic data til 2024 and future scenarios til 2050</t>
+  </si>
+  <si>
+    <t>stocks, flows, and intensive product properties</t>
+  </si>
+  <si>
+    <t>Lorenz curves for in-use stocks and flows (at scale) and normalized Lorenz curves (3_LC)</t>
+  </si>
+  <si>
+    <t>aggregrage processes</t>
+  </si>
+  <si>
+    <t>use phase (stock-flow-service nexus), entire economy</t>
+  </si>
+  <si>
+    <t>depends on dataset</t>
+  </si>
+  <si>
+    <t>all countries and regions, global</t>
+  </si>
+  <si>
+    <t>Different intensive and extensive indicators</t>
+  </si>
+  <si>
+    <t>Different intensive and extensive variables</t>
+  </si>
+  <si>
+    <t>Database of Lorenz curves for socio-metabolic inequality (inequality in service, stocks, and flows across society)</t>
+  </si>
+  <si>
+    <t>Database of Gini cofficients and other indicators for socio-metabolic inequality (inequality in service, stocks, and flows across society)</t>
+  </si>
+  <si>
+    <t>Inequality; socio-metabolic inequality; socio-economic metabolism; Lorenz curve;</t>
+  </si>
+  <si>
+    <t>Inequality; socio-metabolic inequality; socio-economic metabolism; Gini index; Gini coefficient;</t>
+  </si>
+  <si>
+    <t>see the individual datasets</t>
+  </si>
+  <si>
+    <t>POSTED</t>
+  </si>
+  <si>
+    <t>FutuRaM_Logos.png</t>
+  </si>
+  <si>
+    <t>Gini_DLS_1.png</t>
+  </si>
+  <si>
+    <t>https://github.com/PhilippVerpoort/posted</t>
+  </si>
+  <si>
+    <t>POSTED is a public database of techno-economic data on energy and climate-mitigation technologies and a framework for consistent handling of this database.</t>
+  </si>
+  <si>
+    <t>process data; industrial processes; industry technology; climate change mitigation; techno-economic data; unit process inventories; CAPEX; OPEX;</t>
+  </si>
+  <si>
+    <t>POSTED_industry_data</t>
+  </si>
+  <si>
+    <t>Philipp VERPOORT</t>
+  </si>
+  <si>
+    <t>POSTED_PIK_logo-light.png</t>
+  </si>
+  <si>
+    <t>Different intensive variables</t>
+  </si>
+  <si>
+    <t>unit process inventories, economic indicators (CAPEX, OPEX), lifetime</t>
+  </si>
+  <si>
+    <t>major industrial technologies</t>
+  </si>
+  <si>
+    <t>ca. 30 individual technologies and technology groups from the energy-intensive industry, such as cement production, steel production, or steam cracking</t>
+  </si>
+  <si>
+    <t>energy carriers</t>
+  </si>
+  <si>
+    <t>Aggregate values without explicit regional scope</t>
+  </si>
+  <si>
+    <t>single year values, depending on individual datasets</t>
+  </si>
+  <si>
+    <t>iTEM_Open_Transport_Data</t>
+  </si>
+  <si>
+    <t>https://transportenergy.org/open-data/</t>
+  </si>
+  <si>
+    <t>iTEM (International Transport Energy Modelling), a global group of researchers, is working to create a common, public, “best available” database of historical transport statistics for baseline calibration of models, through a transparent, scientific process.</t>
+  </si>
+  <si>
+    <t>transport; energy; vehicles; service; emissions;</t>
+  </si>
+  <si>
+    <t>iTEM team</t>
+  </si>
+  <si>
+    <t>iTEM_Logo.png</t>
+  </si>
+  <si>
+    <t>ca. 1970-2025-2100</t>
+  </si>
+  <si>
+    <t>single year values, historic data til 2024 and future scenarios til 2100</t>
+  </si>
+  <si>
+    <t>all major passenger and freight vehicle groups</t>
+  </si>
+  <si>
+    <t>use phase, manufacturing</t>
+  </si>
+  <si>
+    <t>in-use stocks, flows, service flows, emissions</t>
+  </si>
+  <si>
+    <t>6_MIP_Gini_Socio_Metabolic_Inequality_Collection</t>
+  </si>
+  <si>
+    <t>v1.0_April_2026</t>
+  </si>
+  <si>
+    <t>different focus processes, depends on the different data sources</t>
+  </si>
+  <si>
+    <t>depends on the different data sources</t>
+  </si>
+  <si>
+    <t>ca. 1970-2026</t>
+  </si>
+  <si>
+    <t>Compilation of Gini coeficients / Gini indices for socio-metabolic services, stocks, and flows, from different publications, see the comments for the individual entries in the dataset</t>
+  </si>
+  <si>
+    <t>Gini coefficient; Gini index; inequality; in-use stock; social metabolism; socio-metabolic inequality; provisioning systems; energy; materials; service;</t>
+  </si>
+  <si>
+    <t>Compilation of data from different publications, see the comments for the individual entries in the dataset</t>
+  </si>
+  <si>
+    <t>Value(E,I,g,p,r,t)</t>
+  </si>
+  <si>
+    <t>Gini index of final energy in/into/of/for residential buildings in use phase in Global in 2016 is 0.5838.</t>
+  </si>
+  <si>
+    <t>see the comments for the individual entries in the dataset</t>
+  </si>
+  <si>
+    <t>1_LCF_Final_Energy_Buildings_Vehicles_Global_PAULIUK_2024</t>
+  </si>
+  <si>
+    <t>Lorenz curve, non-normalized, flow</t>
+  </si>
+  <si>
+    <t>final energy for buildings and vehicles</t>
+  </si>
+  <si>
+    <t>all energy carriers for residential buildings, non-residential buildings, and passenger vehicles</t>
+  </si>
+  <si>
+    <t>one aggregate Lorenz curve</t>
+  </si>
+  <si>
+    <t>Lorenz curve for final energy for residential buildings, non-residential buildings, and passenger vehicles, based on region- and country-level data for 21 world regions</t>
+  </si>
+  <si>
+    <t>Value(g,r,t,o,d,1)</t>
+  </si>
+  <si>
+    <t>Lorenz curve, non-normalized, flow for final energy, all energy carriers from markets for final energy, all energy carriers to use phase - residential buildings in Global in 2016 for cumulative population share 0.79 is 16833561.656 TJ/yr.</t>
+  </si>
+  <si>
+    <t>[Data type] for [Aspect 1] from [Aspect 4] to [Aspect 5] in [Aspect 2] in [Aspect 3] for cumulative population share [Aspect 6] is [Value].</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ecolecon.2024.108161</t>
+  </si>
+  <si>
+    <t>Lorenz curve; inequality; use phase; social metabolism; socio-metabolic inequality; provisioning systems; final energy; buildings; passenger vehicles;</t>
+  </si>
+  <si>
+    <t>Data extracted with Python script from supplementary data file Pauliuk_DLS_LorenzCurve_2024_SI.xlsx, sheet "pav_reb_nrb_Global_Fig4", converted to 1_LCF, and converted to IEDC templates. Cumulative population value rounded to two digits "0.xx".</t>
+  </si>
+  <si>
+    <t>Data extracted with Python script from supplementary data file, converted to 1_LCF, and converted to IEDC templates.</t>
+  </si>
+  <si>
+    <t>2_LCS_In_use_stock_Buildings_Vehicles_Global_PAULIUK_2024</t>
+  </si>
+  <si>
+    <t>Lorenz curve, non-normalized, stock</t>
+  </si>
+  <si>
+    <t>buildings and vehicles</t>
+  </si>
+  <si>
+    <t>residential buildings, non-residential buildings, and passenger vehicles</t>
+  </si>
+  <si>
+    <t>Lorenz curve for in-use stock of residential buildings, non-residential buildings, and passenger vehicles, based on region- and country-level data for 21 world regions</t>
+  </si>
+  <si>
+    <t>Lorenz curve; inequality; in-use stock; social metabolism; socio-metabolic inequality; provisioning systems; buildings; passenger vehicles;</t>
+  </si>
+  <si>
+    <t>Data extracted with Python script from supplementary data file Pauliuk_DLS_LorenzCurve_2024_SI.xlsx, sheet "pav_reb_nrb_Global_Fig4", converted to 2_LCS, and converted to IEDC templates. Cumulative population value rounded to two digits "0.xx".</t>
+  </si>
+  <si>
+    <t>Value(g,r,t,p,1)</t>
+  </si>
+  <si>
+    <t>Lorenz curve, non-normalized, stock for passenger vehicles in use phase - passenger vehicles in Global in 2015 for cumulative population share 0.32 is 39.495 million.</t>
+  </si>
+  <si>
+    <t>[Data type] for [Aspect 1] in [Aspect 4] in [Aspect 2] in [Aspect 3] for cumulative population share [Aspect 5] is [Value].</t>
+  </si>
+  <si>
+    <t>Data extracted with Python script from supplementary data file, converted to 2_LCS, and converted to IEDC templates.</t>
+  </si>
+  <si>
+    <t>needs correction, check IEDC-floweaver-Sankey workflow first</t>
+  </si>
+  <si>
+    <t>may need correction, check IEDC-floweaver-Sankey workflow first</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -11768,7 +12206,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11844,12 +12282,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -12036,7 +12468,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12532,7 +12964,14 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -12542,8 +12981,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC9A4E4"/>
       <color rgb="FFD3B5E9"/>
-      <color rgb="FFC9A4E4"/>
     </mruColors>
   </colors>
   <extLst>
@@ -12820,7 +13259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M32"/>
+  <dimension ref="B1:V32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
@@ -12828,16 +13267,24 @@
     <col min="5" max="5" width="28.38671875" customWidth="1"/>
     <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="14" max="15" width="10.6640625" style="105"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.4">
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B2" s="34" t="s">
         <v>186</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B3" s="32"/>
       <c r="C3" s="31" t="s">
         <v>181</v>
@@ -12872,8 +13319,20 @@
       <c r="M3" s="39" t="s">
         <v>3448</v>
       </c>
+      <c r="N3" s="39" t="s">
+        <v>3912</v>
+      </c>
+      <c r="O3" s="39" t="s">
+        <v>3960</v>
+      </c>
+      <c r="P3" s="39" t="s">
+        <v>3906</v>
+      </c>
+      <c r="Q3" s="39" t="s">
+        <v>3944</v>
+      </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B4" s="244" t="s">
         <v>2</v>
       </c>
@@ -12910,8 +13369,21 @@
       <c r="M4" s="140">
         <v>9</v>
       </c>
+      <c r="N4" s="140">
+        <v>10</v>
+      </c>
+      <c r="O4" s="140">
+        <v>11</v>
+      </c>
+      <c r="P4" s="140">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="140">
+        <v>13</v>
+      </c>
+      <c r="R4" s="105"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B5" s="244"/>
       <c r="C5" s="26" t="s">
         <v>422</v>
@@ -12946,8 +13418,20 @@
       <c r="M5" s="118" t="s">
         <v>3448</v>
       </c>
+      <c r="N5" s="118" t="s">
+        <v>3912</v>
+      </c>
+      <c r="O5" s="118" t="s">
+        <v>3960</v>
+      </c>
+      <c r="P5" s="118" t="s">
+        <v>3906</v>
+      </c>
+      <c r="Q5" s="118" t="s">
+        <v>3944</v>
+      </c>
     </row>
-    <row r="6" spans="2:13" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:22" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="245" t="s">
         <v>6</v>
       </c>
@@ -12964,8 +13448,12 @@
       <c r="K6" s="121"/>
       <c r="L6" s="121"/>
       <c r="M6" s="121"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B7" s="245"/>
       <c r="C7" s="26" t="s">
         <v>424</v>
@@ -12980,8 +13468,12 @@
       <c r="K7" s="121"/>
       <c r="L7" s="121"/>
       <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="121"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B8" s="245"/>
       <c r="C8" s="26" t="s">
         <v>425</v>
@@ -12996,8 +13488,12 @@
       <c r="K8" s="121"/>
       <c r="L8" s="121"/>
       <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B9" s="245"/>
       <c r="C9" s="28" t="s">
         <v>426</v>
@@ -13012,8 +13508,12 @@
       <c r="K9" s="121"/>
       <c r="L9" s="121"/>
       <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B10" s="245"/>
       <c r="C10" s="27" t="s">
         <v>427</v>
@@ -13028,8 +13528,12 @@
       <c r="K10" s="121"/>
       <c r="L10" s="121"/>
       <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="121"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B11" s="245"/>
       <c r="C11" s="27" t="s">
         <v>428</v>
@@ -13044,8 +13548,12 @@
       <c r="K11" s="121"/>
       <c r="L11" s="121"/>
       <c r="M11" s="121"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="121"/>
+      <c r="Q11" s="121"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B12" s="245"/>
       <c r="C12" s="27" t="s">
         <v>429</v>
@@ -13060,8 +13568,12 @@
       <c r="K12" s="121"/>
       <c r="L12" s="121"/>
       <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="121"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B13" s="245"/>
       <c r="C13" s="27" t="s">
         <v>430</v>
@@ -13076,8 +13588,12 @@
       <c r="K13" s="121"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="121"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B14" s="245"/>
       <c r="C14" s="27" t="s">
         <v>431</v>
@@ -13092,8 +13608,12 @@
       <c r="K14" s="121"/>
       <c r="L14" s="121"/>
       <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="121"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B15" s="245"/>
       <c r="C15" s="27" t="s">
         <v>432</v>
@@ -13108,8 +13628,12 @@
       <c r="K15" s="121"/>
       <c r="L15" s="121"/>
       <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B16" s="245"/>
       <c r="C16" s="27" t="s">
         <v>433</v>
@@ -13124,8 +13648,12 @@
       <c r="K16" s="121"/>
       <c r="L16" s="121"/>
       <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="121"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B17" s="245"/>
       <c r="C17" s="27" t="s">
         <v>434</v>
@@ -13140,8 +13668,12 @@
       <c r="K17" s="121"/>
       <c r="L17" s="121"/>
       <c r="M17" s="121"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B18" s="245"/>
       <c r="C18" s="27" t="s">
         <v>435</v>
@@ -13156,8 +13688,12 @@
       <c r="K18" s="121"/>
       <c r="L18" s="121"/>
       <c r="M18" s="121"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="121"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B19" s="246" t="s">
         <v>0</v>
       </c>
@@ -13190,8 +13726,20 @@
       <c r="M19" s="118" t="s">
         <v>3450</v>
       </c>
+      <c r="N19" s="118" t="s">
+        <v>3915</v>
+      </c>
+      <c r="O19" s="118" t="s">
+        <v>3962</v>
+      </c>
+      <c r="P19" s="118" t="s">
+        <v>3909</v>
+      </c>
+      <c r="Q19" s="118" t="s">
+        <v>3948</v>
+      </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B20" s="246"/>
       <c r="C20" s="27" t="s">
         <v>437</v>
@@ -13226,8 +13774,20 @@
       <c r="M20" s="118" t="s">
         <v>3451</v>
       </c>
+      <c r="N20" s="118" t="s">
+        <v>3916</v>
+      </c>
+      <c r="O20" s="118" t="s">
+        <v>3963</v>
+      </c>
+      <c r="P20" s="118" t="s">
+        <v>3910</v>
+      </c>
+      <c r="Q20" s="118" t="s">
+        <v>3949</v>
+      </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B21" s="246"/>
       <c r="C21" s="27" t="s">
         <v>438</v>
@@ -13258,8 +13818,12 @@
       <c r="M21" s="118" t="s">
         <v>3452</v>
       </c>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118"/>
     </row>
-    <row r="22" spans="2:13" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:17" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="247" t="s">
         <v>8</v>
       </c>
@@ -13294,8 +13858,20 @@
       <c r="M22" s="121" t="s">
         <v>860</v>
       </c>
+      <c r="N22" s="118" t="s">
+        <v>861</v>
+      </c>
+      <c r="O22" s="118" t="s">
+        <v>861</v>
+      </c>
+      <c r="P22" s="118" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q22" s="118" t="s">
+        <v>861</v>
+      </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B23" s="247"/>
       <c r="C23" s="26" t="s">
         <v>440</v>
@@ -13310,8 +13886,12 @@
       <c r="K23" s="121"/>
       <c r="L23" s="121"/>
       <c r="M23" s="121"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="121"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B24" s="247"/>
       <c r="C24" s="25" t="s">
         <v>441</v>
@@ -13326,8 +13906,12 @@
       <c r="K24" s="121"/>
       <c r="L24" s="121"/>
       <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="121"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B25" s="247"/>
       <c r="C25" s="25" t="s">
         <v>443</v>
@@ -13358,8 +13942,20 @@
       <c r="M25" s="170" t="s">
         <v>3463</v>
       </c>
+      <c r="N25" s="170" t="s">
+        <v>3908</v>
+      </c>
+      <c r="O25" s="170" t="s">
+        <v>3961</v>
+      </c>
+      <c r="P25" s="170" t="s">
+        <v>3907</v>
+      </c>
+      <c r="Q25" s="170" t="s">
+        <v>3947</v>
+      </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B26" s="247"/>
       <c r="C26" s="25" t="s">
         <v>444</v>
@@ -13376,8 +13972,12 @@
       <c r="K26" s="121"/>
       <c r="L26" s="121"/>
       <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="121"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B27" s="247"/>
       <c r="C27" s="25" t="s">
         <v>445</v>
@@ -13392,8 +13992,12 @@
       <c r="K27" s="121"/>
       <c r="L27" s="121"/>
       <c r="M27" s="121"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="121"/>
     </row>
-    <row r="28" spans="2:13" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:17" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="248" t="s">
         <v>9</v>
       </c>
@@ -13430,8 +14034,20 @@
       <c r="M28" s="180">
         <v>46020</v>
       </c>
+      <c r="N28" s="180">
+        <v>46031</v>
+      </c>
+      <c r="O28" s="180">
+        <v>46031</v>
+      </c>
+      <c r="P28" s="180">
+        <v>46031</v>
+      </c>
+      <c r="Q28" s="180">
+        <v>46031</v>
+      </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B29" s="248"/>
       <c r="C29" s="25" t="s">
         <v>447</v>
@@ -13466,8 +14082,20 @@
       <c r="M29" s="124" t="s">
         <v>30</v>
       </c>
+      <c r="N29" s="124" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="124" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="264" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q29" s="124" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B30" s="241" t="s">
         <v>185</v>
       </c>
@@ -13484,8 +14112,12 @@
       <c r="K30" s="181"/>
       <c r="L30" s="181"/>
       <c r="M30" s="181"/>
+      <c r="N30" s="181"/>
+      <c r="O30" s="181"/>
+      <c r="P30" s="181"/>
+      <c r="Q30" s="181"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B31" s="242"/>
       <c r="C31" s="108" t="s">
         <v>449</v>
@@ -13500,8 +14132,12 @@
       <c r="K31" s="164"/>
       <c r="L31" s="164"/>
       <c r="M31" s="164"/>
+      <c r="N31" s="164"/>
+      <c r="O31" s="164"/>
+      <c r="P31" s="164"/>
+      <c r="Q31" s="164"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B32" s="243"/>
       <c r="C32" s="109" t="s">
         <v>450</v>
@@ -13516,6 +14152,10 @@
       <c r="K32" s="166"/>
       <c r="L32" s="166"/>
       <c r="M32" s="166"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="166"/>
+      <c r="P32" s="166"/>
+      <c r="Q32" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -13532,7 +14172,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:AJ39"/>
+  <dimension ref="B2:AO39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
@@ -13554,9 +14194,10 @@
     <col min="22" max="22" width="40.71875" customWidth="1"/>
     <col min="23" max="23" width="32.6640625" customWidth="1"/>
     <col min="27" max="27" width="24.44140625" customWidth="1"/>
+    <col min="38" max="38" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B2" s="34" t="s">
         <v>184</v>
       </c>
@@ -13573,7 +14214,7 @@
       <c r="AE2" s="105"/>
       <c r="AF2" s="105"/>
     </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B3" s="32"/>
       <c r="C3" s="17" t="s">
         <v>181</v>
@@ -13677,8 +14318,23 @@
       <c r="AJ3" s="82" t="s">
         <v>3491</v>
       </c>
+      <c r="AK3" s="82" t="s">
+        <v>3911</v>
+      </c>
+      <c r="AL3" s="82" t="s">
+        <v>3913</v>
+      </c>
+      <c r="AM3" s="82" t="s">
+        <v>3914</v>
+      </c>
+      <c r="AN3" s="82" t="s">
+        <v>3950</v>
+      </c>
+      <c r="AO3" s="82" t="s">
+        <v>3960</v>
+      </c>
     </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B4" s="249" t="s">
         <v>2</v>
       </c>
@@ -13784,8 +14440,23 @@
       <c r="AJ4" s="140">
         <v>32</v>
       </c>
+      <c r="AK4" s="140">
+        <v>33</v>
+      </c>
+      <c r="AL4" s="140">
+        <v>34</v>
+      </c>
+      <c r="AM4" s="140">
+        <v>35</v>
+      </c>
+      <c r="AN4" s="140">
+        <v>36</v>
+      </c>
+      <c r="AO4" s="140">
+        <v>37</v>
+      </c>
     </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B5" s="250"/>
       <c r="C5" s="54" t="s">
         <v>452</v>
@@ -13889,8 +14560,23 @@
       <c r="AJ5" s="164" t="s">
         <v>3491</v>
       </c>
+      <c r="AK5" s="164" t="s">
+        <v>3911</v>
+      </c>
+      <c r="AL5" s="164" t="s">
+        <v>3913</v>
+      </c>
+      <c r="AM5" s="164" t="s">
+        <v>3914</v>
+      </c>
+      <c r="AN5" s="164" t="s">
+        <v>3950</v>
+      </c>
+      <c r="AO5" s="164" t="s">
+        <v>3960</v>
+      </c>
     </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B6" s="33"/>
       <c r="C6" s="54" t="s">
         <v>453</v>
@@ -13992,8 +14678,23 @@
       <c r="AJ6" s="164" t="s">
         <v>11</v>
       </c>
+      <c r="AK6" s="164" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL6" s="164" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM6" s="164" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN6" s="164" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO6" s="164" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B7" s="50" t="s">
         <v>3</v>
       </c>
@@ -14097,8 +14798,23 @@
       <c r="AJ7" s="164" t="s">
         <v>11</v>
       </c>
+      <c r="AK7" t="s">
+        <v>3906</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>3912</v>
+      </c>
+      <c r="AM7" s="105" t="s">
+        <v>3912</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>3944</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>3960</v>
+      </c>
     </row>
-    <row r="8" spans="2:36" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:41" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="245" t="s">
         <v>6</v>
       </c>
@@ -14202,8 +14918,23 @@
       <c r="AJ8" s="23" t="s">
         <v>2574</v>
       </c>
+      <c r="AK8" s="23" t="s">
+        <v>3917</v>
+      </c>
+      <c r="AL8" s="23" t="s">
+        <v>3931</v>
+      </c>
+      <c r="AM8" s="23" t="s">
+        <v>3938</v>
+      </c>
+      <c r="AN8" s="23" t="s">
+        <v>3953</v>
+      </c>
+      <c r="AO8" s="23" t="s">
+        <v>3917</v>
+      </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B9" s="245"/>
       <c r="C9" s="54" t="s">
         <v>424</v>
@@ -14305,8 +15036,23 @@
       <c r="AJ9" s="23" t="s">
         <v>3492</v>
       </c>
+      <c r="AK9" s="23" t="s">
+        <v>3918</v>
+      </c>
+      <c r="AL9" s="23" t="s">
+        <v>3932</v>
+      </c>
+      <c r="AM9" s="23" t="s">
+        <v>3937</v>
+      </c>
+      <c r="AN9" s="23" t="s">
+        <v>3954</v>
+      </c>
+      <c r="AO9" s="23" t="s">
+        <v>3970</v>
+      </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B10" s="245"/>
       <c r="C10" s="54" t="s">
         <v>425</v>
@@ -14408,8 +15154,23 @@
       <c r="AJ10" s="23" t="s">
         <v>199</v>
       </c>
+      <c r="AK10" s="23" t="s">
+        <v>3922</v>
+      </c>
+      <c r="AL10" s="23" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AM10" s="23" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AN10" s="23" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AO10" s="23" t="s">
+        <v>1025</v>
+      </c>
     </row>
-    <row r="11" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B11" s="245"/>
       <c r="C11" s="55" t="s">
         <v>426</v>
@@ -14511,8 +15272,23 @@
       <c r="AJ11" s="23" t="s">
         <v>3493</v>
       </c>
+      <c r="AK11" s="23" t="s">
+        <v>3923</v>
+      </c>
+      <c r="AL11" s="23" t="s">
+        <v>3934</v>
+      </c>
+      <c r="AM11" s="23" t="s">
+        <v>3934</v>
+      </c>
+      <c r="AN11" s="23" t="s">
+        <v>782</v>
+      </c>
+      <c r="AO11" s="23" t="s">
+        <v>3969</v>
+      </c>
     </row>
-    <row r="12" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B12" s="245"/>
       <c r="C12" s="56" t="s">
         <v>427</v>
@@ -14614,8 +15390,23 @@
       <c r="AJ12" s="23" t="s">
         <v>3494</v>
       </c>
+      <c r="AK12" s="23" t="s">
+        <v>3924</v>
+      </c>
+      <c r="AL12" s="23" t="s">
+        <v>3933</v>
+      </c>
+      <c r="AM12" s="23" t="s">
+        <v>3933</v>
+      </c>
+      <c r="AN12" s="23" t="s">
+        <v>2274</v>
+      </c>
+      <c r="AO12" s="23" t="s">
+        <v>1995</v>
+      </c>
     </row>
-    <row r="13" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B13" s="245"/>
       <c r="C13" s="56" t="s">
         <v>428</v>
@@ -14717,8 +15508,23 @@
       <c r="AJ13" s="23" t="s">
         <v>3347</v>
       </c>
+      <c r="AK13" s="23" t="s">
+        <v>3925</v>
+      </c>
+      <c r="AL13" s="23" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AM13" s="23" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AN13" s="23" t="s">
+        <v>3955</v>
+      </c>
+      <c r="AO13" s="23" t="s">
+        <v>597</v>
+      </c>
     </row>
-    <row r="14" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B14" s="245"/>
       <c r="C14" s="56" t="s">
         <v>429</v>
@@ -14820,8 +15626,23 @@
       <c r="AJ14" s="23" t="s">
         <v>3495</v>
       </c>
+      <c r="AK14" s="23" t="s">
+        <v>3926</v>
+      </c>
+      <c r="AL14" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AM14" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AN14" s="23" t="s">
+        <v>3956</v>
+      </c>
+      <c r="AO14" s="23" t="s">
+        <v>3968</v>
+      </c>
     </row>
-    <row r="15" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B15" s="245"/>
       <c r="C15" s="56" t="s">
         <v>430</v>
@@ -14923,8 +15744,23 @@
       <c r="AJ15" s="23" t="s">
         <v>3504</v>
       </c>
+      <c r="AK15" s="23" t="s">
+        <v>3927</v>
+      </c>
+      <c r="AL15" s="23" t="s">
+        <v>1679</v>
+      </c>
+      <c r="AM15" s="23" t="s">
+        <v>1679</v>
+      </c>
+      <c r="AN15" s="23" t="s">
+        <v>3957</v>
+      </c>
+      <c r="AO15" s="23" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B16" s="245"/>
       <c r="C16" s="56" t="s">
         <v>431</v>
@@ -15026,8 +15862,23 @@
       <c r="AJ16" s="23" t="s">
         <v>3503</v>
       </c>
+      <c r="AK16" s="23" t="s">
+        <v>3929</v>
+      </c>
+      <c r="AL16" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AM16" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AN16" s="23" t="s">
+        <v>2526</v>
+      </c>
+      <c r="AO16" s="23" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="17" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B17" s="245"/>
       <c r="C17" s="56" t="s">
         <v>432</v>
@@ -15129,8 +15980,23 @@
       <c r="AJ17" s="164" t="s">
         <v>156</v>
       </c>
+      <c r="AK17" s="164" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AL17" s="164" t="s">
+        <v>3936</v>
+      </c>
+      <c r="AM17" s="164" t="s">
+        <v>3936</v>
+      </c>
+      <c r="AN17" s="164" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO17" s="164" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="18" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B18" s="245"/>
       <c r="C18" s="56" t="s">
         <v>433</v>
@@ -15232,8 +16098,23 @@
       <c r="AJ18" s="164" t="s">
         <v>3502</v>
       </c>
+      <c r="AK18" s="164" t="s">
+        <v>3928</v>
+      </c>
+      <c r="AL18" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AM18" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AN18" s="164" t="s">
+        <v>3958</v>
+      </c>
+      <c r="AO18" s="164" t="s">
+        <v>3928</v>
+      </c>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B19" s="245"/>
       <c r="C19" s="56" t="s">
         <v>434</v>
@@ -15335,8 +16216,23 @@
       <c r="AJ19" s="23" t="s">
         <v>3498</v>
       </c>
+      <c r="AK19" s="23" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AL19" s="23" t="s">
+        <v>3046</v>
+      </c>
+      <c r="AM19" s="23" t="s">
+        <v>3046</v>
+      </c>
+      <c r="AN19" s="23" t="s">
+        <v>3511</v>
+      </c>
+      <c r="AO19" s="23" t="s">
+        <v>3966</v>
+      </c>
     </row>
-    <row r="20" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B20" s="245"/>
       <c r="C20" s="56" t="s">
         <v>435</v>
@@ -15438,8 +16334,23 @@
       <c r="AJ20" s="164" t="s">
         <v>3499</v>
       </c>
+      <c r="AK20" s="164" t="s">
+        <v>3930</v>
+      </c>
+      <c r="AL20" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AM20" s="23" t="s">
+        <v>3935</v>
+      </c>
+      <c r="AN20" s="164" t="s">
+        <v>3959</v>
+      </c>
+      <c r="AO20" s="164" t="s">
+        <v>3967</v>
+      </c>
     </row>
-    <row r="21" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B21" s="246" t="s">
         <v>0</v>
       </c>
@@ -15543,8 +16454,23 @@
       <c r="AJ21" s="23" t="s">
         <v>3500</v>
       </c>
+      <c r="AK21" s="23" t="s">
+        <v>3909</v>
+      </c>
+      <c r="AL21" s="23" t="s">
+        <v>3939</v>
+      </c>
+      <c r="AM21" s="23" t="s">
+        <v>3940</v>
+      </c>
+      <c r="AN21" s="23" t="s">
+        <v>3948</v>
+      </c>
+      <c r="AO21" s="23" t="s">
+        <v>3962</v>
+      </c>
     </row>
-    <row r="22" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B22" s="246"/>
       <c r="C22" s="56" t="s">
         <v>437</v>
@@ -15648,8 +16574,23 @@
       <c r="AJ22" s="164" t="s">
         <v>3501</v>
       </c>
+      <c r="AK22" s="164" t="s">
+        <v>3910</v>
+      </c>
+      <c r="AL22" s="164" t="s">
+        <v>3941</v>
+      </c>
+      <c r="AM22" s="164" t="s">
+        <v>3942</v>
+      </c>
+      <c r="AN22" s="164" t="s">
+        <v>3949</v>
+      </c>
+      <c r="AO22" s="164" t="s">
+        <v>3963</v>
+      </c>
     </row>
-    <row r="23" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B23" s="246"/>
       <c r="C23" s="56" t="s">
         <v>454</v>
@@ -15741,8 +16682,23 @@
       <c r="AH23" s="164"/>
       <c r="AI23" s="164"/>
       <c r="AJ23" s="164"/>
+      <c r="AK23" s="164" t="s">
+        <v>3945</v>
+      </c>
+      <c r="AL23" s="164" t="s">
+        <v>3946</v>
+      </c>
+      <c r="AM23" s="164" t="s">
+        <v>3946</v>
+      </c>
+      <c r="AN23" s="164" t="s">
+        <v>3952</v>
+      </c>
+      <c r="AO23" s="164" t="s">
+        <v>3965</v>
+      </c>
     </row>
-    <row r="24" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B24" s="246"/>
       <c r="C24" s="56" t="s">
         <v>438</v>
@@ -15830,8 +16786,17 @@
         <v>3487</v>
       </c>
       <c r="AJ24" s="164"/>
+      <c r="AK24" s="164"/>
+      <c r="AL24" s="164" t="s">
+        <v>3921</v>
+      </c>
+      <c r="AM24" s="164" t="s">
+        <v>3921</v>
+      </c>
+      <c r="AN24" s="164"/>
+      <c r="AO24" s="164"/>
     </row>
-    <row r="25" spans="2:36" ht="13.3" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:41" ht="13.3" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="247" t="s">
         <v>8</v>
       </c>
@@ -15935,8 +16900,23 @@
       <c r="AJ25" s="23" t="s">
         <v>206</v>
       </c>
+      <c r="AK25" s="23" t="s">
+        <v>861</v>
+      </c>
+      <c r="AL25" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM25" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN25" s="23" t="s">
+        <v>861</v>
+      </c>
+      <c r="AO25" s="23" t="s">
+        <v>861</v>
+      </c>
     </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B26" s="247"/>
       <c r="C26" s="54" t="s">
         <v>440</v>
@@ -16038,8 +17018,23 @@
       <c r="AJ26" s="164" t="s">
         <v>3109</v>
       </c>
+      <c r="AK26" s="164" t="s">
+        <v>2651</v>
+      </c>
+      <c r="AL26" s="164" t="s">
+        <v>2651</v>
+      </c>
+      <c r="AM26" s="164" t="s">
+        <v>2651</v>
+      </c>
+      <c r="AN26" s="164" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO26" s="164" t="s">
+        <v>2651</v>
+      </c>
     </row>
-    <row r="27" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B27" s="247"/>
       <c r="C27" s="13" t="s">
         <v>441</v>
@@ -16141,8 +17136,23 @@
       <c r="AJ27" s="164" t="s">
         <v>3497</v>
       </c>
+      <c r="AK27" s="164" t="s">
+        <v>3920</v>
+      </c>
+      <c r="AL27" s="164" t="s">
+        <v>3919</v>
+      </c>
+      <c r="AM27" s="164" t="s">
+        <v>3919</v>
+      </c>
+      <c r="AN27" s="164" t="s">
+        <v>3951</v>
+      </c>
+      <c r="AO27" s="164" t="s">
+        <v>3964</v>
+      </c>
     </row>
-    <row r="28" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B28" s="247"/>
       <c r="C28" s="13" t="s">
         <v>443</v>
@@ -16244,8 +17254,23 @@
       <c r="AJ28" s="179" t="s">
         <v>3496</v>
       </c>
+      <c r="AK28" s="170" t="s">
+        <v>3907</v>
+      </c>
+      <c r="AL28" s="170" t="s">
+        <v>3908</v>
+      </c>
+      <c r="AM28" s="170" t="s">
+        <v>3908</v>
+      </c>
+      <c r="AN28" s="170" t="s">
+        <v>3947</v>
+      </c>
+      <c r="AO28" s="170" t="s">
+        <v>3961</v>
+      </c>
     </row>
-    <row r="29" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B29" s="247"/>
       <c r="C29" s="13" t="s">
         <v>444</v>
@@ -16347,8 +17372,23 @@
       <c r="AJ29" s="179" t="s">
         <v>3496</v>
       </c>
+      <c r="AK29" s="170" t="s">
+        <v>3907</v>
+      </c>
+      <c r="AL29" s="179" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AM29" s="179" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AN29" s="170" t="s">
+        <v>3947</v>
+      </c>
+      <c r="AO29" s="170" t="s">
+        <v>3961</v>
+      </c>
     </row>
-    <row r="30" spans="2:36" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:41" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B30" s="247"/>
       <c r="C30" s="13" t="s">
         <v>445</v>
@@ -16450,8 +17490,23 @@
       <c r="AJ30" s="179" t="s">
         <v>3496</v>
       </c>
+      <c r="AK30" s="170" t="s">
+        <v>3907</v>
+      </c>
+      <c r="AL30" s="179" t="s">
+        <v>3943</v>
+      </c>
+      <c r="AM30" s="179" t="s">
+        <v>3943</v>
+      </c>
+      <c r="AN30" s="170" t="s">
+        <v>3947</v>
+      </c>
+      <c r="AO30" s="170" t="s">
+        <v>3961</v>
+      </c>
     </row>
-    <row r="31" spans="2:36" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:41" ht="13.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="248" t="s">
         <v>9</v>
       </c>
@@ -16557,8 +17612,23 @@
       <c r="AJ31" s="161">
         <v>46024</v>
       </c>
+      <c r="AK31" s="161">
+        <v>46031</v>
+      </c>
+      <c r="AL31" s="161">
+        <v>46031</v>
+      </c>
+      <c r="AM31" s="161">
+        <v>46031</v>
+      </c>
+      <c r="AN31" s="161">
+        <v>46031</v>
+      </c>
+      <c r="AO31" s="161">
+        <v>46031</v>
+      </c>
     </row>
-    <row r="32" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B32" s="251"/>
       <c r="C32" s="86" t="s">
         <v>447</v>
@@ -16662,8 +17732,23 @@
       <c r="AJ32" s="164" t="s">
         <v>30</v>
       </c>
+      <c r="AK32" s="164" t="s">
+        <v>30</v>
+      </c>
+      <c r="AL32" s="164" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM32" s="164" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN32" s="164" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO32" s="164" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B33" s="241" t="s">
         <v>185</v>
       </c>
@@ -16703,8 +17788,13 @@
       <c r="AH33" s="164"/>
       <c r="AI33" s="164"/>
       <c r="AJ33" s="164"/>
+      <c r="AK33" s="164"/>
+      <c r="AL33" s="164"/>
+      <c r="AM33" s="164"/>
+      <c r="AN33" s="164"/>
+      <c r="AO33" s="164"/>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B34" s="242"/>
       <c r="C34" s="15" t="s">
         <v>449</v>
@@ -16742,8 +17832,13 @@
       <c r="AH34" s="164"/>
       <c r="AI34" s="164"/>
       <c r="AJ34" s="164"/>
+      <c r="AK34" s="164"/>
+      <c r="AL34" s="164"/>
+      <c r="AM34" s="164"/>
+      <c r="AN34" s="164"/>
+      <c r="AO34" s="164"/>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.4">
       <c r="B35" s="243"/>
       <c r="C35" s="16" t="s">
         <v>450</v>
@@ -16781,11 +17876,16 @@
       <c r="AH35" s="166"/>
       <c r="AI35" s="166"/>
       <c r="AJ35" s="166"/>
+      <c r="AK35" s="166"/>
+      <c r="AL35" s="166"/>
+      <c r="AM35" s="166"/>
+      <c r="AN35" s="166"/>
+      <c r="AO35" s="166"/>
     </row>
-    <row r="36" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:41" x14ac:dyDescent="0.4">
       <c r="W36" s="105"/>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.4">
       <c r="I39" s="12"/>
     </row>
   </sheetData>
@@ -16870,7 +17970,7 @@
     <col min="239" max="16384" width="11.5546875" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:257" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:260" x14ac:dyDescent="0.4">
       <c r="C1" s="73" t="s">
         <v>269</v>
       </c>
@@ -17431,20 +18531,17 @@
       <c r="IQ1" s="174"/>
       <c r="IR1" s="174"/>
       <c r="IS1" s="174"/>
-      <c r="IT1" s="263" t="s">
-        <v>3862</v>
-      </c>
-      <c r="IU1" s="263" t="s">
-        <v>3862</v>
-      </c>
-      <c r="IV1" s="263" t="s">
-        <v>3862</v>
-      </c>
-      <c r="IW1" s="263" t="s">
-        <v>3862</v>
-      </c>
+      <c r="IT1" s="174"/>
+      <c r="IU1" s="174"/>
+      <c r="IV1" s="174"/>
+      <c r="IW1" s="233" t="s">
+        <v>3905</v>
+      </c>
+      <c r="IX1" s="174"/>
+      <c r="IY1" s="174"/>
+      <c r="IZ1" s="174"/>
     </row>
-    <row r="2" spans="1:257" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:260" ht="13.8" x14ac:dyDescent="0.45">
       <c r="B2" s="34" t="s">
         <v>183</v>
       </c>
@@ -17938,6 +19035,9 @@
       <c r="HR2" s="154" t="s">
         <v>3846</v>
       </c>
+      <c r="HS2" s="233" t="s">
+        <v>3845</v>
+      </c>
       <c r="HT2" s="154" t="s">
         <v>3846</v>
       </c>
@@ -17953,6 +19053,9 @@
       <c r="HX2" s="154" t="s">
         <v>3846</v>
       </c>
+      <c r="HY2" s="233" t="s">
+        <v>3845</v>
+      </c>
       <c r="HZ2" s="154" t="s">
         <v>3846</v>
       </c>
@@ -18013,12 +19116,29 @@
       <c r="IS2" s="154" t="s">
         <v>3846</v>
       </c>
-      <c r="IT2" s="263"/>
-      <c r="IU2" s="263"/>
-      <c r="IV2" s="263"/>
-      <c r="IW2" s="263"/>
+      <c r="IT2" s="154" t="s">
+        <v>3846</v>
+      </c>
+      <c r="IU2" s="154" t="s">
+        <v>3846</v>
+      </c>
+      <c r="IV2" s="154" t="s">
+        <v>3846</v>
+      </c>
+      <c r="IW2" s="233" t="s">
+        <v>3845</v>
+      </c>
+      <c r="IX2" s="233" t="s">
+        <v>3845</v>
+      </c>
+      <c r="IY2" s="154" t="s">
+        <v>3846</v>
+      </c>
+      <c r="IZ2" s="154" t="s">
+        <v>3846</v>
+      </c>
     </row>
-    <row r="3" spans="1:257" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:260" x14ac:dyDescent="0.4">
       <c r="B3" s="58"/>
       <c r="C3" s="17" t="s">
         <v>181</v>
@@ -18272,15 +19392,24 @@
       <c r="DT3" s="105"/>
       <c r="HN3" s="105"/>
       <c r="HO3" s="105"/>
-      <c r="HS3" s="233" t="s">
-        <v>3845</v>
-      </c>
       <c r="HT3" s="105"/>
-      <c r="HY3" s="233" t="s">
-        <v>3845</v>
+      <c r="IK3" s="265" t="s">
+        <v>4006</v>
+      </c>
+      <c r="IT3" s="233" t="s">
+        <v>4007</v>
+      </c>
+      <c r="IU3" s="233" t="s">
+        <v>4007</v>
+      </c>
+      <c r="IV3" s="233" t="s">
+        <v>4007</v>
+      </c>
+      <c r="IW3" s="266" t="s">
+        <v>4008</v>
       </c>
     </row>
-    <row r="4" spans="1:257" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:260" x14ac:dyDescent="0.4">
       <c r="A4" s="41">
         <v>1</v>
       </c>
@@ -18538,7 +19667,7 @@
       <c r="DS4" s="105"/>
       <c r="DT4" s="105"/>
     </row>
-    <row r="5" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="41">
         <v>2</v>
       </c>
@@ -19296,8 +20425,29 @@
       <c r="IS5" s="115" t="s">
         <v>3847</v>
       </c>
+      <c r="IT5" s="115" t="s">
+        <v>3862</v>
+      </c>
+      <c r="IU5" s="115" t="s">
+        <v>3877</v>
+      </c>
+      <c r="IV5" s="115" t="s">
+        <v>3890</v>
+      </c>
+      <c r="IW5" s="105" t="s">
+        <v>3889</v>
+      </c>
+      <c r="IX5" s="115" t="s">
+        <v>3971</v>
+      </c>
+      <c r="IY5" s="115" t="s">
+        <v>3982</v>
+      </c>
+      <c r="IZ5" s="115" t="s">
+        <v>3995</v>
+      </c>
     </row>
-    <row r="6" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="92">
         <v>3</v>
       </c>
@@ -20053,8 +21203,26 @@
       <c r="IS6" s="115" t="s">
         <v>11</v>
       </c>
+      <c r="IT6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX6" s="263" t="s">
+        <v>3972</v>
+      </c>
+      <c r="IY6" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ6" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="92">
         <v>4</v>
       </c>
@@ -20812,8 +21980,26 @@
       <c r="IS7" s="115" t="s">
         <v>845</v>
       </c>
+      <c r="IT7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="IU7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="IV7" s="115" t="s">
+        <v>845</v>
+      </c>
+      <c r="IX7" s="115">
+        <v>35</v>
+      </c>
+      <c r="IY7" s="115">
+        <v>34</v>
+      </c>
+      <c r="IZ7" s="115">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="92">
         <v>5</v>
       </c>
@@ -21571,8 +22757,26 @@
       <c r="IS8" s="115">
         <v>3</v>
       </c>
+      <c r="IT8" s="115">
+        <v>1</v>
+      </c>
+      <c r="IU8" s="115">
+        <v>1</v>
+      </c>
+      <c r="IV8" s="115">
+        <v>1</v>
+      </c>
+      <c r="IX8" s="115">
+        <v>6</v>
+      </c>
+      <c r="IY8" s="115">
+        <v>1</v>
+      </c>
+      <c r="IZ8" s="115">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:257" ht="28.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:260" ht="28.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="92">
         <v>6</v>
       </c>
@@ -22330,8 +23534,26 @@
       <c r="IS9" s="115" t="s">
         <v>846</v>
       </c>
+      <c r="IT9" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="IU9" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="IV9" s="115" t="s">
+        <v>1</v>
+      </c>
+      <c r="IX9" s="115" t="s">
+        <v>1676</v>
+      </c>
+      <c r="IY9" s="115" t="s">
+        <v>3983</v>
+      </c>
+      <c r="IZ9" s="115" t="s">
+        <v>3996</v>
+      </c>
     </row>
-    <row r="10" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="92">
         <v>7</v>
       </c>
@@ -23089,8 +24311,26 @@
       <c r="IS10" s="115" t="s">
         <v>824</v>
       </c>
+      <c r="IT10" s="115" t="s">
+        <v>2007</v>
+      </c>
+      <c r="IU10" s="115" t="s">
+        <v>2007</v>
+      </c>
+      <c r="IV10" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="IX10" s="115" t="s">
+        <v>3613</v>
+      </c>
+      <c r="IY10" s="115" t="s">
+        <v>3018</v>
+      </c>
+      <c r="IZ10" s="115" t="s">
+        <v>1025</v>
+      </c>
     </row>
-    <row r="11" spans="1:257" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:260" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="92">
         <v>8</v>
       </c>
@@ -23848,8 +25088,26 @@
       <c r="IS11" s="115" t="s">
         <v>782</v>
       </c>
+      <c r="IT11" s="115" t="s">
+        <v>1677</v>
+      </c>
+      <c r="IU11" s="115" t="s">
+        <v>1677</v>
+      </c>
+      <c r="IV11" s="115" t="s">
+        <v>3891</v>
+      </c>
+      <c r="IX11" s="115" t="s">
+        <v>1460</v>
+      </c>
+      <c r="IY11" s="115" t="s">
+        <v>782</v>
+      </c>
+      <c r="IZ11" s="115" t="s">
+        <v>782</v>
+      </c>
     </row>
-    <row r="12" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="92">
         <v>9</v>
       </c>
@@ -24605,8 +25863,26 @@
       <c r="IS12" s="115" t="s">
         <v>2274</v>
       </c>
+      <c r="IT12" s="115" t="s">
+        <v>3863</v>
+      </c>
+      <c r="IU12" s="115" t="s">
+        <v>3863</v>
+      </c>
+      <c r="IV12" s="115" t="s">
+        <v>3892</v>
+      </c>
+      <c r="IX12" s="115" t="s">
+        <v>3973</v>
+      </c>
+      <c r="IY12" s="115" t="s">
+        <v>2274</v>
+      </c>
+      <c r="IZ12" s="115" t="s">
+        <v>2274</v>
+      </c>
     </row>
-    <row r="13" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="92">
         <v>10</v>
       </c>
@@ -25362,8 +26638,26 @@
       <c r="IS13" s="115" t="s">
         <v>816</v>
       </c>
+      <c r="IT13" s="115" t="s">
+        <v>3864</v>
+      </c>
+      <c r="IU13" s="115" t="s">
+        <v>3864</v>
+      </c>
+      <c r="IV13" s="115" t="s">
+        <v>3893</v>
+      </c>
+      <c r="IX13" s="115" t="s">
+        <v>3568</v>
+      </c>
+      <c r="IY13" s="115" t="s">
+        <v>3984</v>
+      </c>
+      <c r="IZ13" s="115" t="s">
+        <v>3997</v>
+      </c>
     </row>
-    <row r="14" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="92">
         <v>11</v>
       </c>
@@ -26119,8 +27413,26 @@
       <c r="IS14" s="115" t="s">
         <v>3848</v>
       </c>
+      <c r="IT14" s="115" t="s">
+        <v>3865</v>
+      </c>
+      <c r="IU14" s="115" t="s">
+        <v>3865</v>
+      </c>
+      <c r="IV14" s="115" t="s">
+        <v>3894</v>
+      </c>
+      <c r="IX14" s="115" t="s">
+        <v>3974</v>
+      </c>
+      <c r="IY14" s="115" t="s">
+        <v>3985</v>
+      </c>
+      <c r="IZ14" s="115" t="s">
+        <v>3998</v>
+      </c>
     </row>
-    <row r="15" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="92">
         <v>12</v>
       </c>
@@ -26876,8 +28188,26 @@
       <c r="IS15" s="115" t="s">
         <v>3849</v>
       </c>
+      <c r="IT15" s="115" t="s">
+        <v>3864</v>
+      </c>
+      <c r="IU15" s="115" t="s">
+        <v>3864</v>
+      </c>
+      <c r="IV15" s="115" t="s">
+        <v>3895</v>
+      </c>
+      <c r="IX15" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY15" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ15" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="16" spans="1:257" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="92">
         <v>13</v>
       </c>
@@ -27633,8 +28963,26 @@
       <c r="IS16" s="115" t="s">
         <v>3850</v>
       </c>
+      <c r="IT16" s="115" t="s">
+        <v>3865</v>
+      </c>
+      <c r="IU16" s="115" t="s">
+        <v>3865</v>
+      </c>
+      <c r="IV16" s="115" t="s">
+        <v>1680</v>
+      </c>
+      <c r="IX16" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY16" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ16" s="115" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="17" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="92">
         <v>14</v>
       </c>
@@ -28390,8 +29738,26 @@
       <c r="IS17" s="115" t="s">
         <v>3139</v>
       </c>
+      <c r="IT17" s="115" t="s">
+        <v>3866</v>
+      </c>
+      <c r="IU17" s="115" t="s">
+        <v>3878</v>
+      </c>
+      <c r="IV17" s="115" t="s">
+        <v>19</v>
+      </c>
+      <c r="IX17" s="115" t="s">
+        <v>819</v>
+      </c>
+      <c r="IY17" s="115" t="s">
+        <v>19</v>
+      </c>
+      <c r="IZ17" s="115" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="18" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="92">
         <v>15</v>
       </c>
@@ -29147,8 +30513,26 @@
       <c r="IS18" s="115" t="s">
         <v>3851</v>
       </c>
+      <c r="IT18" s="115" t="s">
+        <v>3867</v>
+      </c>
+      <c r="IU18" s="115" t="s">
+        <v>3879</v>
+      </c>
+      <c r="IV18" s="115" t="s">
+        <v>3896</v>
+      </c>
+      <c r="IX18" s="115" t="s">
+        <v>3974</v>
+      </c>
+      <c r="IY18" s="115" t="s">
+        <v>3986</v>
+      </c>
+      <c r="IZ18" s="115" t="s">
+        <v>3986</v>
+      </c>
     </row>
-    <row r="19" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="92">
         <v>16</v>
       </c>
@@ -29904,8 +31288,26 @@
       <c r="IS19" s="115" t="s">
         <v>3852</v>
       </c>
+      <c r="IT19" s="115">
+        <v>2005</v>
+      </c>
+      <c r="IU19" s="115">
+        <v>2014</v>
+      </c>
+      <c r="IV19" s="115" t="s">
+        <v>3897</v>
+      </c>
+      <c r="IX19" s="115" t="s">
+        <v>3975</v>
+      </c>
+      <c r="IY19" s="115">
+        <v>2016</v>
+      </c>
+      <c r="IZ19" s="115">
+        <v>2015</v>
+      </c>
     </row>
-    <row r="20" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="92">
         <v>17</v>
       </c>
@@ -30661,8 +32063,26 @@
       <c r="IS20" s="115" t="s">
         <v>3853</v>
       </c>
+      <c r="IT20" s="115" t="s">
+        <v>1871</v>
+      </c>
+      <c r="IU20" s="115" t="s">
+        <v>1871</v>
+      </c>
+      <c r="IV20" s="115" t="s">
+        <v>1145</v>
+      </c>
+      <c r="IX20" s="115" t="s">
+        <v>3974</v>
+      </c>
+      <c r="IY20" s="115" t="s">
+        <v>2679</v>
+      </c>
+      <c r="IZ20" s="115" t="s">
+        <v>2679</v>
+      </c>
     </row>
-    <row r="21" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="92">
         <v>18</v>
       </c>
@@ -31414,8 +32834,26 @@
       <c r="IS21" s="115" t="s">
         <v>3854</v>
       </c>
+      <c r="IT21" s="115" t="s">
+        <v>3868</v>
+      </c>
+      <c r="IU21" s="115" t="s">
+        <v>3880</v>
+      </c>
+      <c r="IV21" s="115" t="s">
+        <v>3898</v>
+      </c>
+      <c r="IX21" s="159" t="s">
+        <v>3976</v>
+      </c>
+      <c r="IY21" s="115" t="s">
+        <v>3987</v>
+      </c>
+      <c r="IZ21" s="115" t="s">
+        <v>3999</v>
+      </c>
     </row>
-    <row r="22" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="92">
         <v>19</v>
       </c>
@@ -32173,8 +33611,26 @@
       <c r="IS22" s="115" t="s">
         <v>3855</v>
       </c>
+      <c r="IT22" s="115" t="s">
+        <v>3869</v>
+      </c>
+      <c r="IU22" s="115" t="s">
+        <v>3881</v>
+      </c>
+      <c r="IV22" s="115" t="s">
+        <v>3899</v>
+      </c>
+      <c r="IX22" s="115" t="s">
+        <v>3977</v>
+      </c>
+      <c r="IY22" s="115" t="s">
+        <v>3992</v>
+      </c>
+      <c r="IZ22" s="115" t="s">
+        <v>4000</v>
+      </c>
     </row>
-    <row r="23" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="92">
         <v>20</v>
       </c>
@@ -32932,8 +34388,26 @@
       <c r="IS23" s="115" t="s">
         <v>24</v>
       </c>
+      <c r="IT23" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="IU23" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="IV23" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="IX23" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="IY23" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="IZ23" s="115" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="24" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="92">
         <v>21</v>
       </c>
@@ -33691,8 +35165,26 @@
       <c r="IS24" s="115">
         <v>92</v>
       </c>
+      <c r="IT24" s="159">
+        <v>308</v>
+      </c>
+      <c r="IU24" s="115">
+        <v>192</v>
+      </c>
+      <c r="IV24" s="115">
+        <v>21345</v>
+      </c>
+      <c r="IX24" s="263">
+        <v>6</v>
+      </c>
+      <c r="IY24" s="115">
+        <v>63</v>
+      </c>
+      <c r="IZ24" s="115">
+        <v>63</v>
+      </c>
     </row>
-    <row r="25" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="92">
         <v>22</v>
       </c>
@@ -34443,8 +35935,26 @@
       <c r="IS25" s="159" t="s">
         <v>3856</v>
       </c>
+      <c r="IT25" s="217" t="s">
+        <v>3870</v>
+      </c>
+      <c r="IU25" s="217" t="s">
+        <v>3882</v>
+      </c>
+      <c r="IV25" s="159" t="s">
+        <v>3900</v>
+      </c>
+      <c r="IX25" s="159" t="s">
+        <v>3978</v>
+      </c>
+      <c r="IY25" s="159" t="s">
+        <v>3993</v>
+      </c>
+      <c r="IZ25" s="159" t="s">
+        <v>4001</v>
+      </c>
     </row>
-    <row r="26" spans="1:253" s="68" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:260" s="68" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="92">
         <v>23</v>
       </c>
@@ -35204,8 +36714,26 @@
       <c r="IS26" s="159" t="s">
         <v>698</v>
       </c>
+      <c r="IT26" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="IU26" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="IV26" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="IX26" s="159" t="s">
+        <v>1697</v>
+      </c>
+      <c r="IY26" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="IZ26" s="159" t="s">
+        <v>696</v>
+      </c>
     </row>
-    <row r="27" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="92">
         <v>24</v>
       </c>
@@ -35963,8 +37491,26 @@
       <c r="IS27" s="159">
         <v>2</v>
       </c>
+      <c r="IT27" s="159">
+        <v>7</v>
+      </c>
+      <c r="IU27" s="159">
+        <v>7</v>
+      </c>
+      <c r="IV27" s="159">
+        <v>7</v>
+      </c>
+      <c r="IX27" s="159">
+        <v>28</v>
+      </c>
+      <c r="IY27" s="159">
+        <v>7</v>
+      </c>
+      <c r="IZ27" s="159">
+        <v>7</v>
+      </c>
     </row>
-    <row r="28" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="92">
         <v>25</v>
       </c>
@@ -36720,8 +38266,26 @@
       <c r="IS28" s="159" t="s">
         <v>696</v>
       </c>
+      <c r="IT28" s="159" t="s">
+        <v>1033</v>
+      </c>
+      <c r="IU28" s="159" t="s">
+        <v>1033</v>
+      </c>
+      <c r="IV28" s="159" t="s">
+        <v>1033</v>
+      </c>
+      <c r="IX28" s="159" t="s">
+        <v>1657</v>
+      </c>
+      <c r="IY28" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="IZ28" s="184" t="s">
+        <v>698</v>
+      </c>
     </row>
-    <row r="29" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="92">
         <v>26</v>
       </c>
@@ -37477,8 +39041,26 @@
       <c r="IS29" s="182">
         <v>7</v>
       </c>
+      <c r="IT29" s="159">
+        <v>4</v>
+      </c>
+      <c r="IU29" s="159">
+        <v>4</v>
+      </c>
+      <c r="IV29" s="159">
+        <v>4</v>
+      </c>
+      <c r="IX29" s="184">
+        <v>28</v>
+      </c>
+      <c r="IY29" s="184">
+        <v>2</v>
+      </c>
+      <c r="IZ29" s="184">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="92">
         <v>27</v>
       </c>
@@ -38234,8 +39816,26 @@
       <c r="IS30" s="159" t="s">
         <v>704</v>
       </c>
+      <c r="IT30" s="159" t="s">
+        <v>1034</v>
+      </c>
+      <c r="IU30" s="159" t="s">
+        <v>1034</v>
+      </c>
+      <c r="IV30" s="159" t="s">
+        <v>1034</v>
+      </c>
+      <c r="IX30" s="159" t="s">
+        <v>696</v>
+      </c>
+      <c r="IY30" s="184" t="s">
+        <v>702</v>
+      </c>
+      <c r="IZ30" s="184" t="s">
+        <v>702</v>
+      </c>
     </row>
-    <row r="31" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="92">
         <v>28</v>
       </c>
@@ -38991,8 +40591,26 @@
       <c r="IS31" s="159">
         <v>9</v>
       </c>
+      <c r="IT31" s="184">
+        <v>20</v>
+      </c>
+      <c r="IU31" s="184">
+        <v>20</v>
+      </c>
+      <c r="IV31" s="184">
+        <v>20</v>
+      </c>
+      <c r="IX31" s="184">
+        <v>7</v>
+      </c>
+      <c r="IY31" s="184">
+        <v>3</v>
+      </c>
+      <c r="IZ31" s="184">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="92">
         <v>29</v>
       </c>
@@ -39748,8 +41366,26 @@
       <c r="IS32" s="184" t="s">
         <v>849</v>
       </c>
+      <c r="IT32" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="IU32" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="IV32" s="184" t="s">
+        <v>698</v>
+      </c>
+      <c r="IX32" s="159" t="s">
+        <v>697</v>
+      </c>
+      <c r="IY32" s="159" t="s">
+        <v>699</v>
+      </c>
+      <c r="IZ32" s="159" t="s">
+        <v>697</v>
+      </c>
     </row>
-    <row r="33" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="92">
         <v>30</v>
       </c>
@@ -40505,8 +42141,26 @@
       <c r="IS33" s="159">
         <v>4</v>
       </c>
+      <c r="IT33" s="184">
+        <v>2</v>
+      </c>
+      <c r="IU33" s="184">
+        <v>2</v>
+      </c>
+      <c r="IV33" s="184">
+        <v>2</v>
+      </c>
+      <c r="IX33" s="159">
+        <v>6</v>
+      </c>
+      <c r="IY33" s="159">
+        <v>6</v>
+      </c>
+      <c r="IZ33" s="159">
+        <v>6</v>
+      </c>
     </row>
-    <row r="34" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="92">
         <v>31</v>
       </c>
@@ -41262,8 +42916,26 @@
       <c r="IS34" s="184" t="s">
         <v>11</v>
       </c>
+      <c r="IT34" s="184" t="s">
+        <v>702</v>
+      </c>
+      <c r="IU34" s="184" t="s">
+        <v>702</v>
+      </c>
+      <c r="IV34" s="184" t="s">
+        <v>702</v>
+      </c>
+      <c r="IX34" s="159" t="s">
+        <v>698</v>
+      </c>
+      <c r="IY34" s="159" t="s">
+        <v>700</v>
+      </c>
+      <c r="IZ34" s="159" t="s">
+        <v>2179</v>
+      </c>
     </row>
-    <row r="35" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="92">
         <v>32</v>
       </c>
@@ -42019,8 +43691,26 @@
       <c r="IS35" s="184" t="s">
         <v>11</v>
       </c>
+      <c r="IT35" s="184">
+        <v>3</v>
+      </c>
+      <c r="IU35" s="184">
+        <v>3</v>
+      </c>
+      <c r="IV35" s="184">
+        <v>3</v>
+      </c>
+      <c r="IX35" s="184">
+        <v>2</v>
+      </c>
+      <c r="IY35" s="184">
+        <v>6</v>
+      </c>
+      <c r="IZ35" s="159">
+        <v>88</v>
+      </c>
     </row>
-    <row r="36" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="92">
         <v>33</v>
       </c>
@@ -42776,8 +44466,26 @@
       <c r="IS36" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT36" s="159" t="s">
+        <v>699</v>
+      </c>
+      <c r="IU36" s="159" t="s">
+        <v>699</v>
+      </c>
+      <c r="IV36" s="159" t="s">
+        <v>699</v>
+      </c>
+      <c r="IX36" s="159" t="s">
+        <v>702</v>
+      </c>
+      <c r="IY36" s="159" t="s">
+        <v>2179</v>
+      </c>
+      <c r="IZ36" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="37" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="92">
         <v>34</v>
       </c>
@@ -43533,8 +45241,26 @@
       <c r="IS37" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT37" s="159">
+        <v>6</v>
+      </c>
+      <c r="IU37" s="159">
+        <v>6</v>
+      </c>
+      <c r="IV37" s="159">
+        <v>6</v>
+      </c>
+      <c r="IX37" s="159">
+        <v>3</v>
+      </c>
+      <c r="IY37" s="159">
+        <v>88</v>
+      </c>
+      <c r="IZ37" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="38" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="92">
         <v>35</v>
       </c>
@@ -44290,8 +46016,26 @@
       <c r="IS38" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT38" s="159" t="s">
+        <v>700</v>
+      </c>
+      <c r="IU38" s="159" t="s">
+        <v>700</v>
+      </c>
+      <c r="IV38" s="159" t="s">
+        <v>700</v>
+      </c>
+      <c r="IX38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY38" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ38" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="39" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="92">
         <v>36</v>
       </c>
@@ -45047,8 +46791,26 @@
       <c r="IS39" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT39" s="184">
+        <v>6</v>
+      </c>
+      <c r="IU39" s="184">
+        <v>6</v>
+      </c>
+      <c r="IV39" s="184">
+        <v>6</v>
+      </c>
+      <c r="IX39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY39" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ39" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="40" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="92">
         <v>37</v>
       </c>
@@ -45804,8 +47566,26 @@
       <c r="IS40" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY40" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ40" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="41" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="92">
         <v>38</v>
       </c>
@@ -46561,8 +48341,26 @@
       <c r="IS41" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY41" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ41" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="42" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="92">
         <v>39</v>
       </c>
@@ -47318,8 +49116,26 @@
       <c r="IS42" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY42" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ42" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="43" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="92">
         <v>40</v>
       </c>
@@ -48075,8 +49891,26 @@
       <c r="IS43" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY43" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ43" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="44" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="92">
         <v>41</v>
       </c>
@@ -48832,8 +50666,26 @@
       <c r="IS44" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY44" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ44" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="45" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="92">
         <v>42</v>
       </c>
@@ -49589,8 +51441,26 @@
       <c r="IS45" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY45" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ45" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="46" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="92">
         <v>43</v>
       </c>
@@ -50346,8 +52216,26 @@
       <c r="IS46" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY46" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ46" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="47" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="92">
         <v>44</v>
       </c>
@@ -51103,8 +52991,26 @@
       <c r="IS47" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY47" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ47" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="48" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="92">
         <v>45</v>
       </c>
@@ -51860,8 +53766,26 @@
       <c r="IS48" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY48" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ48" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="49" spans="1:253" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:260" s="68" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="92">
         <v>46</v>
       </c>
@@ -52617,8 +54541,26 @@
       <c r="IS49" s="159" t="s">
         <v>11</v>
       </c>
+      <c r="IT49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IV49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IX49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IY49" s="159" t="s">
+        <v>11</v>
+      </c>
+      <c r="IZ49" s="159" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="50" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="92">
         <v>47</v>
       </c>
@@ -53376,8 +55318,26 @@
       <c r="IS50" s="115" t="s">
         <v>2229</v>
       </c>
+      <c r="IT50" s="115" t="s">
+        <v>3776</v>
+      </c>
+      <c r="IU50" s="115" t="s">
+        <v>3776</v>
+      </c>
+      <c r="IV50" s="115" t="s">
+        <v>3776</v>
+      </c>
+      <c r="IX50" s="159" t="s">
+        <v>3979</v>
+      </c>
+      <c r="IY50" s="115" t="s">
+        <v>3988</v>
+      </c>
+      <c r="IZ50" s="115" t="s">
+        <v>4002</v>
+      </c>
     </row>
-    <row r="51" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="92">
         <v>48</v>
       </c>
@@ -54135,8 +56095,26 @@
       <c r="IS51" s="115" t="s">
         <v>3857</v>
       </c>
+      <c r="IT51" s="115" t="s">
+        <v>3871</v>
+      </c>
+      <c r="IU51" s="115" t="s">
+        <v>3883</v>
+      </c>
+      <c r="IV51" s="159" t="s">
+        <v>3901</v>
+      </c>
+      <c r="IX51" s="159" t="s">
+        <v>3980</v>
+      </c>
+      <c r="IY51" s="115" t="s">
+        <v>3989</v>
+      </c>
+      <c r="IZ51" s="115" t="s">
+        <v>4003</v>
+      </c>
     </row>
-    <row r="52" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="92">
         <v>49</v>
       </c>
@@ -54894,8 +56872,26 @@
       <c r="IS52" s="115" t="s">
         <v>3858</v>
       </c>
+      <c r="IT52" s="159" t="s">
+        <v>3778</v>
+      </c>
+      <c r="IU52" s="115" t="s">
+        <v>3778</v>
+      </c>
+      <c r="IV52" s="115" t="s">
+        <v>3778</v>
+      </c>
+      <c r="IX52" s="159" t="s">
+        <v>3619</v>
+      </c>
+      <c r="IY52" s="115" t="s">
+        <v>3990</v>
+      </c>
+      <c r="IZ52" s="115" t="s">
+        <v>4004</v>
+      </c>
     </row>
-    <row r="53" spans="1:253" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:260" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="92">
         <v>50</v>
       </c>
@@ -55655,8 +57651,26 @@
       <c r="IS53" s="183" t="s">
         <v>206</v>
       </c>
+      <c r="IT53" s="183" t="s">
+        <v>206</v>
+      </c>
+      <c r="IU53" s="185" t="s">
+        <v>206</v>
+      </c>
+      <c r="IV53" s="185" t="s">
+        <v>206</v>
+      </c>
+      <c r="IX53" s="183" t="s">
+        <v>206</v>
+      </c>
+      <c r="IY53" s="185" t="s">
+        <v>206</v>
+      </c>
+      <c r="IZ53" s="185" t="s">
+        <v>206</v>
+      </c>
     </row>
-    <row r="54" spans="1:253" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:260" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A54" s="92">
         <v>51</v>
       </c>
@@ -56414,8 +58428,26 @@
       <c r="IS54" s="115" t="s">
         <v>61</v>
       </c>
+      <c r="IT54" s="183" t="s">
+        <v>61</v>
+      </c>
+      <c r="IU54" s="185" t="s">
+        <v>61</v>
+      </c>
+      <c r="IV54" s="185" t="s">
+        <v>61</v>
+      </c>
+      <c r="IX54" s="159" t="s">
+        <v>2651</v>
+      </c>
+      <c r="IY54" s="185" t="s">
+        <v>3109</v>
+      </c>
+      <c r="IZ54" s="185" t="s">
+        <v>3109</v>
+      </c>
     </row>
-    <row r="55" spans="1:253" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:260" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A55" s="92">
         <v>52</v>
       </c>
@@ -57173,8 +59205,26 @@
       <c r="IS55" s="159" t="s">
         <v>3859</v>
       </c>
+      <c r="IT55" s="183" t="s">
+        <v>3872</v>
+      </c>
+      <c r="IU55" s="185" t="s">
+        <v>3884</v>
+      </c>
+      <c r="IV55" s="185" t="s">
+        <v>3243</v>
+      </c>
+      <c r="IX55" s="159" t="s">
+        <v>3981</v>
+      </c>
+      <c r="IY55" s="185" t="s">
+        <v>40</v>
+      </c>
+      <c r="IZ55" s="185" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="56" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="92">
         <v>53</v>
       </c>
@@ -57930,8 +59980,26 @@
       <c r="IS56" s="159" t="s">
         <v>3860</v>
       </c>
+      <c r="IT56" s="183" t="s">
+        <v>3873</v>
+      </c>
+      <c r="IU56" s="185" t="s">
+        <v>3885</v>
+      </c>
+      <c r="IV56" s="185" t="s">
+        <v>3902</v>
+      </c>
+      <c r="IX56" s="215" t="s">
+        <v>3981</v>
+      </c>
+      <c r="IY56" s="185" t="s">
+        <v>3991</v>
+      </c>
+      <c r="IZ56" s="185" t="s">
+        <v>3991</v>
+      </c>
     </row>
-    <row r="57" spans="1:253" ht="13.8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:260" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A57" s="92">
         <v>54</v>
       </c>
@@ -58689,8 +60757,26 @@
       <c r="IS57" s="159" t="s">
         <v>3861</v>
       </c>
+      <c r="IT57" s="159" t="s">
+        <v>3874</v>
+      </c>
+      <c r="IU57" s="115" t="s">
+        <v>3886</v>
+      </c>
+      <c r="IV57" s="115" t="s">
+        <v>3903</v>
+      </c>
+      <c r="IX57" s="159" t="s">
+        <v>3981</v>
+      </c>
+      <c r="IY57" s="115" t="s">
+        <v>3671</v>
+      </c>
+      <c r="IZ57" s="115" t="s">
+        <v>3671</v>
+      </c>
     </row>
-    <row r="58" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="92">
         <v>55</v>
       </c>
@@ -59419,8 +61505,26 @@
       <c r="IS58" s="159" t="s">
         <v>3860</v>
       </c>
+      <c r="IT58" s="183" t="s">
+        <v>3873</v>
+      </c>
+      <c r="IU58" s="185" t="s">
+        <v>3887</v>
+      </c>
+      <c r="IV58" s="185" t="s">
+        <v>3904</v>
+      </c>
+      <c r="IX58" s="215" t="s">
+        <v>3981</v>
+      </c>
+      <c r="IY58" s="185" t="s">
+        <v>3991</v>
+      </c>
+      <c r="IZ58" s="185" t="s">
+        <v>3991</v>
+      </c>
     </row>
-    <row r="59" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="92">
         <v>56</v>
       </c>
@@ -60178,8 +62282,26 @@
       <c r="IS59" s="159" t="s">
         <v>3860</v>
       </c>
+      <c r="IT59" s="183" t="s">
+        <v>3873</v>
+      </c>
+      <c r="IU59" s="185" t="s">
+        <v>3887</v>
+      </c>
+      <c r="IV59" s="185" t="s">
+        <v>3904</v>
+      </c>
+      <c r="IX59" s="215" t="s">
+        <v>3981</v>
+      </c>
+      <c r="IY59" s="185" t="s">
+        <v>3991</v>
+      </c>
+      <c r="IZ59" s="185" t="s">
+        <v>3991</v>
+      </c>
     </row>
-    <row r="60" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="92">
         <v>57</v>
       </c>
@@ -60937,8 +63059,26 @@
       <c r="IS60" s="182">
         <v>1</v>
       </c>
+      <c r="IT60" s="182">
+        <v>1</v>
+      </c>
+      <c r="IU60" s="184">
+        <v>1</v>
+      </c>
+      <c r="IV60" s="184">
+        <v>1</v>
+      </c>
+      <c r="IX60" s="65">
+        <v>1</v>
+      </c>
+      <c r="IY60" s="184">
+        <v>1</v>
+      </c>
+      <c r="IZ60" s="184">
+        <v>1</v>
+      </c>
     </row>
-    <row r="61" spans="1:253" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:260" ht="14.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="92">
         <v>58</v>
       </c>
@@ -61696,8 +63836,26 @@
       <c r="IS61" s="157">
         <v>46028</v>
       </c>
+      <c r="IT61" s="221">
+        <v>46029</v>
+      </c>
+      <c r="IU61" s="157">
+        <v>46028</v>
+      </c>
+      <c r="IV61" s="157">
+        <v>45823</v>
+      </c>
+      <c r="IX61" s="157">
+        <v>46031</v>
+      </c>
+      <c r="IY61" s="157">
+        <v>46031</v>
+      </c>
+      <c r="IZ61" s="157">
+        <v>46031</v>
+      </c>
     </row>
-    <row r="62" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="92">
         <v>59</v>
       </c>
@@ -62455,8 +64613,26 @@
       <c r="IS62" s="157">
         <v>46028</v>
       </c>
+      <c r="IT62" s="221">
+        <v>46029</v>
+      </c>
+      <c r="IU62" s="157">
+        <v>46028</v>
+      </c>
+      <c r="IV62" s="157">
+        <v>45825</v>
+      </c>
+      <c r="IX62" s="157">
+        <v>46031</v>
+      </c>
+      <c r="IY62" s="157">
+        <v>46031</v>
+      </c>
+      <c r="IZ62" s="157">
+        <v>46031</v>
+      </c>
     </row>
-    <row r="63" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="92">
         <v>60</v>
       </c>
@@ -63214,8 +65390,26 @@
       <c r="IS63" s="115" t="s">
         <v>30</v>
       </c>
+      <c r="IT63" s="159" t="s">
+        <v>30</v>
+      </c>
+      <c r="IU63" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="IV63" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="IX63" s="169" t="s">
+        <v>30</v>
+      </c>
+      <c r="IY63" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="IZ63" s="115" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="64" spans="1:253" ht="14.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:260" ht="14.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="92">
         <v>61</v>
       </c>
@@ -63972,6 +66166,24 @@
       </c>
       <c r="IS64" s="115" t="s">
         <v>3165</v>
+      </c>
+      <c r="IT64" s="159" t="s">
+        <v>3875</v>
+      </c>
+      <c r="IU64" s="217" t="s">
+        <v>3888</v>
+      </c>
+      <c r="IV64" s="159" t="s">
+        <v>3900</v>
+      </c>
+      <c r="IX64" s="185" t="s">
+        <v>3580</v>
+      </c>
+      <c r="IY64" s="159" t="s">
+        <v>3994</v>
+      </c>
+      <c r="IZ64" s="159" t="s">
+        <v>4005</v>
       </c>
     </row>
     <row r="65" spans="1:263" ht="14.4" x14ac:dyDescent="0.55000000000000004">
@@ -64435,6 +66647,24 @@
       <c r="IS65" s="157">
         <v>46028</v>
       </c>
+      <c r="IT65" s="221">
+        <v>46029</v>
+      </c>
+      <c r="IU65" s="157">
+        <v>46028</v>
+      </c>
+      <c r="IV65" s="221">
+        <v>46029</v>
+      </c>
+      <c r="IX65" s="157">
+        <v>46031</v>
+      </c>
+      <c r="IY65" s="157">
+        <v>46031</v>
+      </c>
+      <c r="IZ65" s="157">
+        <v>46031</v>
+      </c>
     </row>
     <row r="66" spans="1:263" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A66" s="92">
@@ -64893,6 +67123,24 @@
         <v>30</v>
       </c>
       <c r="IS66" s="169" t="s">
+        <v>30</v>
+      </c>
+      <c r="IT66" s="159" t="s">
+        <v>30</v>
+      </c>
+      <c r="IU66" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="IV66" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="IX66" s="169" t="s">
+        <v>30</v>
+      </c>
+      <c r="IY66" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="IZ66" s="115" t="s">
         <v>30</v>
       </c>
     </row>
@@ -65055,6 +67303,12 @@
       <c r="IM67" s="156"/>
       <c r="IQ67" s="206"/>
       <c r="IR67" s="156"/>
+      <c r="IT67" s="237"/>
+      <c r="IU67" s="206"/>
+      <c r="IV67" s="206"/>
+      <c r="IX67" s="156"/>
+      <c r="IY67" s="206"/>
+      <c r="IZ67" s="206"/>
     </row>
     <row r="68" spans="1:263" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A68" s="92">
@@ -65142,7 +67396,21 @@
       <c r="HK68" s="185"/>
       <c r="HL68" s="156"/>
       <c r="HM68" s="169"/>
+      <c r="IK68" s="237" t="s">
+        <v>3876</v>
+      </c>
       <c r="IR68" s="156"/>
+      <c r="IT68" s="237" t="s">
+        <v>3876</v>
+      </c>
+      <c r="IU68" s="237" t="s">
+        <v>3876</v>
+      </c>
+      <c r="IV68" s="237" t="s">
+        <v>3876</v>
+      </c>
+      <c r="IX68" s="156"/>
+      <c r="IY68" s="206"/>
     </row>
     <row r="69" spans="1:263" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A69" s="92">
@@ -65198,6 +67466,9 @@
       <c r="HK69" s="185"/>
       <c r="HM69" s="156"/>
       <c r="IR69" s="156"/>
+      <c r="IU69" s="206"/>
+      <c r="IV69" s="206"/>
+      <c r="IY69" s="206"/>
     </row>
     <row r="70" spans="1:263" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A70" s="92">
@@ -65240,6 +67511,7 @@
       <c r="GW70" s="206"/>
       <c r="HK70" s="156"/>
       <c r="IR70" s="156"/>
+      <c r="IV70" s="206"/>
     </row>
     <row r="71" spans="1:263" ht="13.8" x14ac:dyDescent="0.45">
       <c r="A71" s="92">
